--- a/cd3_automation_toolkit/example/CD3-Azure-template.xlsx
+++ b/cd3_automation_toolkit/example/CD3-Azure-template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10621"/>
   <workbookPr updateLinks="never" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/susingla/PycharmProjects/orahub-develop/cd3_automation_toolkit/example/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B020AF44-9EAB-B442-B5EF-65782E103F6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{106C4731-84FE-0A4A-9F63-F9F5FA6A0484}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3960" yWindow="3000" windowWidth="30240" windowHeight="17440" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1587,51 +1587,6 @@
     <t>Customer Contacts</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>CD3 Automation Toolkit</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Release - v2025.2.0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-  </si>
-  <si>
     <t>abc@yahoo.com,def@gmail.com</t>
   </si>
   <si>
@@ -2009,6 +1964,51 @@
   </si>
   <si>
     <t>vmname2</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>CD3 Automation Toolkit</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Release - v2026.2.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -4432,7 +4432,7 @@
     <row r="1" spans="1:1" ht="16" thickBot="1"/>
     <row r="2" spans="1:1" ht="59.25" customHeight="1" thickBot="1">
       <c r="A2" s="36" t="s">
-        <v>471</v>
+        <v>541</v>
       </c>
     </row>
   </sheetData>
@@ -4464,7 +4464,7 @@
   <sheetData>
     <row r="1" spans="1:20" ht="79" customHeight="1">
       <c r="A1" s="57" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B1" s="57"/>
       <c r="C1" s="57"/>
@@ -4491,16 +4491,16 @@
         <v>0</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>180</v>
       </c>
       <c r="D2" s="7" t="s">
+        <v>529</v>
+      </c>
+      <c r="E2" s="7" t="s">
         <v>530</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>531</v>
       </c>
       <c r="F2" s="7" t="s">
         <v>110</v>
@@ -4550,19 +4550,19 @@
     </row>
     <row r="3" spans="1:20" ht="63" customHeight="1">
       <c r="A3" s="24" t="s">
+        <v>527</v>
+      </c>
+      <c r="B3" s="24" t="s">
         <v>528</v>
-      </c>
-      <c r="B3" s="24" t="s">
-        <v>529</v>
       </c>
       <c r="C3" s="24" t="s">
         <v>182</v>
       </c>
       <c r="D3" s="25" t="s">
+        <v>532</v>
+      </c>
+      <c r="E3" s="25" t="s">
         <v>533</v>
-      </c>
-      <c r="E3" s="25" t="s">
-        <v>534</v>
       </c>
       <c r="F3" s="24" t="s">
         <v>468</v>
@@ -4604,10 +4604,10 @@
         <v>0</v>
       </c>
       <c r="S3" s="25" t="s">
+        <v>471</v>
+      </c>
+      <c r="T3" s="25" t="s">
         <v>472</v>
-      </c>
-      <c r="T3" s="25" t="s">
-        <v>473</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -4692,7 +4692,7 @@
   <sheetData>
     <row r="1" spans="1:18" ht="20" customHeight="1">
       <c r="A1" s="58" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B1" s="57"/>
       <c r="C1" s="57"/>
@@ -4717,49 +4717,49 @@
         <v>0</v>
       </c>
       <c r="B2" s="47" t="s">
+        <v>473</v>
+      </c>
+      <c r="C2" s="48" t="s">
         <v>474</v>
       </c>
-      <c r="C2" s="48" t="s">
+      <c r="D2" s="47" t="s">
         <v>475</v>
-      </c>
-      <c r="D2" s="47" t="s">
-        <v>476</v>
       </c>
       <c r="E2" s="47" t="s">
         <v>14</v>
       </c>
       <c r="F2" s="47" t="s">
+        <v>476</v>
+      </c>
+      <c r="G2" s="47" t="s">
         <v>477</v>
       </c>
-      <c r="G2" s="47" t="s">
+      <c r="H2" s="47" t="s">
         <v>478</v>
       </c>
-      <c r="H2" s="47" t="s">
+      <c r="I2" s="47" t="s">
         <v>479</v>
       </c>
-      <c r="I2" s="47" t="s">
+      <c r="J2" s="47" t="s">
         <v>480</v>
       </c>
-      <c r="J2" s="47" t="s">
+      <c r="K2" s="47" t="s">
         <v>481</v>
       </c>
-      <c r="K2" s="47" t="s">
+      <c r="L2" s="47" t="s">
         <v>482</v>
       </c>
-      <c r="L2" s="47" t="s">
+      <c r="M2" s="47" t="s">
         <v>483</v>
       </c>
-      <c r="M2" s="47" t="s">
+      <c r="N2" s="47" t="s">
         <v>484</v>
       </c>
-      <c r="N2" s="47" t="s">
+      <c r="O2" s="47" t="s">
         <v>485</v>
       </c>
-      <c r="O2" s="47" t="s">
+      <c r="P2" s="47" t="s">
         <v>486</v>
-      </c>
-      <c r="P2" s="47" t="s">
-        <v>487</v>
       </c>
       <c r="Q2" s="47" t="s">
         <v>470</v>
@@ -4773,16 +4773,16 @@
         <v>467</v>
       </c>
       <c r="B3" s="24" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C3" s="38" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D3" s="24">
         <v>1</v>
       </c>
       <c r="E3" s="38" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="F3" s="25">
         <v>2</v>
@@ -4791,37 +4791,37 @@
         <v>3</v>
       </c>
       <c r="H3" s="24" t="s">
+        <v>489</v>
+      </c>
+      <c r="I3" s="24" t="s">
         <v>490</v>
       </c>
-      <c r="I3" s="24" t="s">
+      <c r="J3" s="24" t="s">
         <v>491</v>
       </c>
-      <c r="J3" s="24" t="s">
+      <c r="K3" s="24" t="s">
         <v>492</v>
       </c>
-      <c r="K3" s="24" t="s">
+      <c r="L3" s="24" t="s">
         <v>493</v>
-      </c>
-      <c r="L3" s="24" t="s">
-        <v>494</v>
       </c>
       <c r="M3" s="24">
         <v>4</v>
       </c>
       <c r="N3" s="24" t="s">
+        <v>494</v>
+      </c>
+      <c r="O3" s="24" t="s">
         <v>495</v>
-      </c>
-      <c r="O3" s="24" t="s">
-        <v>496</v>
       </c>
       <c r="P3" s="24">
         <v>1</v>
       </c>
       <c r="Q3" s="24" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="R3" s="24" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -4829,16 +4829,16 @@
         <v>467</v>
       </c>
       <c r="B4" s="24" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C4" s="38" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="D4" s="24">
         <v>2</v>
       </c>
       <c r="E4" s="38" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="F4" s="25">
         <v>2</v>
@@ -4847,16 +4847,16 @@
         <v>3</v>
       </c>
       <c r="H4" s="24" t="s">
+        <v>489</v>
+      </c>
+      <c r="I4" s="24" t="s">
         <v>490</v>
       </c>
-      <c r="I4" s="24" t="s">
+      <c r="J4" s="24" t="s">
         <v>491</v>
       </c>
-      <c r="J4" s="24" t="s">
-        <v>492</v>
-      </c>
       <c r="K4" s="24" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="L4" s="24"/>
       <c r="M4" s="24"/>
@@ -4892,7 +4892,7 @@
     </row>
     <row r="13" spans="1:18">
       <c r="D13" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="E13" s="51"/>
     </row>
@@ -7681,7 +7681,7 @@
   <sheetData>
     <row r="1" spans="1:30" s="1" customFormat="1" ht="93" customHeight="1">
       <c r="A1" s="59" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B1" s="60"/>
       <c r="C1" s="60"/>
@@ -7718,67 +7718,67 @@
         <v>0</v>
       </c>
       <c r="B2" s="47" t="s">
+        <v>473</v>
+      </c>
+      <c r="C2" s="48" t="s">
         <v>474</v>
       </c>
-      <c r="C2" s="48" t="s">
-        <v>475</v>
-      </c>
       <c r="D2" s="48" t="s">
+        <v>500</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>529</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>530</v>
+      </c>
+      <c r="G2" s="47" t="s">
         <v>501</v>
       </c>
-      <c r="E2" s="7" t="s">
-        <v>530</v>
-      </c>
-      <c r="F2" s="7" t="s">
-        <v>531</v>
-      </c>
-      <c r="G2" s="47" t="s">
+      <c r="H2" s="47" t="s">
         <v>502</v>
-      </c>
-      <c r="H2" s="47" t="s">
-        <v>503</v>
       </c>
       <c r="I2" s="48" t="s">
         <v>179</v>
       </c>
       <c r="J2" s="47" t="s">
+        <v>503</v>
+      </c>
+      <c r="K2" s="47" t="s">
         <v>504</v>
       </c>
-      <c r="K2" s="47" t="s">
+      <c r="L2" s="47" t="s">
         <v>505</v>
       </c>
-      <c r="L2" s="47" t="s">
+      <c r="M2" s="47" t="s">
         <v>506</v>
       </c>
-      <c r="M2" s="47" t="s">
+      <c r="N2" s="47" t="s">
         <v>507</v>
       </c>
-      <c r="N2" s="47" t="s">
+      <c r="O2" s="47" t="s">
+        <v>521</v>
+      </c>
+      <c r="P2" s="47" t="s">
+        <v>522</v>
+      </c>
+      <c r="Q2" s="47" t="s">
+        <v>525</v>
+      </c>
+      <c r="R2" s="47" t="s">
+        <v>515</v>
+      </c>
+      <c r="S2" s="47" t="s">
+        <v>516</v>
+      </c>
+      <c r="T2" s="47" t="s">
         <v>508</v>
       </c>
-      <c r="O2" s="47" t="s">
-        <v>522</v>
-      </c>
-      <c r="P2" s="47" t="s">
-        <v>523</v>
-      </c>
-      <c r="Q2" s="47" t="s">
-        <v>526</v>
-      </c>
-      <c r="R2" s="47" t="s">
-        <v>516</v>
-      </c>
-      <c r="S2" s="47" t="s">
+      <c r="U2" s="47" t="s">
+        <v>509</v>
+      </c>
+      <c r="V2" s="47" t="s">
         <v>517</v>
-      </c>
-      <c r="T2" s="47" t="s">
-        <v>509</v>
-      </c>
-      <c r="U2" s="47" t="s">
-        <v>510</v>
-      </c>
-      <c r="V2" s="47" t="s">
-        <v>518</v>
       </c>
       <c r="W2" s="53" t="s">
         <v>461</v>
@@ -7796,22 +7796,22 @@
         <v>467</v>
       </c>
       <c r="B3" s="24" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C3" s="38" t="s">
+        <v>510</v>
+      </c>
+      <c r="D3" s="24" t="s">
         <v>511</v>
       </c>
-      <c r="D3" s="24" t="s">
+      <c r="E3" s="25" t="s">
+        <v>535</v>
+      </c>
+      <c r="F3" s="25" t="s">
+        <v>533</v>
+      </c>
+      <c r="G3" s="25" t="s">
         <v>512</v>
-      </c>
-      <c r="E3" s="25" t="s">
-        <v>536</v>
-      </c>
-      <c r="F3" s="25" t="s">
-        <v>534</v>
-      </c>
-      <c r="G3" s="25" t="s">
-        <v>513</v>
       </c>
       <c r="H3" s="24">
         <v>4</v>
@@ -7820,10 +7820,10 @@
         <v>225</v>
       </c>
       <c r="J3" s="38" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="K3" s="38" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="L3" s="38">
         <v>914</v>
@@ -7835,10 +7835,10 @@
         <v>96</v>
       </c>
       <c r="O3" s="38" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="P3" s="56" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="Q3" s="56"/>
       <c r="R3" s="38" t="b">
@@ -7848,16 +7848,16 @@
         <v>0</v>
       </c>
       <c r="T3" s="38" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="U3" s="55" t="s">
+        <v>513</v>
+      </c>
+      <c r="V3" s="55" t="s">
+        <v>518</v>
+      </c>
+      <c r="W3" s="25" t="s">
         <v>514</v>
-      </c>
-      <c r="V3" s="55" t="s">
-        <v>519</v>
-      </c>
-      <c r="W3" s="25" t="s">
-        <v>515</v>
       </c>
     </row>
     <row r="4" spans="1:30" ht="48">
@@ -7865,22 +7865,22 @@
         <v>467</v>
       </c>
       <c r="B4" s="24" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C4" s="38" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="D4" s="24" t="s">
+        <v>536</v>
+      </c>
+      <c r="E4" s="25" t="s">
         <v>537</v>
       </c>
-      <c r="E4" s="25" t="s">
+      <c r="F4" s="25" t="s">
         <v>538</v>
       </c>
-      <c r="F4" s="25" t="s">
-        <v>539</v>
-      </c>
       <c r="G4" s="25" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H4" s="24">
         <v>4</v>
@@ -7889,10 +7889,10 @@
         <v>225</v>
       </c>
       <c r="J4" s="38" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="K4" s="38" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="L4" s="38">
         <v>914</v>
@@ -7904,10 +7904,10 @@
         <v>96</v>
       </c>
       <c r="O4" s="38" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="P4" s="56" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="Q4" s="56"/>
       <c r="R4" s="38" t="b">
@@ -7917,16 +7917,16 @@
         <v>0</v>
       </c>
       <c r="T4" s="38" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="U4" s="55" t="s">
+        <v>513</v>
+      </c>
+      <c r="V4" s="55" t="s">
+        <v>518</v>
+      </c>
+      <c r="W4" s="25" t="s">
         <v>514</v>
-      </c>
-      <c r="V4" s="55" t="s">
-        <v>519</v>
-      </c>
-      <c r="W4" s="25" t="s">
-        <v>515</v>
       </c>
     </row>
     <row r="5" spans="1:30">

--- a/cd3_automation_toolkit/example/CD3-Azure-template.xlsx
+++ b/cd3_automation_toolkit/example/CD3-Azure-template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10621"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10726"/>
   <workbookPr updateLinks="never" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/susingla/PycharmProjects/orahub-develop/cd3_automation_toolkit/example/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ulaganathan/Documents/CD3_Developer/release-v2026.2.0/outputs/workbook-audit-v2026.2.0-20260731/candidate/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{106C4731-84FE-0A4A-9F63-F9F5FA6A0484}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF26B8A2-93CD-1743-80E5-C440DC473D49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3960" yWindow="3000" windowWidth="30240" windowHeight="17440" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1768,186 +1768,12 @@
     <t>ODB Network Subnet Details</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve"># Rows after &lt;END&gt; will not be processed (Sample data is provided for reference after &lt;END&gt;);
-ODB Network Details  : </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">CREATE::&lt;Resource_Group_Name&gt;::&lt;VNet_Name&gt;::&lt;Region&gt;::&lt;CIDR&gt;
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">ODB Network Subnet Details : </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>&lt;Client_Subnet_Name&gt;::&lt;CIDR&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Admin Password  : P</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>assword must be 9 to 30 characters and contain at least 2 uppercase, 2 lowercase, 2 special, and 2 numeric 
-                                  characters. The special characters must be _, #, or -.</t>
-    </r>
-  </si>
-  <si>
     <t>CREATE::odb_network::VNET1::eastus2::10.0.0.0/16</t>
   </si>
   <si>
     <t>Client-Subnet::10.0.1.0/24</t>
   </si>
   <si>
-    <r>
-      <t># Rows after &lt;END&gt; will not be processed (Sample data is provided for reference after &lt;END&gt;);</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Change CPU core as per shape selected.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">ODB Network Details  : </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>CREATE::&lt;Resource_Group_Name&gt;::&lt;VNet_Name&gt;::&lt;Region&gt;::&lt;CIDR&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-ODB Network Subnet Details : </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>&lt;Client_Subnet_Name&gt;::&lt;CIDR&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>"Time Zone"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> - Specify the time zone to use for the DB system.
-                           </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="5" tint="-0.249977111117893"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Example: Asia/Calcutta | UTC | US/Pacific-New</t>
-    </r>
-  </si>
-  <si>
     <t>CREATE::odb_network::VNET1::eastus::10.0.0.0/16</t>
   </si>
   <si>
@@ -1966,56 +1792,28 @@
     <t>vmname2</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>CD3 Automation Toolkit</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Release - v2026.2.0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
+    <t>CD3 Automation Toolkit Release - v2026.2.0
+Added create and offline tfvars support for ADB and Exadata at Azure, plus ADB export. Exadata export is not included.</t>
+  </si>
+  <si>
+    <t># Rows after &lt;END&gt; will not be processed (Sample data is provided for reference after &lt;END&gt;);
+ODB Network Details - New network: CREATE::&lt;Resource_Group_Name&gt;::&lt;VNet_Name&gt;::&lt;Region&gt;::&lt;CIDR&gt;; existing network: &lt;Resource_Group_Name&gt;::&lt;VNet_Name&gt;.
+ODB Network Subnet Details - New subnet: &lt;Client_Subnet_Name&gt;::&lt;CIDR&gt;; existing subnet: &lt;Client_Subnet_Name&gt;.
+Admin Password - Password must be 9 to 30 characters and contain at least 2 uppercase, 2 lowercase, 2 special, and 2 numeric characters. The special characters must be _, #, or -.</t>
+  </si>
+  <si>
+    <t># Rows after &lt;END&gt; will not be processed (Sample data is provided for reference after &lt;END&gt;);
+Change CPU core count as required for the selected shape.
+ODB Network Details - New network: CREATE::&lt;Resource_Group_Name&gt;::&lt;VNet_Name&gt;::&lt;Region&gt;::&lt;CIDR&gt;; existing network: &lt;Resource_Group_Name&gt;::&lt;VNet_Name&gt;.
+ODB Network Subnet Details - New subnet: &lt;Client_Subnet_Name&gt;::&lt;CIDR&gt;; existing subnet: &lt;Client_Subnet_Name&gt;.
+"Time Zone" - Specify the DB system time zone. Examples: Asia/Calcutta | UTC | US/Pacific-New</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="17">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2083,34 +1881,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color theme="5" tint="-0.249977111117893"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -2499,7 +2269,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
       <protection locked="0"/>
@@ -4432,7 +4202,7 @@
     <row r="1" spans="1:1" ht="16" thickBot="1"/>
     <row r="2" spans="1:1" ht="59.25" customHeight="1" thickBot="1">
       <c r="A2" s="36" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
     </row>
   </sheetData>
@@ -4462,9 +4232,9 @@
     <col min="10" max="14" width="10.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="79" customHeight="1">
+    <row r="1" spans="1:20" ht="105" customHeight="1">
       <c r="A1" s="57" t="s">
-        <v>531</v>
+        <v>540</v>
       </c>
       <c r="B1" s="57"/>
       <c r="C1" s="57"/>
@@ -4559,10 +4329,10 @@
         <v>182</v>
       </c>
       <c r="D3" s="25" t="s">
+        <v>531</v>
+      </c>
+      <c r="E3" s="25" t="s">
         <v>532</v>
-      </c>
-      <c r="E3" s="25" t="s">
-        <v>533</v>
       </c>
       <c r="F3" s="24" t="s">
         <v>468</v>
@@ -7679,9 +7449,9 @@
     <col min="32" max="32" width="15.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" s="1" customFormat="1" ht="93" customHeight="1">
+    <row r="1" spans="1:30" s="1" customFormat="1" ht="125" customHeight="1">
       <c r="A1" s="59" t="s">
-        <v>534</v>
+        <v>541</v>
       </c>
       <c r="B1" s="60"/>
       <c r="C1" s="60"/>
@@ -7805,10 +7575,10 @@
         <v>511</v>
       </c>
       <c r="E3" s="25" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="F3" s="25" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="G3" s="25" t="s">
         <v>512</v>
@@ -7820,7 +7590,7 @@
         <v>225</v>
       </c>
       <c r="J3" s="38" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="K3" s="38" t="s">
         <v>526</v>
@@ -7871,13 +7641,13 @@
         <v>510</v>
       </c>
       <c r="D4" s="24" t="s">
+        <v>534</v>
+      </c>
+      <c r="E4" s="25" t="s">
+        <v>535</v>
+      </c>
+      <c r="F4" s="25" t="s">
         <v>536</v>
-      </c>
-      <c r="E4" s="25" t="s">
-        <v>537</v>
-      </c>
-      <c r="F4" s="25" t="s">
-        <v>538</v>
       </c>
       <c r="G4" s="25" t="s">
         <v>512</v>
@@ -7889,7 +7659,7 @@
         <v>225</v>
       </c>
       <c r="J4" s="38" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="K4" s="38" t="s">
         <v>526</v>

--- a/cd3_automation_toolkit/example/CD3-Azure-template.xlsx
+++ b/cd3_automation_toolkit/example/CD3-Azure-template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr updateLinks="never" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ulaganathan/Documents/CD3_Developer/release-v2026.2.0/outputs/workbook-audit-v2026.2.0-20260731/candidate/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ulaganathan/Documents/CD3_Developer/release-v2026.2.0/CD3/Workbook_RichText_Fix_20260731/formatted/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF26B8A2-93CD-1743-80E5-C440DC473D49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2B9A2A49-0575-9B47-B182-67551F29E726}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3960" yWindow="3000" windowWidth="30240" windowHeight="17440" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3960" yWindow="2900" windowWidth="30240" windowHeight="17440" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Release-Info" sheetId="1" r:id="rId1"/>
@@ -1792,28 +1792,201 @@
     <t>vmname2</t>
   </si>
   <si>
-    <t>CD3 Automation Toolkit Release - v2026.2.0
+    <r>
+      <t># Rows after &lt;END&gt; will not be processed (Sample data is provided for reference after &lt;END&gt;);
+ODB Network Details -</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> New network: CREATE::&lt;Resource_Group_Name&gt;::&lt;VNet_Name&gt;::&lt;Region&gt;::&lt;CIDR&gt;; existing network: &lt;Resource_Group_Name&gt;::&lt;VNet_Name&gt;.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ODB Network Subnet Details -</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> New subnet: &lt;Client_Subnet_Name&gt;::&lt;CIDR&gt;; existing subnet: &lt;Client_Subnet_Name&gt;.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Admin Password -</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Password must be 9 to 30 characters and contain at least 2 uppercase, 2 lowercase, 2 special, and 2 numeric characters. The special characters must be _, #, or -.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"># Rows after &lt;END&gt; will not be processed (Sample data is provided for reference after &lt;END&gt;);
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Change CPU core count as required for the selected shape.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ODB Network Details -</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> New network: CREATE::&lt;Resource_Group_Name&gt;::&lt;VNet_Name&gt;::&lt;Region&gt;::&lt;CIDR&gt;; existing network: &lt;Resource_Group_Name&gt;::&lt;VNet_Name&gt;.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ODB Network Subnet Details -</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> New subnet: &lt;Client_Subnet_Name&gt;::&lt;CIDR&gt;; existing subnet: &lt;Client_Subnet_Name&gt;.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"Time Zone" -</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Specify the DB system time zone. </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF903C3A"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Examples: Asia/Calcutta | UTC | US/Pacific-New</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CD3 Automation Toolkit</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Release - v2026.2.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
 Added create and offline tfvars support for ADB and Exadata at Azure, plus ADB export. Exadata export is not included.</t>
-  </si>
-  <si>
-    <t># Rows after &lt;END&gt; will not be processed (Sample data is provided for reference after &lt;END&gt;);
-ODB Network Details - New network: CREATE::&lt;Resource_Group_Name&gt;::&lt;VNet_Name&gt;::&lt;Region&gt;::&lt;CIDR&gt;; existing network: &lt;Resource_Group_Name&gt;::&lt;VNet_Name&gt;.
-ODB Network Subnet Details - New subnet: &lt;Client_Subnet_Name&gt;::&lt;CIDR&gt;; existing subnet: &lt;Client_Subnet_Name&gt;.
-Admin Password - Password must be 9 to 30 characters and contain at least 2 uppercase, 2 lowercase, 2 special, and 2 numeric characters. The special characters must be _, #, or -.</t>
-  </si>
-  <si>
-    <t># Rows after &lt;END&gt; will not be processed (Sample data is provided for reference after &lt;END&gt;);
-Change CPU core count as required for the selected shape.
-ODB Network Details - New network: CREATE::&lt;Resource_Group_Name&gt;::&lt;VNet_Name&gt;::&lt;Region&gt;::&lt;CIDR&gt;; existing network: &lt;Resource_Group_Name&gt;::&lt;VNet_Name&gt;.
-ODB Network Subnet Details - New subnet: &lt;Client_Subnet_Name&gt;::&lt;CIDR&gt;; existing subnet: &lt;Client_Subnet_Name&gt;.
-"Time Zone" - Specify the DB system time zone. Examples: Asia/Calcutta | UTC | US/Pacific-New</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1902,6 +2075,22 @@
       <b/>
       <sz val="10"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF903C3A"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -2126,7 +2315,7 @@
     <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2214,9 +2403,6 @@
     <xf numFmtId="49" fontId="4" fillId="8" borderId="11" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
       <protection hidden="1"/>
@@ -2280,11 +2466,17 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -4201,8 +4393,8 @@
   <sheetData>
     <row r="1" spans="1:1" ht="16" thickBot="1"/>
     <row r="2" spans="1:1" ht="59.25" customHeight="1" thickBot="1">
-      <c r="A2" s="36" t="s">
-        <v>539</v>
+      <c r="A2" s="61" t="s">
+        <v>541</v>
       </c>
     </row>
   </sheetData>
@@ -4233,28 +4425,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="105" customHeight="1">
-      <c r="A1" s="57" t="s">
-        <v>540</v>
-      </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
-      <c r="F1" s="57"/>
-      <c r="G1" s="57"/>
-      <c r="H1" s="57"/>
-      <c r="I1" s="57"/>
-      <c r="J1" s="57"/>
-      <c r="K1" s="57"/>
-      <c r="L1" s="57"/>
-      <c r="M1" s="57"/>
-      <c r="N1" s="57"/>
-      <c r="O1" s="57"/>
-      <c r="P1" s="57"/>
-      <c r="Q1" s="57"/>
-      <c r="R1" s="57"/>
-      <c r="S1" s="57"/>
-      <c r="T1" s="57"/>
+      <c r="A1" s="59" t="s">
+        <v>539</v>
+      </c>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="56"/>
+      <c r="J1" s="56"/>
+      <c r="K1" s="56"/>
+      <c r="L1" s="56"/>
+      <c r="M1" s="56"/>
+      <c r="N1" s="56"/>
+      <c r="O1" s="56"/>
+      <c r="P1" s="56"/>
+      <c r="Q1" s="56"/>
+      <c r="R1" s="56"/>
+      <c r="S1" s="56"/>
+      <c r="T1" s="56"/>
     </row>
     <row r="2" spans="1:20" ht="80">
       <c r="A2" s="7" t="s">
@@ -4275,10 +4467,10 @@
       <c r="F2" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="G2" s="37" t="s">
+      <c r="G2" s="36" t="s">
         <v>90</v>
       </c>
-      <c r="H2" s="37" t="s">
+      <c r="H2" s="36" t="s">
         <v>460</v>
       </c>
       <c r="I2" s="7" t="s">
@@ -4337,10 +4529,10 @@
       <c r="F3" s="24" t="s">
         <v>468</v>
       </c>
-      <c r="G3" s="38" t="s">
+      <c r="G3" s="37" t="s">
         <v>98</v>
       </c>
-      <c r="H3" s="38" t="s">
+      <c r="H3" s="37" t="s">
         <v>469</v>
       </c>
       <c r="I3" s="24">
@@ -4461,97 +4653,97 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="20" customHeight="1">
-      <c r="A1" s="58" t="s">
+      <c r="A1" s="57" t="s">
         <v>519</v>
       </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
-      <c r="F1" s="57"/>
-      <c r="G1" s="57"/>
-      <c r="H1" s="57"/>
-      <c r="I1" s="57"/>
-      <c r="J1" s="57"/>
-      <c r="K1" s="57"/>
-      <c r="L1" s="57"/>
-      <c r="M1" s="57"/>
-      <c r="N1" s="57"/>
-      <c r="O1" s="57"/>
-      <c r="P1" s="57"/>
-      <c r="Q1" s="57"/>
-      <c r="R1" s="57"/>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="56"/>
+      <c r="J1" s="56"/>
+      <c r="K1" s="56"/>
+      <c r="L1" s="56"/>
+      <c r="M1" s="56"/>
+      <c r="N1" s="56"/>
+      <c r="O1" s="56"/>
+      <c r="P1" s="56"/>
+      <c r="Q1" s="56"/>
+      <c r="R1" s="56"/>
     </row>
     <row r="2" spans="1:18" ht="48">
-      <c r="A2" s="47" t="s">
+      <c r="A2" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="47" t="s">
+      <c r="B2" s="46" t="s">
         <v>473</v>
       </c>
-      <c r="C2" s="48" t="s">
+      <c r="C2" s="47" t="s">
         <v>474</v>
       </c>
-      <c r="D2" s="47" t="s">
+      <c r="D2" s="46" t="s">
         <v>475</v>
       </c>
-      <c r="E2" s="47" t="s">
+      <c r="E2" s="46" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="47" t="s">
+      <c r="F2" s="46" t="s">
         <v>476</v>
       </c>
-      <c r="G2" s="47" t="s">
+      <c r="G2" s="46" t="s">
         <v>477</v>
       </c>
-      <c r="H2" s="47" t="s">
+      <c r="H2" s="46" t="s">
         <v>478</v>
       </c>
-      <c r="I2" s="47" t="s">
+      <c r="I2" s="46" t="s">
         <v>479</v>
       </c>
-      <c r="J2" s="47" t="s">
+      <c r="J2" s="46" t="s">
         <v>480</v>
       </c>
-      <c r="K2" s="47" t="s">
+      <c r="K2" s="46" t="s">
         <v>481</v>
       </c>
-      <c r="L2" s="47" t="s">
+      <c r="L2" s="46" t="s">
         <v>482</v>
       </c>
-      <c r="M2" s="47" t="s">
+      <c r="M2" s="46" t="s">
         <v>483</v>
       </c>
-      <c r="N2" s="47" t="s">
+      <c r="N2" s="46" t="s">
         <v>484</v>
       </c>
-      <c r="O2" s="47" t="s">
+      <c r="O2" s="46" t="s">
         <v>485</v>
       </c>
-      <c r="P2" s="47" t="s">
+      <c r="P2" s="46" t="s">
         <v>486</v>
       </c>
-      <c r="Q2" s="47" t="s">
+      <c r="Q2" s="46" t="s">
         <v>470</v>
       </c>
-      <c r="R2" s="49" t="s">
+      <c r="R2" s="48" t="s">
         <v>461</v>
       </c>
     </row>
     <row r="3" spans="1:18">
-      <c r="A3" s="50" t="s">
+      <c r="A3" s="49" t="s">
         <v>467</v>
       </c>
       <c r="B3" s="24" t="s">
         <v>528</v>
       </c>
-      <c r="C3" s="38" t="s">
+      <c r="C3" s="37" t="s">
         <v>487</v>
       </c>
       <c r="D3" s="24">
         <v>1</v>
       </c>
-      <c r="E3" s="38" t="s">
+      <c r="E3" s="37" t="s">
         <v>488</v>
       </c>
       <c r="F3" s="25">
@@ -4595,19 +4787,19 @@
       </c>
     </row>
     <row r="4" spans="1:18">
-      <c r="A4" s="50" t="s">
+      <c r="A4" s="49" t="s">
         <v>467</v>
       </c>
       <c r="B4" s="24" t="s">
         <v>528</v>
       </c>
-      <c r="C4" s="38" t="s">
+      <c r="C4" s="37" t="s">
         <v>497</v>
       </c>
       <c r="D4" s="24">
         <v>2</v>
       </c>
-      <c r="E4" s="38" t="s">
+      <c r="E4" s="37" t="s">
         <v>488</v>
       </c>
       <c r="F4" s="25">
@@ -4637,2764 +4829,2764 @@
       <c r="R4" s="25"/>
     </row>
     <row r="5" spans="1:18">
-      <c r="E5" s="51"/>
+      <c r="E5" s="50"/>
     </row>
     <row r="6" spans="1:18">
-      <c r="E6" s="51"/>
+      <c r="E6" s="50"/>
     </row>
     <row r="7" spans="1:18">
-      <c r="E7" s="51"/>
+      <c r="E7" s="50"/>
     </row>
     <row r="8" spans="1:18">
-      <c r="E8" s="51"/>
+      <c r="E8" s="50"/>
     </row>
     <row r="9" spans="1:18">
-      <c r="E9" s="51"/>
+      <c r="E9" s="50"/>
     </row>
     <row r="10" spans="1:18">
-      <c r="E10" s="51"/>
+      <c r="E10" s="50"/>
     </row>
     <row r="11" spans="1:18">
-      <c r="E11" s="51"/>
+      <c r="E11" s="50"/>
     </row>
     <row r="12" spans="1:18">
-      <c r="E12" s="51"/>
+      <c r="E12" s="50"/>
     </row>
     <row r="13" spans="1:18">
       <c r="D13" t="s">
         <v>499</v>
       </c>
-      <c r="E13" s="51"/>
+      <c r="E13" s="50"/>
     </row>
     <row r="14" spans="1:18">
-      <c r="E14" s="51"/>
+      <c r="E14" s="50"/>
     </row>
     <row r="15" spans="1:18">
-      <c r="E15" s="51"/>
+      <c r="E15" s="50"/>
     </row>
     <row r="16" spans="1:18">
-      <c r="E16" s="51"/>
+      <c r="E16" s="50"/>
     </row>
     <row r="17" spans="5:5">
-      <c r="E17" s="51"/>
+      <c r="E17" s="50"/>
     </row>
     <row r="18" spans="5:5">
-      <c r="E18" s="51"/>
+      <c r="E18" s="50"/>
     </row>
     <row r="19" spans="5:5">
-      <c r="E19" s="51"/>
+      <c r="E19" s="50"/>
     </row>
     <row r="20" spans="5:5">
-      <c r="E20" s="51"/>
+      <c r="E20" s="50"/>
     </row>
     <row r="21" spans="5:5">
-      <c r="E21" s="51"/>
+      <c r="E21" s="50"/>
     </row>
     <row r="22" spans="5:5">
-      <c r="E22" s="51"/>
+      <c r="E22" s="50"/>
     </row>
     <row r="23" spans="5:5">
-      <c r="E23" s="51"/>
+      <c r="E23" s="50"/>
     </row>
     <row r="24" spans="5:5">
-      <c r="E24" s="51"/>
+      <c r="E24" s="50"/>
     </row>
     <row r="25" spans="5:5">
-      <c r="E25" s="51"/>
+      <c r="E25" s="50"/>
     </row>
     <row r="26" spans="5:5">
-      <c r="E26" s="51"/>
+      <c r="E26" s="50"/>
     </row>
     <row r="27" spans="5:5">
-      <c r="E27" s="51"/>
+      <c r="E27" s="50"/>
     </row>
     <row r="28" spans="5:5">
-      <c r="E28" s="51"/>
+      <c r="E28" s="50"/>
     </row>
     <row r="29" spans="5:5">
-      <c r="E29" s="51"/>
+      <c r="E29" s="50"/>
     </row>
     <row r="30" spans="5:5">
-      <c r="E30" s="51"/>
+      <c r="E30" s="50"/>
     </row>
     <row r="31" spans="5:5">
-      <c r="E31" s="51"/>
+      <c r="E31" s="50"/>
     </row>
     <row r="32" spans="5:5">
-      <c r="E32" s="51"/>
+      <c r="E32" s="50"/>
     </row>
     <row r="33" spans="5:5">
-      <c r="E33" s="51"/>
+      <c r="E33" s="50"/>
     </row>
     <row r="34" spans="5:5">
-      <c r="E34" s="51"/>
+      <c r="E34" s="50"/>
     </row>
     <row r="35" spans="5:5">
-      <c r="E35" s="51"/>
+      <c r="E35" s="50"/>
     </row>
     <row r="36" spans="5:5">
-      <c r="E36" s="51"/>
+      <c r="E36" s="50"/>
     </row>
     <row r="37" spans="5:5">
-      <c r="E37" s="51"/>
+      <c r="E37" s="50"/>
     </row>
     <row r="38" spans="5:5">
-      <c r="E38" s="51"/>
+      <c r="E38" s="50"/>
     </row>
     <row r="39" spans="5:5">
-      <c r="E39" s="51"/>
+      <c r="E39" s="50"/>
     </row>
     <row r="40" spans="5:5">
-      <c r="E40" s="51"/>
+      <c r="E40" s="50"/>
     </row>
     <row r="41" spans="5:5">
-      <c r="E41" s="51"/>
+      <c r="E41" s="50"/>
     </row>
     <row r="42" spans="5:5">
-      <c r="E42" s="51"/>
+      <c r="E42" s="50"/>
     </row>
     <row r="43" spans="5:5">
-      <c r="E43" s="51"/>
+      <c r="E43" s="50"/>
     </row>
     <row r="44" spans="5:5">
-      <c r="E44" s="51"/>
+      <c r="E44" s="50"/>
     </row>
     <row r="45" spans="5:5">
-      <c r="E45" s="51"/>
+      <c r="E45" s="50"/>
     </row>
     <row r="46" spans="5:5">
-      <c r="E46" s="51"/>
+      <c r="E46" s="50"/>
     </row>
     <row r="47" spans="5:5">
-      <c r="E47" s="51"/>
+      <c r="E47" s="50"/>
     </row>
     <row r="48" spans="5:5">
-      <c r="E48" s="51"/>
+      <c r="E48" s="50"/>
     </row>
     <row r="49" spans="5:5">
-      <c r="E49" s="51"/>
+      <c r="E49" s="50"/>
     </row>
     <row r="50" spans="5:5">
-      <c r="E50" s="51"/>
+      <c r="E50" s="50"/>
     </row>
     <row r="51" spans="5:5">
-      <c r="E51" s="51"/>
+      <c r="E51" s="50"/>
     </row>
     <row r="52" spans="5:5">
-      <c r="E52" s="51"/>
+      <c r="E52" s="50"/>
     </row>
     <row r="53" spans="5:5">
-      <c r="E53" s="51"/>
+      <c r="E53" s="50"/>
     </row>
     <row r="54" spans="5:5">
-      <c r="E54" s="51"/>
+      <c r="E54" s="50"/>
     </row>
     <row r="55" spans="5:5">
-      <c r="E55" s="51"/>
+      <c r="E55" s="50"/>
     </row>
     <row r="56" spans="5:5">
-      <c r="E56" s="51"/>
+      <c r="E56" s="50"/>
     </row>
     <row r="57" spans="5:5">
-      <c r="E57" s="51"/>
+      <c r="E57" s="50"/>
     </row>
     <row r="58" spans="5:5">
-      <c r="E58" s="51"/>
+      <c r="E58" s="50"/>
     </row>
     <row r="59" spans="5:5">
-      <c r="E59" s="51"/>
+      <c r="E59" s="50"/>
     </row>
     <row r="60" spans="5:5">
-      <c r="E60" s="51"/>
+      <c r="E60" s="50"/>
     </row>
     <row r="61" spans="5:5">
-      <c r="E61" s="51"/>
+      <c r="E61" s="50"/>
     </row>
     <row r="62" spans="5:5">
-      <c r="E62" s="51"/>
+      <c r="E62" s="50"/>
     </row>
     <row r="63" spans="5:5">
-      <c r="E63" s="51"/>
+      <c r="E63" s="50"/>
     </row>
     <row r="64" spans="5:5">
-      <c r="E64" s="51"/>
+      <c r="E64" s="50"/>
     </row>
     <row r="65" spans="5:5">
-      <c r="E65" s="51"/>
+      <c r="E65" s="50"/>
     </row>
     <row r="66" spans="5:5">
-      <c r="E66" s="51"/>
+      <c r="E66" s="50"/>
     </row>
     <row r="67" spans="5:5">
-      <c r="E67" s="51"/>
+      <c r="E67" s="50"/>
     </row>
     <row r="68" spans="5:5">
-      <c r="E68" s="51"/>
+      <c r="E68" s="50"/>
     </row>
     <row r="69" spans="5:5">
-      <c r="E69" s="51"/>
+      <c r="E69" s="50"/>
     </row>
     <row r="70" spans="5:5">
-      <c r="E70" s="51"/>
+      <c r="E70" s="50"/>
     </row>
     <row r="71" spans="5:5">
-      <c r="E71" s="51"/>
+      <c r="E71" s="50"/>
     </row>
     <row r="72" spans="5:5">
-      <c r="E72" s="51"/>
+      <c r="E72" s="50"/>
     </row>
     <row r="73" spans="5:5">
-      <c r="E73" s="51"/>
+      <c r="E73" s="50"/>
     </row>
     <row r="74" spans="5:5">
-      <c r="E74" s="51"/>
+      <c r="E74" s="50"/>
     </row>
     <row r="75" spans="5:5">
-      <c r="E75" s="51"/>
+      <c r="E75" s="50"/>
     </row>
     <row r="76" spans="5:5">
-      <c r="E76" s="51"/>
+      <c r="E76" s="50"/>
     </row>
     <row r="77" spans="5:5">
-      <c r="E77" s="51"/>
+      <c r="E77" s="50"/>
     </row>
     <row r="78" spans="5:5">
-      <c r="E78" s="51"/>
+      <c r="E78" s="50"/>
     </row>
     <row r="79" spans="5:5">
-      <c r="E79" s="51"/>
+      <c r="E79" s="50"/>
     </row>
     <row r="80" spans="5:5">
-      <c r="E80" s="51"/>
+      <c r="E80" s="50"/>
     </row>
     <row r="81" spans="5:5">
-      <c r="E81" s="51"/>
+      <c r="E81" s="50"/>
     </row>
     <row r="82" spans="5:5">
-      <c r="E82" s="51"/>
+      <c r="E82" s="50"/>
     </row>
     <row r="83" spans="5:5">
-      <c r="E83" s="51"/>
+      <c r="E83" s="50"/>
     </row>
     <row r="84" spans="5:5">
-      <c r="E84" s="51"/>
+      <c r="E84" s="50"/>
     </row>
     <row r="85" spans="5:5">
-      <c r="E85" s="51"/>
+      <c r="E85" s="50"/>
     </row>
     <row r="86" spans="5:5">
-      <c r="E86" s="51"/>
+      <c r="E86" s="50"/>
     </row>
     <row r="87" spans="5:5">
-      <c r="E87" s="51"/>
+      <c r="E87" s="50"/>
     </row>
     <row r="88" spans="5:5">
-      <c r="E88" s="51"/>
+      <c r="E88" s="50"/>
     </row>
     <row r="89" spans="5:5">
-      <c r="E89" s="51"/>
+      <c r="E89" s="50"/>
     </row>
     <row r="90" spans="5:5">
-      <c r="E90" s="51"/>
+      <c r="E90" s="50"/>
     </row>
     <row r="91" spans="5:5">
-      <c r="E91" s="51"/>
+      <c r="E91" s="50"/>
     </row>
     <row r="92" spans="5:5">
-      <c r="E92" s="51"/>
+      <c r="E92" s="50"/>
     </row>
     <row r="93" spans="5:5">
-      <c r="E93" s="51"/>
+      <c r="E93" s="50"/>
     </row>
     <row r="94" spans="5:5">
-      <c r="E94" s="51"/>
+      <c r="E94" s="50"/>
     </row>
     <row r="95" spans="5:5">
-      <c r="E95" s="51"/>
+      <c r="E95" s="50"/>
     </row>
     <row r="96" spans="5:5">
-      <c r="E96" s="51"/>
+      <c r="E96" s="50"/>
     </row>
     <row r="97" spans="5:5">
-      <c r="E97" s="51"/>
+      <c r="E97" s="50"/>
     </row>
     <row r="98" spans="5:5">
-      <c r="E98" s="51"/>
+      <c r="E98" s="50"/>
     </row>
     <row r="99" spans="5:5">
-      <c r="E99" s="51"/>
+      <c r="E99" s="50"/>
     </row>
     <row r="100" spans="5:5">
-      <c r="E100" s="51"/>
+      <c r="E100" s="50"/>
     </row>
     <row r="101" spans="5:5">
-      <c r="E101" s="51"/>
+      <c r="E101" s="50"/>
     </row>
     <row r="102" spans="5:5">
-      <c r="E102" s="51"/>
+      <c r="E102" s="50"/>
     </row>
     <row r="103" spans="5:5">
-      <c r="E103" s="51"/>
+      <c r="E103" s="50"/>
     </row>
     <row r="104" spans="5:5">
-      <c r="E104" s="51"/>
+      <c r="E104" s="50"/>
     </row>
     <row r="105" spans="5:5">
-      <c r="E105" s="51"/>
+      <c r="E105" s="50"/>
     </row>
     <row r="106" spans="5:5">
-      <c r="E106" s="51"/>
+      <c r="E106" s="50"/>
     </row>
     <row r="107" spans="5:5">
-      <c r="E107" s="51"/>
+      <c r="E107" s="50"/>
     </row>
     <row r="108" spans="5:5">
-      <c r="E108" s="51"/>
+      <c r="E108" s="50"/>
     </row>
     <row r="109" spans="5:5">
-      <c r="E109" s="51"/>
+      <c r="E109" s="50"/>
     </row>
     <row r="110" spans="5:5">
-      <c r="E110" s="51"/>
+      <c r="E110" s="50"/>
     </row>
     <row r="111" spans="5:5">
-      <c r="E111" s="51"/>
+      <c r="E111" s="50"/>
     </row>
     <row r="112" spans="5:5">
-      <c r="E112" s="51"/>
+      <c r="E112" s="50"/>
     </row>
     <row r="113" spans="5:5">
-      <c r="E113" s="51"/>
+      <c r="E113" s="50"/>
     </row>
     <row r="114" spans="5:5">
-      <c r="E114" s="51"/>
+      <c r="E114" s="50"/>
     </row>
     <row r="115" spans="5:5">
-      <c r="E115" s="51"/>
+      <c r="E115" s="50"/>
     </row>
     <row r="116" spans="5:5">
-      <c r="E116" s="51"/>
+      <c r="E116" s="50"/>
     </row>
     <row r="117" spans="5:5">
-      <c r="E117" s="51"/>
+      <c r="E117" s="50"/>
     </row>
     <row r="118" spans="5:5">
-      <c r="E118" s="51"/>
+      <c r="E118" s="50"/>
     </row>
     <row r="119" spans="5:5">
-      <c r="E119" s="51"/>
+      <c r="E119" s="50"/>
     </row>
     <row r="120" spans="5:5">
-      <c r="E120" s="51"/>
+      <c r="E120" s="50"/>
     </row>
     <row r="121" spans="5:5">
-      <c r="E121" s="51"/>
+      <c r="E121" s="50"/>
     </row>
     <row r="122" spans="5:5">
-      <c r="E122" s="51"/>
+      <c r="E122" s="50"/>
     </row>
     <row r="123" spans="5:5">
-      <c r="E123" s="51"/>
+      <c r="E123" s="50"/>
     </row>
     <row r="124" spans="5:5">
-      <c r="E124" s="51"/>
+      <c r="E124" s="50"/>
     </row>
     <row r="125" spans="5:5">
-      <c r="E125" s="51"/>
+      <c r="E125" s="50"/>
     </row>
     <row r="126" spans="5:5">
-      <c r="E126" s="51"/>
+      <c r="E126" s="50"/>
     </row>
     <row r="127" spans="5:5">
-      <c r="E127" s="51"/>
+      <c r="E127" s="50"/>
     </row>
     <row r="128" spans="5:5">
-      <c r="E128" s="51"/>
+      <c r="E128" s="50"/>
     </row>
     <row r="129" spans="5:5">
-      <c r="E129" s="51"/>
+      <c r="E129" s="50"/>
     </row>
     <row r="130" spans="5:5">
-      <c r="E130" s="51"/>
+      <c r="E130" s="50"/>
     </row>
     <row r="131" spans="5:5">
-      <c r="E131" s="51"/>
+      <c r="E131" s="50"/>
     </row>
     <row r="132" spans="5:5">
-      <c r="E132" s="51"/>
+      <c r="E132" s="50"/>
     </row>
     <row r="133" spans="5:5">
-      <c r="E133" s="51"/>
+      <c r="E133" s="50"/>
     </row>
     <row r="134" spans="5:5">
-      <c r="E134" s="51"/>
+      <c r="E134" s="50"/>
     </row>
     <row r="135" spans="5:5">
-      <c r="E135" s="51"/>
+      <c r="E135" s="50"/>
     </row>
     <row r="136" spans="5:5">
-      <c r="E136" s="51"/>
+      <c r="E136" s="50"/>
     </row>
     <row r="137" spans="5:5">
-      <c r="E137" s="51"/>
+      <c r="E137" s="50"/>
     </row>
     <row r="138" spans="5:5">
-      <c r="E138" s="51"/>
+      <c r="E138" s="50"/>
     </row>
     <row r="139" spans="5:5">
-      <c r="E139" s="51"/>
+      <c r="E139" s="50"/>
     </row>
     <row r="140" spans="5:5">
-      <c r="E140" s="51"/>
+      <c r="E140" s="50"/>
     </row>
     <row r="141" spans="5:5">
-      <c r="E141" s="51"/>
+      <c r="E141" s="50"/>
     </row>
     <row r="142" spans="5:5">
-      <c r="E142" s="51"/>
+      <c r="E142" s="50"/>
     </row>
     <row r="143" spans="5:5">
-      <c r="E143" s="51"/>
+      <c r="E143" s="50"/>
     </row>
     <row r="144" spans="5:5">
-      <c r="E144" s="51"/>
+      <c r="E144" s="50"/>
     </row>
     <row r="145" spans="5:5">
-      <c r="E145" s="51"/>
+      <c r="E145" s="50"/>
     </row>
     <row r="146" spans="5:5">
-      <c r="E146" s="51"/>
+      <c r="E146" s="50"/>
     </row>
     <row r="147" spans="5:5">
-      <c r="E147" s="51"/>
+      <c r="E147" s="50"/>
     </row>
     <row r="148" spans="5:5">
-      <c r="E148" s="51"/>
+      <c r="E148" s="50"/>
     </row>
     <row r="149" spans="5:5">
-      <c r="E149" s="51"/>
+      <c r="E149" s="50"/>
     </row>
     <row r="150" spans="5:5">
-      <c r="E150" s="51"/>
+      <c r="E150" s="50"/>
     </row>
     <row r="151" spans="5:5">
-      <c r="E151" s="51"/>
+      <c r="E151" s="50"/>
     </row>
     <row r="152" spans="5:5">
-      <c r="E152" s="51"/>
+      <c r="E152" s="50"/>
     </row>
     <row r="153" spans="5:5">
-      <c r="E153" s="51"/>
+      <c r="E153" s="50"/>
     </row>
     <row r="154" spans="5:5">
-      <c r="E154" s="51"/>
+      <c r="E154" s="50"/>
     </row>
     <row r="155" spans="5:5">
-      <c r="E155" s="51"/>
+      <c r="E155" s="50"/>
     </row>
     <row r="156" spans="5:5">
-      <c r="E156" s="51"/>
+      <c r="E156" s="50"/>
     </row>
     <row r="157" spans="5:5">
-      <c r="E157" s="51"/>
+      <c r="E157" s="50"/>
     </row>
     <row r="158" spans="5:5">
-      <c r="E158" s="51"/>
+      <c r="E158" s="50"/>
     </row>
     <row r="159" spans="5:5">
-      <c r="E159" s="51"/>
+      <c r="E159" s="50"/>
     </row>
     <row r="160" spans="5:5">
-      <c r="E160" s="51"/>
+      <c r="E160" s="50"/>
     </row>
     <row r="161" spans="5:5">
-      <c r="E161" s="51"/>
+      <c r="E161" s="50"/>
     </row>
     <row r="162" spans="5:5">
-      <c r="E162" s="51"/>
+      <c r="E162" s="50"/>
     </row>
     <row r="163" spans="5:5">
-      <c r="E163" s="51"/>
+      <c r="E163" s="50"/>
     </row>
     <row r="164" spans="5:5">
-      <c r="E164" s="51"/>
+      <c r="E164" s="50"/>
     </row>
     <row r="165" spans="5:5">
-      <c r="E165" s="51"/>
+      <c r="E165" s="50"/>
     </row>
     <row r="166" spans="5:5">
-      <c r="E166" s="51"/>
+      <c r="E166" s="50"/>
     </row>
     <row r="167" spans="5:5">
-      <c r="E167" s="51"/>
+      <c r="E167" s="50"/>
     </row>
     <row r="168" spans="5:5">
-      <c r="E168" s="51"/>
+      <c r="E168" s="50"/>
     </row>
     <row r="169" spans="5:5">
-      <c r="E169" s="51"/>
+      <c r="E169" s="50"/>
     </row>
     <row r="170" spans="5:5">
-      <c r="E170" s="51"/>
+      <c r="E170" s="50"/>
     </row>
     <row r="171" spans="5:5">
-      <c r="E171" s="51"/>
+      <c r="E171" s="50"/>
     </row>
     <row r="172" spans="5:5">
-      <c r="E172" s="51"/>
+      <c r="E172" s="50"/>
     </row>
     <row r="173" spans="5:5">
-      <c r="E173" s="51"/>
+      <c r="E173" s="50"/>
     </row>
     <row r="174" spans="5:5">
-      <c r="E174" s="51"/>
+      <c r="E174" s="50"/>
     </row>
     <row r="175" spans="5:5">
-      <c r="E175" s="51"/>
+      <c r="E175" s="50"/>
     </row>
     <row r="176" spans="5:5">
-      <c r="E176" s="51"/>
+      <c r="E176" s="50"/>
     </row>
     <row r="177" spans="5:5">
-      <c r="E177" s="51"/>
+      <c r="E177" s="50"/>
     </row>
     <row r="178" spans="5:5">
-      <c r="E178" s="51"/>
+      <c r="E178" s="50"/>
     </row>
     <row r="179" spans="5:5">
-      <c r="E179" s="51"/>
+      <c r="E179" s="50"/>
     </row>
     <row r="180" spans="5:5">
-      <c r="E180" s="51"/>
+      <c r="E180" s="50"/>
     </row>
     <row r="181" spans="5:5">
-      <c r="E181" s="51"/>
+      <c r="E181" s="50"/>
     </row>
     <row r="182" spans="5:5">
-      <c r="E182" s="51"/>
+      <c r="E182" s="50"/>
     </row>
     <row r="183" spans="5:5">
-      <c r="E183" s="51"/>
+      <c r="E183" s="50"/>
     </row>
     <row r="184" spans="5:5">
-      <c r="E184" s="51"/>
+      <c r="E184" s="50"/>
     </row>
     <row r="185" spans="5:5">
-      <c r="E185" s="51"/>
+      <c r="E185" s="50"/>
     </row>
     <row r="186" spans="5:5">
-      <c r="E186" s="51"/>
+      <c r="E186" s="50"/>
     </row>
     <row r="187" spans="5:5">
-      <c r="E187" s="51"/>
+      <c r="E187" s="50"/>
     </row>
     <row r="188" spans="5:5">
-      <c r="E188" s="51"/>
+      <c r="E188" s="50"/>
     </row>
     <row r="189" spans="5:5">
-      <c r="E189" s="51"/>
+      <c r="E189" s="50"/>
     </row>
     <row r="190" spans="5:5">
-      <c r="E190" s="51"/>
+      <c r="E190" s="50"/>
     </row>
     <row r="191" spans="5:5">
-      <c r="E191" s="51"/>
+      <c r="E191" s="50"/>
     </row>
     <row r="192" spans="5:5">
-      <c r="E192" s="51"/>
+      <c r="E192" s="50"/>
     </row>
     <row r="193" spans="5:5">
-      <c r="E193" s="51"/>
+      <c r="E193" s="50"/>
     </row>
     <row r="194" spans="5:5">
-      <c r="E194" s="51"/>
+      <c r="E194" s="50"/>
     </row>
     <row r="195" spans="5:5">
-      <c r="E195" s="51"/>
+      <c r="E195" s="50"/>
     </row>
     <row r="196" spans="5:5">
-      <c r="E196" s="51"/>
+      <c r="E196" s="50"/>
     </row>
     <row r="197" spans="5:5">
-      <c r="E197" s="51"/>
+      <c r="E197" s="50"/>
     </row>
     <row r="198" spans="5:5">
-      <c r="E198" s="51"/>
+      <c r="E198" s="50"/>
     </row>
     <row r="199" spans="5:5">
-      <c r="E199" s="51"/>
+      <c r="E199" s="50"/>
     </row>
     <row r="200" spans="5:5">
-      <c r="E200" s="51"/>
+      <c r="E200" s="50"/>
     </row>
     <row r="201" spans="5:5">
-      <c r="E201" s="51"/>
+      <c r="E201" s="50"/>
     </row>
     <row r="202" spans="5:5">
-      <c r="E202" s="51"/>
+      <c r="E202" s="50"/>
     </row>
     <row r="203" spans="5:5">
-      <c r="E203" s="51"/>
+      <c r="E203" s="50"/>
     </row>
     <row r="204" spans="5:5">
-      <c r="E204" s="51"/>
+      <c r="E204" s="50"/>
     </row>
     <row r="205" spans="5:5">
-      <c r="E205" s="51"/>
+      <c r="E205" s="50"/>
     </row>
     <row r="206" spans="5:5">
-      <c r="E206" s="51"/>
+      <c r="E206" s="50"/>
     </row>
     <row r="207" spans="5:5">
-      <c r="E207" s="51"/>
+      <c r="E207" s="50"/>
     </row>
     <row r="208" spans="5:5">
-      <c r="E208" s="51"/>
+      <c r="E208" s="50"/>
     </row>
     <row r="209" spans="5:5">
-      <c r="E209" s="51"/>
+      <c r="E209" s="50"/>
     </row>
     <row r="210" spans="5:5">
-      <c r="E210" s="51"/>
+      <c r="E210" s="50"/>
     </row>
     <row r="211" spans="5:5">
-      <c r="E211" s="51"/>
+      <c r="E211" s="50"/>
     </row>
     <row r="212" spans="5:5">
-      <c r="E212" s="51"/>
+      <c r="E212" s="50"/>
     </row>
     <row r="213" spans="5:5">
-      <c r="E213" s="51"/>
+      <c r="E213" s="50"/>
     </row>
     <row r="214" spans="5:5">
-      <c r="E214" s="51"/>
+      <c r="E214" s="50"/>
     </row>
     <row r="215" spans="5:5">
-      <c r="E215" s="51"/>
+      <c r="E215" s="50"/>
     </row>
     <row r="216" spans="5:5">
-      <c r="E216" s="51"/>
+      <c r="E216" s="50"/>
     </row>
     <row r="217" spans="5:5">
-      <c r="E217" s="51"/>
+      <c r="E217" s="50"/>
     </row>
     <row r="218" spans="5:5">
-      <c r="E218" s="51"/>
+      <c r="E218" s="50"/>
     </row>
     <row r="219" spans="5:5">
-      <c r="E219" s="51"/>
+      <c r="E219" s="50"/>
     </row>
     <row r="220" spans="5:5">
-      <c r="E220" s="51"/>
+      <c r="E220" s="50"/>
     </row>
     <row r="221" spans="5:5">
-      <c r="E221" s="51"/>
+      <c r="E221" s="50"/>
     </row>
     <row r="222" spans="5:5">
-      <c r="E222" s="51"/>
+      <c r="E222" s="50"/>
     </row>
     <row r="223" spans="5:5">
-      <c r="E223" s="51"/>
+      <c r="E223" s="50"/>
     </row>
     <row r="224" spans="5:5">
-      <c r="E224" s="51"/>
+      <c r="E224" s="50"/>
     </row>
     <row r="225" spans="5:5">
-      <c r="E225" s="51"/>
+      <c r="E225" s="50"/>
     </row>
     <row r="226" spans="5:5">
-      <c r="E226" s="51"/>
+      <c r="E226" s="50"/>
     </row>
     <row r="227" spans="5:5">
-      <c r="E227" s="51"/>
+      <c r="E227" s="50"/>
     </row>
     <row r="228" spans="5:5">
-      <c r="E228" s="51"/>
+      <c r="E228" s="50"/>
     </row>
     <row r="229" spans="5:5">
-      <c r="E229" s="51"/>
+      <c r="E229" s="50"/>
     </row>
     <row r="230" spans="5:5">
-      <c r="E230" s="51"/>
+      <c r="E230" s="50"/>
     </row>
     <row r="231" spans="5:5">
-      <c r="E231" s="51"/>
+      <c r="E231" s="50"/>
     </row>
     <row r="232" spans="5:5">
-      <c r="E232" s="51"/>
+      <c r="E232" s="50"/>
     </row>
     <row r="233" spans="5:5">
-      <c r="E233" s="51"/>
+      <c r="E233" s="50"/>
     </row>
     <row r="234" spans="5:5">
-      <c r="E234" s="51"/>
+      <c r="E234" s="50"/>
     </row>
     <row r="235" spans="5:5">
-      <c r="E235" s="51"/>
+      <c r="E235" s="50"/>
     </row>
     <row r="236" spans="5:5">
-      <c r="E236" s="51"/>
+      <c r="E236" s="50"/>
     </row>
     <row r="237" spans="5:5">
-      <c r="E237" s="51"/>
+      <c r="E237" s="50"/>
     </row>
     <row r="238" spans="5:5">
-      <c r="E238" s="51"/>
+      <c r="E238" s="50"/>
     </row>
     <row r="239" spans="5:5">
-      <c r="E239" s="51"/>
+      <c r="E239" s="50"/>
     </row>
     <row r="240" spans="5:5">
-      <c r="E240" s="51"/>
+      <c r="E240" s="50"/>
     </row>
     <row r="241" spans="5:5">
-      <c r="E241" s="51"/>
+      <c r="E241" s="50"/>
     </row>
     <row r="242" spans="5:5">
-      <c r="E242" s="51"/>
+      <c r="E242" s="50"/>
     </row>
     <row r="243" spans="5:5">
-      <c r="E243" s="51"/>
+      <c r="E243" s="50"/>
     </row>
     <row r="244" spans="5:5">
-      <c r="E244" s="51"/>
+      <c r="E244" s="50"/>
     </row>
     <row r="245" spans="5:5">
-      <c r="E245" s="51"/>
+      <c r="E245" s="50"/>
     </row>
     <row r="246" spans="5:5">
-      <c r="E246" s="51"/>
+      <c r="E246" s="50"/>
     </row>
     <row r="247" spans="5:5">
-      <c r="E247" s="51"/>
+      <c r="E247" s="50"/>
     </row>
     <row r="248" spans="5:5">
-      <c r="E248" s="51"/>
+      <c r="E248" s="50"/>
     </row>
     <row r="249" spans="5:5">
-      <c r="E249" s="51"/>
+      <c r="E249" s="50"/>
     </row>
     <row r="250" spans="5:5">
-      <c r="E250" s="51"/>
+      <c r="E250" s="50"/>
     </row>
     <row r="251" spans="5:5">
-      <c r="E251" s="51"/>
+      <c r="E251" s="50"/>
     </row>
     <row r="252" spans="5:5">
-      <c r="E252" s="51"/>
+      <c r="E252" s="50"/>
     </row>
     <row r="253" spans="5:5">
-      <c r="E253" s="51"/>
+      <c r="E253" s="50"/>
     </row>
     <row r="254" spans="5:5">
-      <c r="E254" s="51"/>
+      <c r="E254" s="50"/>
     </row>
     <row r="255" spans="5:5">
-      <c r="E255" s="51"/>
+      <c r="E255" s="50"/>
     </row>
     <row r="256" spans="5:5">
-      <c r="E256" s="51"/>
+      <c r="E256" s="50"/>
     </row>
     <row r="257" spans="5:5">
-      <c r="E257" s="51"/>
+      <c r="E257" s="50"/>
     </row>
     <row r="258" spans="5:5">
-      <c r="E258" s="51"/>
+      <c r="E258" s="50"/>
     </row>
     <row r="259" spans="5:5">
-      <c r="E259" s="51"/>
+      <c r="E259" s="50"/>
     </row>
     <row r="260" spans="5:5">
-      <c r="E260" s="51"/>
+      <c r="E260" s="50"/>
     </row>
     <row r="261" spans="5:5">
-      <c r="E261" s="51"/>
+      <c r="E261" s="50"/>
     </row>
     <row r="262" spans="5:5">
-      <c r="E262" s="51"/>
+      <c r="E262" s="50"/>
     </row>
     <row r="263" spans="5:5">
-      <c r="E263" s="51"/>
+      <c r="E263" s="50"/>
     </row>
     <row r="264" spans="5:5">
-      <c r="E264" s="51"/>
+      <c r="E264" s="50"/>
     </row>
     <row r="265" spans="5:5">
-      <c r="E265" s="51"/>
+      <c r="E265" s="50"/>
     </row>
     <row r="266" spans="5:5">
-      <c r="E266" s="51"/>
+      <c r="E266" s="50"/>
     </row>
     <row r="267" spans="5:5">
-      <c r="E267" s="51"/>
+      <c r="E267" s="50"/>
     </row>
     <row r="268" spans="5:5">
-      <c r="E268" s="51"/>
+      <c r="E268" s="50"/>
     </row>
     <row r="269" spans="5:5">
-      <c r="E269" s="51"/>
+      <c r="E269" s="50"/>
     </row>
     <row r="270" spans="5:5">
-      <c r="E270" s="51"/>
+      <c r="E270" s="50"/>
     </row>
     <row r="271" spans="5:5">
-      <c r="E271" s="51"/>
+      <c r="E271" s="50"/>
     </row>
     <row r="272" spans="5:5">
-      <c r="E272" s="51"/>
+      <c r="E272" s="50"/>
     </row>
     <row r="273" spans="5:5">
-      <c r="E273" s="51"/>
+      <c r="E273" s="50"/>
     </row>
     <row r="274" spans="5:5">
-      <c r="E274" s="51"/>
+      <c r="E274" s="50"/>
     </row>
     <row r="275" spans="5:5">
-      <c r="E275" s="51"/>
+      <c r="E275" s="50"/>
     </row>
     <row r="276" spans="5:5">
-      <c r="E276" s="51"/>
+      <c r="E276" s="50"/>
     </row>
     <row r="277" spans="5:5">
-      <c r="E277" s="51"/>
+      <c r="E277" s="50"/>
     </row>
     <row r="278" spans="5:5">
-      <c r="E278" s="51"/>
+      <c r="E278" s="50"/>
     </row>
     <row r="279" spans="5:5">
-      <c r="E279" s="51"/>
+      <c r="E279" s="50"/>
     </row>
     <row r="280" spans="5:5">
-      <c r="E280" s="51"/>
+      <c r="E280" s="50"/>
     </row>
     <row r="281" spans="5:5">
-      <c r="E281" s="51"/>
+      <c r="E281" s="50"/>
     </row>
     <row r="282" spans="5:5">
-      <c r="E282" s="51"/>
+      <c r="E282" s="50"/>
     </row>
     <row r="283" spans="5:5">
-      <c r="E283" s="51"/>
+      <c r="E283" s="50"/>
     </row>
     <row r="284" spans="5:5">
-      <c r="E284" s="51"/>
+      <c r="E284" s="50"/>
     </row>
     <row r="285" spans="5:5">
-      <c r="E285" s="51"/>
+      <c r="E285" s="50"/>
     </row>
     <row r="286" spans="5:5">
-      <c r="E286" s="51"/>
+      <c r="E286" s="50"/>
     </row>
     <row r="287" spans="5:5">
-      <c r="E287" s="51"/>
+      <c r="E287" s="50"/>
     </row>
     <row r="288" spans="5:5">
-      <c r="E288" s="51"/>
+      <c r="E288" s="50"/>
     </row>
     <row r="289" spans="5:5">
-      <c r="E289" s="51"/>
+      <c r="E289" s="50"/>
     </row>
     <row r="290" spans="5:5">
-      <c r="E290" s="51"/>
+      <c r="E290" s="50"/>
     </row>
     <row r="291" spans="5:5">
-      <c r="E291" s="51"/>
+      <c r="E291" s="50"/>
     </row>
     <row r="292" spans="5:5">
-      <c r="E292" s="51"/>
+      <c r="E292" s="50"/>
     </row>
     <row r="293" spans="5:5">
-      <c r="E293" s="51"/>
+      <c r="E293" s="50"/>
     </row>
     <row r="294" spans="5:5">
-      <c r="E294" s="51"/>
+      <c r="E294" s="50"/>
     </row>
     <row r="295" spans="5:5">
-      <c r="E295" s="51"/>
+      <c r="E295" s="50"/>
     </row>
     <row r="296" spans="5:5">
-      <c r="E296" s="51"/>
+      <c r="E296" s="50"/>
     </row>
     <row r="297" spans="5:5">
-      <c r="E297" s="51"/>
+      <c r="E297" s="50"/>
     </row>
     <row r="298" spans="5:5">
-      <c r="E298" s="51"/>
+      <c r="E298" s="50"/>
     </row>
     <row r="299" spans="5:5">
-      <c r="E299" s="51"/>
+      <c r="E299" s="50"/>
     </row>
     <row r="300" spans="5:5">
-      <c r="E300" s="51"/>
+      <c r="E300" s="50"/>
     </row>
     <row r="301" spans="5:5">
-      <c r="E301" s="51"/>
+      <c r="E301" s="50"/>
     </row>
     <row r="302" spans="5:5">
-      <c r="E302" s="51"/>
+      <c r="E302" s="50"/>
     </row>
     <row r="303" spans="5:5">
-      <c r="E303" s="51"/>
+      <c r="E303" s="50"/>
     </row>
     <row r="304" spans="5:5">
-      <c r="E304" s="51"/>
+      <c r="E304" s="50"/>
     </row>
     <row r="305" spans="5:5">
-      <c r="E305" s="51"/>
+      <c r="E305" s="50"/>
     </row>
     <row r="306" spans="5:5">
-      <c r="E306" s="51"/>
+      <c r="E306" s="50"/>
     </row>
     <row r="307" spans="5:5">
-      <c r="E307" s="51"/>
+      <c r="E307" s="50"/>
     </row>
     <row r="308" spans="5:5">
-      <c r="E308" s="51"/>
+      <c r="E308" s="50"/>
     </row>
     <row r="309" spans="5:5">
-      <c r="E309" s="51"/>
+      <c r="E309" s="50"/>
     </row>
     <row r="310" spans="5:5">
-      <c r="E310" s="51"/>
+      <c r="E310" s="50"/>
     </row>
     <row r="311" spans="5:5">
-      <c r="E311" s="51"/>
+      <c r="E311" s="50"/>
     </row>
     <row r="312" spans="5:5">
-      <c r="E312" s="51"/>
+      <c r="E312" s="50"/>
     </row>
     <row r="313" spans="5:5">
-      <c r="E313" s="51"/>
+      <c r="E313" s="50"/>
     </row>
     <row r="314" spans="5:5">
-      <c r="E314" s="51"/>
+      <c r="E314" s="50"/>
     </row>
     <row r="315" spans="5:5">
-      <c r="E315" s="51"/>
+      <c r="E315" s="50"/>
     </row>
     <row r="316" spans="5:5">
-      <c r="E316" s="51"/>
+      <c r="E316" s="50"/>
     </row>
     <row r="317" spans="5:5">
-      <c r="E317" s="51"/>
+      <c r="E317" s="50"/>
     </row>
     <row r="318" spans="5:5">
-      <c r="E318" s="51"/>
+      <c r="E318" s="50"/>
     </row>
     <row r="319" spans="5:5">
-      <c r="E319" s="51"/>
+      <c r="E319" s="50"/>
     </row>
     <row r="320" spans="5:5">
-      <c r="E320" s="51"/>
+      <c r="E320" s="50"/>
     </row>
     <row r="321" spans="5:5">
-      <c r="E321" s="51"/>
+      <c r="E321" s="50"/>
     </row>
     <row r="322" spans="5:5">
-      <c r="E322" s="51"/>
+      <c r="E322" s="50"/>
     </row>
     <row r="323" spans="5:5">
-      <c r="E323" s="51"/>
+      <c r="E323" s="50"/>
     </row>
     <row r="324" spans="5:5">
-      <c r="E324" s="51"/>
+      <c r="E324" s="50"/>
     </row>
     <row r="325" spans="5:5">
-      <c r="E325" s="51"/>
+      <c r="E325" s="50"/>
     </row>
     <row r="326" spans="5:5">
-      <c r="E326" s="51"/>
+      <c r="E326" s="50"/>
     </row>
     <row r="327" spans="5:5">
-      <c r="E327" s="51"/>
+      <c r="E327" s="50"/>
     </row>
     <row r="328" spans="5:5">
-      <c r="E328" s="51"/>
+      <c r="E328" s="50"/>
     </row>
     <row r="329" spans="5:5">
-      <c r="E329" s="51"/>
+      <c r="E329" s="50"/>
     </row>
     <row r="330" spans="5:5">
-      <c r="E330" s="51"/>
+      <c r="E330" s="50"/>
     </row>
     <row r="331" spans="5:5">
-      <c r="E331" s="51"/>
+      <c r="E331" s="50"/>
     </row>
     <row r="332" spans="5:5">
-      <c r="E332" s="51"/>
+      <c r="E332" s="50"/>
     </row>
     <row r="333" spans="5:5">
-      <c r="E333" s="51"/>
+      <c r="E333" s="50"/>
     </row>
     <row r="334" spans="5:5">
-      <c r="E334" s="51"/>
+      <c r="E334" s="50"/>
     </row>
     <row r="335" spans="5:5">
-      <c r="E335" s="51"/>
+      <c r="E335" s="50"/>
     </row>
     <row r="336" spans="5:5">
-      <c r="E336" s="51"/>
+      <c r="E336" s="50"/>
     </row>
     <row r="337" spans="5:5">
-      <c r="E337" s="51"/>
+      <c r="E337" s="50"/>
     </row>
     <row r="338" spans="5:5">
-      <c r="E338" s="51"/>
+      <c r="E338" s="50"/>
     </row>
     <row r="339" spans="5:5">
-      <c r="E339" s="51"/>
+      <c r="E339" s="50"/>
     </row>
     <row r="340" spans="5:5">
-      <c r="E340" s="51"/>
+      <c r="E340" s="50"/>
     </row>
     <row r="341" spans="5:5">
-      <c r="E341" s="51"/>
+      <c r="E341" s="50"/>
     </row>
     <row r="342" spans="5:5">
-      <c r="E342" s="51"/>
+      <c r="E342" s="50"/>
     </row>
     <row r="343" spans="5:5">
-      <c r="E343" s="51"/>
+      <c r="E343" s="50"/>
     </row>
     <row r="344" spans="5:5">
-      <c r="E344" s="51"/>
+      <c r="E344" s="50"/>
     </row>
     <row r="345" spans="5:5">
-      <c r="E345" s="51"/>
+      <c r="E345" s="50"/>
     </row>
     <row r="346" spans="5:5">
-      <c r="E346" s="51"/>
+      <c r="E346" s="50"/>
     </row>
     <row r="347" spans="5:5">
-      <c r="E347" s="51"/>
+      <c r="E347" s="50"/>
     </row>
     <row r="348" spans="5:5">
-      <c r="E348" s="51"/>
+      <c r="E348" s="50"/>
     </row>
     <row r="349" spans="5:5">
-      <c r="E349" s="51"/>
+      <c r="E349" s="50"/>
     </row>
     <row r="350" spans="5:5">
-      <c r="E350" s="51"/>
+      <c r="E350" s="50"/>
     </row>
     <row r="351" spans="5:5">
-      <c r="E351" s="51"/>
+      <c r="E351" s="50"/>
     </row>
     <row r="352" spans="5:5">
-      <c r="E352" s="51"/>
+      <c r="E352" s="50"/>
     </row>
     <row r="353" spans="5:5">
-      <c r="E353" s="51"/>
+      <c r="E353" s="50"/>
     </row>
     <row r="354" spans="5:5">
-      <c r="E354" s="51"/>
+      <c r="E354" s="50"/>
     </row>
     <row r="355" spans="5:5">
-      <c r="E355" s="51"/>
+      <c r="E355" s="50"/>
     </row>
     <row r="356" spans="5:5">
-      <c r="E356" s="51"/>
+      <c r="E356" s="50"/>
     </row>
     <row r="357" spans="5:5">
-      <c r="E357" s="51"/>
+      <c r="E357" s="50"/>
     </row>
     <row r="358" spans="5:5">
-      <c r="E358" s="51"/>
+      <c r="E358" s="50"/>
     </row>
     <row r="359" spans="5:5">
-      <c r="E359" s="51"/>
+      <c r="E359" s="50"/>
     </row>
     <row r="360" spans="5:5">
-      <c r="E360" s="51"/>
+      <c r="E360" s="50"/>
     </row>
     <row r="361" spans="5:5">
-      <c r="E361" s="51"/>
+      <c r="E361" s="50"/>
     </row>
     <row r="362" spans="5:5">
-      <c r="E362" s="51"/>
+      <c r="E362" s="50"/>
     </row>
     <row r="363" spans="5:5">
-      <c r="E363" s="51"/>
+      <c r="E363" s="50"/>
     </row>
     <row r="364" spans="5:5">
-      <c r="E364" s="51"/>
+      <c r="E364" s="50"/>
     </row>
     <row r="365" spans="5:5">
-      <c r="E365" s="51"/>
+      <c r="E365" s="50"/>
     </row>
     <row r="366" spans="5:5">
-      <c r="E366" s="51"/>
+      <c r="E366" s="50"/>
     </row>
     <row r="367" spans="5:5">
-      <c r="E367" s="51"/>
+      <c r="E367" s="50"/>
     </row>
     <row r="368" spans="5:5">
-      <c r="E368" s="51"/>
+      <c r="E368" s="50"/>
     </row>
     <row r="369" spans="5:5">
-      <c r="E369" s="51"/>
+      <c r="E369" s="50"/>
     </row>
     <row r="370" spans="5:5">
-      <c r="E370" s="51"/>
+      <c r="E370" s="50"/>
     </row>
     <row r="371" spans="5:5">
-      <c r="E371" s="51"/>
+      <c r="E371" s="50"/>
     </row>
     <row r="372" spans="5:5">
-      <c r="E372" s="51"/>
+      <c r="E372" s="50"/>
     </row>
     <row r="373" spans="5:5">
-      <c r="E373" s="51"/>
+      <c r="E373" s="50"/>
     </row>
     <row r="374" spans="5:5">
-      <c r="E374" s="51"/>
+      <c r="E374" s="50"/>
     </row>
     <row r="375" spans="5:5">
-      <c r="E375" s="51"/>
+      <c r="E375" s="50"/>
     </row>
     <row r="376" spans="5:5">
-      <c r="E376" s="51"/>
+      <c r="E376" s="50"/>
     </row>
     <row r="377" spans="5:5">
-      <c r="E377" s="51"/>
+      <c r="E377" s="50"/>
     </row>
     <row r="378" spans="5:5">
-      <c r="E378" s="51"/>
+      <c r="E378" s="50"/>
     </row>
     <row r="379" spans="5:5">
-      <c r="E379" s="51"/>
+      <c r="E379" s="50"/>
     </row>
     <row r="380" spans="5:5">
-      <c r="E380" s="51"/>
+      <c r="E380" s="50"/>
     </row>
     <row r="381" spans="5:5">
-      <c r="E381" s="51"/>
+      <c r="E381" s="50"/>
     </row>
     <row r="382" spans="5:5">
-      <c r="E382" s="51"/>
+      <c r="E382" s="50"/>
     </row>
     <row r="383" spans="5:5">
-      <c r="E383" s="51"/>
+      <c r="E383" s="50"/>
     </row>
     <row r="384" spans="5:5">
-      <c r="E384" s="51"/>
+      <c r="E384" s="50"/>
     </row>
     <row r="385" spans="5:5">
-      <c r="E385" s="51"/>
+      <c r="E385" s="50"/>
     </row>
     <row r="386" spans="5:5">
-      <c r="E386" s="51"/>
+      <c r="E386" s="50"/>
     </row>
     <row r="387" spans="5:5">
-      <c r="E387" s="51"/>
+      <c r="E387" s="50"/>
     </row>
     <row r="388" spans="5:5">
-      <c r="E388" s="51"/>
+      <c r="E388" s="50"/>
     </row>
     <row r="389" spans="5:5">
-      <c r="E389" s="51"/>
+      <c r="E389" s="50"/>
     </row>
     <row r="390" spans="5:5">
-      <c r="E390" s="51"/>
+      <c r="E390" s="50"/>
     </row>
     <row r="391" spans="5:5">
-      <c r="E391" s="51"/>
+      <c r="E391" s="50"/>
     </row>
     <row r="392" spans="5:5">
-      <c r="E392" s="51"/>
+      <c r="E392" s="50"/>
     </row>
     <row r="393" spans="5:5">
-      <c r="E393" s="51"/>
+      <c r="E393" s="50"/>
     </row>
     <row r="394" spans="5:5">
-      <c r="E394" s="51"/>
+      <c r="E394" s="50"/>
     </row>
     <row r="395" spans="5:5">
-      <c r="E395" s="51"/>
+      <c r="E395" s="50"/>
     </row>
     <row r="396" spans="5:5">
-      <c r="E396" s="51"/>
+      <c r="E396" s="50"/>
     </row>
     <row r="397" spans="5:5">
-      <c r="E397" s="51"/>
+      <c r="E397" s="50"/>
     </row>
     <row r="398" spans="5:5">
-      <c r="E398" s="51"/>
+      <c r="E398" s="50"/>
     </row>
     <row r="399" spans="5:5">
-      <c r="E399" s="51"/>
+      <c r="E399" s="50"/>
     </row>
     <row r="400" spans="5:5">
-      <c r="E400" s="51"/>
+      <c r="E400" s="50"/>
     </row>
     <row r="401" spans="5:5">
-      <c r="E401" s="51"/>
+      <c r="E401" s="50"/>
     </row>
     <row r="402" spans="5:5">
-      <c r="E402" s="51"/>
+      <c r="E402" s="50"/>
     </row>
     <row r="403" spans="5:5">
-      <c r="E403" s="51"/>
+      <c r="E403" s="50"/>
     </row>
     <row r="404" spans="5:5">
-      <c r="E404" s="51"/>
+      <c r="E404" s="50"/>
     </row>
     <row r="405" spans="5:5">
-      <c r="E405" s="51"/>
+      <c r="E405" s="50"/>
     </row>
     <row r="406" spans="5:5">
-      <c r="E406" s="51"/>
+      <c r="E406" s="50"/>
     </row>
     <row r="407" spans="5:5">
-      <c r="E407" s="51"/>
+      <c r="E407" s="50"/>
     </row>
     <row r="408" spans="5:5">
-      <c r="E408" s="51"/>
+      <c r="E408" s="50"/>
     </row>
     <row r="409" spans="5:5">
-      <c r="E409" s="51"/>
+      <c r="E409" s="50"/>
     </row>
     <row r="410" spans="5:5">
-      <c r="E410" s="51"/>
+      <c r="E410" s="50"/>
     </row>
     <row r="411" spans="5:5">
-      <c r="E411" s="51"/>
+      <c r="E411" s="50"/>
     </row>
     <row r="412" spans="5:5">
-      <c r="E412" s="51"/>
+      <c r="E412" s="50"/>
     </row>
     <row r="413" spans="5:5">
-      <c r="E413" s="51"/>
+      <c r="E413" s="50"/>
     </row>
     <row r="414" spans="5:5">
-      <c r="E414" s="51"/>
+      <c r="E414" s="50"/>
     </row>
     <row r="415" spans="5:5">
-      <c r="E415" s="51"/>
+      <c r="E415" s="50"/>
     </row>
     <row r="416" spans="5:5">
-      <c r="E416" s="51"/>
+      <c r="E416" s="50"/>
     </row>
     <row r="417" spans="5:5">
-      <c r="E417" s="51"/>
+      <c r="E417" s="50"/>
     </row>
     <row r="418" spans="5:5">
-      <c r="E418" s="51"/>
+      <c r="E418" s="50"/>
     </row>
     <row r="419" spans="5:5">
-      <c r="E419" s="51"/>
+      <c r="E419" s="50"/>
     </row>
     <row r="420" spans="5:5">
-      <c r="E420" s="51"/>
+      <c r="E420" s="50"/>
     </row>
     <row r="421" spans="5:5">
-      <c r="E421" s="51"/>
+      <c r="E421" s="50"/>
     </row>
     <row r="422" spans="5:5">
-      <c r="E422" s="51"/>
+      <c r="E422" s="50"/>
     </row>
     <row r="423" spans="5:5">
-      <c r="E423" s="51"/>
+      <c r="E423" s="50"/>
     </row>
     <row r="424" spans="5:5">
-      <c r="E424" s="51"/>
+      <c r="E424" s="50"/>
     </row>
     <row r="425" spans="5:5">
-      <c r="E425" s="51"/>
+      <c r="E425" s="50"/>
     </row>
     <row r="426" spans="5:5">
-      <c r="E426" s="51"/>
+      <c r="E426" s="50"/>
     </row>
     <row r="427" spans="5:5">
-      <c r="E427" s="51"/>
+      <c r="E427" s="50"/>
     </row>
     <row r="428" spans="5:5">
-      <c r="E428" s="51"/>
+      <c r="E428" s="50"/>
     </row>
     <row r="429" spans="5:5">
-      <c r="E429" s="51"/>
+      <c r="E429" s="50"/>
     </row>
     <row r="430" spans="5:5">
-      <c r="E430" s="51"/>
+      <c r="E430" s="50"/>
     </row>
     <row r="431" spans="5:5">
-      <c r="E431" s="51"/>
+      <c r="E431" s="50"/>
     </row>
     <row r="432" spans="5:5">
-      <c r="E432" s="51"/>
+      <c r="E432" s="50"/>
     </row>
     <row r="433" spans="5:5">
-      <c r="E433" s="51"/>
+      <c r="E433" s="50"/>
     </row>
     <row r="434" spans="5:5">
-      <c r="E434" s="51"/>
+      <c r="E434" s="50"/>
     </row>
     <row r="435" spans="5:5">
-      <c r="E435" s="51"/>
+      <c r="E435" s="50"/>
     </row>
     <row r="436" spans="5:5">
-      <c r="E436" s="51"/>
+      <c r="E436" s="50"/>
     </row>
     <row r="437" spans="5:5">
-      <c r="E437" s="51"/>
+      <c r="E437" s="50"/>
     </row>
     <row r="438" spans="5:5">
-      <c r="E438" s="51"/>
+      <c r="E438" s="50"/>
     </row>
     <row r="439" spans="5:5">
-      <c r="E439" s="51"/>
+      <c r="E439" s="50"/>
     </row>
     <row r="440" spans="5:5">
-      <c r="E440" s="51"/>
+      <c r="E440" s="50"/>
     </row>
     <row r="441" spans="5:5">
-      <c r="E441" s="51"/>
+      <c r="E441" s="50"/>
     </row>
     <row r="442" spans="5:5">
-      <c r="E442" s="51"/>
+      <c r="E442" s="50"/>
     </row>
     <row r="443" spans="5:5">
-      <c r="E443" s="51"/>
+      <c r="E443" s="50"/>
     </row>
     <row r="444" spans="5:5">
-      <c r="E444" s="51"/>
+      <c r="E444" s="50"/>
     </row>
     <row r="445" spans="5:5">
-      <c r="E445" s="51"/>
+      <c r="E445" s="50"/>
     </row>
     <row r="446" spans="5:5">
-      <c r="E446" s="51"/>
+      <c r="E446" s="50"/>
     </row>
     <row r="447" spans="5:5">
-      <c r="E447" s="51"/>
+      <c r="E447" s="50"/>
     </row>
     <row r="448" spans="5:5">
-      <c r="E448" s="51"/>
+      <c r="E448" s="50"/>
     </row>
     <row r="449" spans="5:5">
-      <c r="E449" s="51"/>
+      <c r="E449" s="50"/>
     </row>
     <row r="450" spans="5:5">
-      <c r="E450" s="51"/>
+      <c r="E450" s="50"/>
     </row>
     <row r="451" spans="5:5">
-      <c r="E451" s="51"/>
+      <c r="E451" s="50"/>
     </row>
     <row r="452" spans="5:5">
-      <c r="E452" s="51"/>
+      <c r="E452" s="50"/>
     </row>
     <row r="453" spans="5:5">
-      <c r="E453" s="51"/>
+      <c r="E453" s="50"/>
     </row>
     <row r="454" spans="5:5">
-      <c r="E454" s="51"/>
+      <c r="E454" s="50"/>
     </row>
     <row r="455" spans="5:5">
-      <c r="E455" s="51"/>
+      <c r="E455" s="50"/>
     </row>
     <row r="456" spans="5:5">
-      <c r="E456" s="51"/>
+      <c r="E456" s="50"/>
     </row>
     <row r="457" spans="5:5">
-      <c r="E457" s="51"/>
+      <c r="E457" s="50"/>
     </row>
     <row r="458" spans="5:5">
-      <c r="E458" s="51"/>
+      <c r="E458" s="50"/>
     </row>
     <row r="459" spans="5:5">
-      <c r="E459" s="51"/>
+      <c r="E459" s="50"/>
     </row>
     <row r="460" spans="5:5">
-      <c r="E460" s="51"/>
+      <c r="E460" s="50"/>
     </row>
     <row r="461" spans="5:5">
-      <c r="E461" s="51"/>
+      <c r="E461" s="50"/>
     </row>
     <row r="462" spans="5:5">
-      <c r="E462" s="51"/>
+      <c r="E462" s="50"/>
     </row>
     <row r="463" spans="5:5">
-      <c r="E463" s="51"/>
+      <c r="E463" s="50"/>
     </row>
     <row r="464" spans="5:5">
-      <c r="E464" s="51"/>
+      <c r="E464" s="50"/>
     </row>
     <row r="465" spans="5:5">
-      <c r="E465" s="51"/>
+      <c r="E465" s="50"/>
     </row>
     <row r="466" spans="5:5">
-      <c r="E466" s="51"/>
+      <c r="E466" s="50"/>
     </row>
     <row r="467" spans="5:5">
-      <c r="E467" s="51"/>
+      <c r="E467" s="50"/>
     </row>
     <row r="468" spans="5:5">
-      <c r="E468" s="51"/>
+      <c r="E468" s="50"/>
     </row>
     <row r="469" spans="5:5">
-      <c r="E469" s="51"/>
+      <c r="E469" s="50"/>
     </row>
     <row r="470" spans="5:5">
-      <c r="E470" s="51"/>
+      <c r="E470" s="50"/>
     </row>
     <row r="471" spans="5:5">
-      <c r="E471" s="51"/>
+      <c r="E471" s="50"/>
     </row>
     <row r="472" spans="5:5">
-      <c r="E472" s="51"/>
+      <c r="E472" s="50"/>
     </row>
     <row r="473" spans="5:5">
-      <c r="E473" s="51"/>
+      <c r="E473" s="50"/>
     </row>
     <row r="474" spans="5:5">
-      <c r="E474" s="51"/>
+      <c r="E474" s="50"/>
     </row>
     <row r="475" spans="5:5">
-      <c r="E475" s="51"/>
+      <c r="E475" s="50"/>
     </row>
     <row r="476" spans="5:5">
-      <c r="E476" s="51"/>
+      <c r="E476" s="50"/>
     </row>
     <row r="477" spans="5:5">
-      <c r="E477" s="51"/>
+      <c r="E477" s="50"/>
     </row>
     <row r="478" spans="5:5">
-      <c r="E478" s="51"/>
+      <c r="E478" s="50"/>
     </row>
     <row r="479" spans="5:5">
-      <c r="E479" s="51"/>
+      <c r="E479" s="50"/>
     </row>
     <row r="480" spans="5:5">
-      <c r="E480" s="51"/>
+      <c r="E480" s="50"/>
     </row>
     <row r="481" spans="5:5">
-      <c r="E481" s="51"/>
+      <c r="E481" s="50"/>
     </row>
     <row r="482" spans="5:5">
-      <c r="E482" s="51"/>
+      <c r="E482" s="50"/>
     </row>
     <row r="483" spans="5:5">
-      <c r="E483" s="51"/>
+      <c r="E483" s="50"/>
     </row>
     <row r="484" spans="5:5">
-      <c r="E484" s="51"/>
+      <c r="E484" s="50"/>
     </row>
     <row r="485" spans="5:5">
-      <c r="E485" s="51"/>
+      <c r="E485" s="50"/>
     </row>
     <row r="486" spans="5:5">
-      <c r="E486" s="51"/>
+      <c r="E486" s="50"/>
     </row>
     <row r="487" spans="5:5">
-      <c r="E487" s="51"/>
+      <c r="E487" s="50"/>
     </row>
     <row r="488" spans="5:5">
-      <c r="E488" s="51"/>
+      <c r="E488" s="50"/>
     </row>
     <row r="489" spans="5:5">
-      <c r="E489" s="51"/>
+      <c r="E489" s="50"/>
     </row>
     <row r="490" spans="5:5">
-      <c r="E490" s="51"/>
+      <c r="E490" s="50"/>
     </row>
     <row r="491" spans="5:5">
-      <c r="E491" s="51"/>
+      <c r="E491" s="50"/>
     </row>
     <row r="492" spans="5:5">
-      <c r="E492" s="51"/>
+      <c r="E492" s="50"/>
     </row>
     <row r="493" spans="5:5">
-      <c r="E493" s="51"/>
+      <c r="E493" s="50"/>
     </row>
     <row r="494" spans="5:5">
-      <c r="E494" s="51"/>
+      <c r="E494" s="50"/>
     </row>
     <row r="495" spans="5:5">
-      <c r="E495" s="51"/>
+      <c r="E495" s="50"/>
     </row>
     <row r="496" spans="5:5">
-      <c r="E496" s="51"/>
+      <c r="E496" s="50"/>
     </row>
     <row r="497" spans="5:5">
-      <c r="E497" s="51"/>
+      <c r="E497" s="50"/>
     </row>
     <row r="498" spans="5:5">
-      <c r="E498" s="51"/>
+      <c r="E498" s="50"/>
     </row>
     <row r="499" spans="5:5">
-      <c r="E499" s="51"/>
+      <c r="E499" s="50"/>
     </row>
     <row r="500" spans="5:5">
-      <c r="E500" s="51"/>
+      <c r="E500" s="50"/>
     </row>
     <row r="501" spans="5:5">
-      <c r="E501" s="51"/>
+      <c r="E501" s="50"/>
     </row>
     <row r="502" spans="5:5">
-      <c r="E502" s="51"/>
+      <c r="E502" s="50"/>
     </row>
     <row r="503" spans="5:5">
-      <c r="E503" s="51"/>
+      <c r="E503" s="50"/>
     </row>
     <row r="504" spans="5:5">
-      <c r="E504" s="51"/>
+      <c r="E504" s="50"/>
     </row>
     <row r="505" spans="5:5">
-      <c r="E505" s="51"/>
+      <c r="E505" s="50"/>
     </row>
     <row r="506" spans="5:5">
-      <c r="E506" s="51"/>
+      <c r="E506" s="50"/>
     </row>
     <row r="507" spans="5:5">
-      <c r="E507" s="51"/>
+      <c r="E507" s="50"/>
     </row>
     <row r="508" spans="5:5">
-      <c r="E508" s="51"/>
+      <c r="E508" s="50"/>
     </row>
     <row r="509" spans="5:5">
-      <c r="E509" s="51"/>
+      <c r="E509" s="50"/>
     </row>
     <row r="510" spans="5:5">
-      <c r="E510" s="51"/>
+      <c r="E510" s="50"/>
     </row>
     <row r="511" spans="5:5">
-      <c r="E511" s="51"/>
+      <c r="E511" s="50"/>
     </row>
     <row r="512" spans="5:5">
-      <c r="E512" s="51"/>
+      <c r="E512" s="50"/>
     </row>
     <row r="513" spans="5:5">
-      <c r="E513" s="51"/>
+      <c r="E513" s="50"/>
     </row>
     <row r="514" spans="5:5">
-      <c r="E514" s="51"/>
+      <c r="E514" s="50"/>
     </row>
     <row r="515" spans="5:5">
-      <c r="E515" s="51"/>
+      <c r="E515" s="50"/>
     </row>
     <row r="516" spans="5:5">
-      <c r="E516" s="51"/>
+      <c r="E516" s="50"/>
     </row>
     <row r="517" spans="5:5">
-      <c r="E517" s="51"/>
+      <c r="E517" s="50"/>
     </row>
     <row r="518" spans="5:5">
-      <c r="E518" s="51"/>
+      <c r="E518" s="50"/>
     </row>
     <row r="519" spans="5:5">
-      <c r="E519" s="51"/>
+      <c r="E519" s="50"/>
     </row>
     <row r="520" spans="5:5">
-      <c r="E520" s="51"/>
+      <c r="E520" s="50"/>
     </row>
     <row r="521" spans="5:5">
-      <c r="E521" s="51"/>
+      <c r="E521" s="50"/>
     </row>
     <row r="522" spans="5:5">
-      <c r="E522" s="51"/>
+      <c r="E522" s="50"/>
     </row>
     <row r="523" spans="5:5">
-      <c r="E523" s="51"/>
+      <c r="E523" s="50"/>
     </row>
     <row r="524" spans="5:5">
-      <c r="E524" s="51"/>
+      <c r="E524" s="50"/>
     </row>
     <row r="525" spans="5:5">
-      <c r="E525" s="51"/>
+      <c r="E525" s="50"/>
     </row>
     <row r="526" spans="5:5">
-      <c r="E526" s="51"/>
+      <c r="E526" s="50"/>
     </row>
     <row r="527" spans="5:5">
-      <c r="E527" s="51"/>
+      <c r="E527" s="50"/>
     </row>
     <row r="528" spans="5:5">
-      <c r="E528" s="51"/>
+      <c r="E528" s="50"/>
     </row>
     <row r="529" spans="5:5">
-      <c r="E529" s="51"/>
+      <c r="E529" s="50"/>
     </row>
     <row r="530" spans="5:5">
-      <c r="E530" s="51"/>
+      <c r="E530" s="50"/>
     </row>
     <row r="531" spans="5:5">
-      <c r="E531" s="51"/>
+      <c r="E531" s="50"/>
     </row>
     <row r="532" spans="5:5">
-      <c r="E532" s="51"/>
+      <c r="E532" s="50"/>
     </row>
     <row r="533" spans="5:5">
-      <c r="E533" s="51"/>
+      <c r="E533" s="50"/>
     </row>
     <row r="534" spans="5:5">
-      <c r="E534" s="51"/>
+      <c r="E534" s="50"/>
     </row>
     <row r="535" spans="5:5">
-      <c r="E535" s="51"/>
+      <c r="E535" s="50"/>
     </row>
     <row r="536" spans="5:5">
-      <c r="E536" s="51"/>
+      <c r="E536" s="50"/>
     </row>
     <row r="537" spans="5:5">
-      <c r="E537" s="51"/>
+      <c r="E537" s="50"/>
     </row>
     <row r="538" spans="5:5">
-      <c r="E538" s="51"/>
+      <c r="E538" s="50"/>
     </row>
     <row r="539" spans="5:5">
-      <c r="E539" s="51"/>
+      <c r="E539" s="50"/>
     </row>
     <row r="540" spans="5:5">
-      <c r="E540" s="51"/>
+      <c r="E540" s="50"/>
     </row>
     <row r="541" spans="5:5">
-      <c r="E541" s="51"/>
+      <c r="E541" s="50"/>
     </row>
     <row r="542" spans="5:5">
-      <c r="E542" s="51"/>
+      <c r="E542" s="50"/>
     </row>
     <row r="543" spans="5:5">
-      <c r="E543" s="51"/>
+      <c r="E543" s="50"/>
     </row>
     <row r="544" spans="5:5">
-      <c r="E544" s="51"/>
+      <c r="E544" s="50"/>
     </row>
     <row r="545" spans="5:5">
-      <c r="E545" s="51"/>
+      <c r="E545" s="50"/>
     </row>
     <row r="546" spans="5:5">
-      <c r="E546" s="51"/>
+      <c r="E546" s="50"/>
     </row>
     <row r="547" spans="5:5">
-      <c r="E547" s="51"/>
+      <c r="E547" s="50"/>
     </row>
     <row r="548" spans="5:5">
-      <c r="E548" s="51"/>
+      <c r="E548" s="50"/>
     </row>
     <row r="549" spans="5:5">
-      <c r="E549" s="51"/>
+      <c r="E549" s="50"/>
     </row>
     <row r="550" spans="5:5">
-      <c r="E550" s="51"/>
+      <c r="E550" s="50"/>
     </row>
     <row r="551" spans="5:5">
-      <c r="E551" s="51"/>
+      <c r="E551" s="50"/>
     </row>
     <row r="552" spans="5:5">
-      <c r="E552" s="51"/>
+      <c r="E552" s="50"/>
     </row>
     <row r="553" spans="5:5">
-      <c r="E553" s="51"/>
+      <c r="E553" s="50"/>
     </row>
     <row r="554" spans="5:5">
-      <c r="E554" s="51"/>
+      <c r="E554" s="50"/>
     </row>
     <row r="555" spans="5:5">
-      <c r="E555" s="51"/>
+      <c r="E555" s="50"/>
     </row>
     <row r="556" spans="5:5">
-      <c r="E556" s="51"/>
+      <c r="E556" s="50"/>
     </row>
     <row r="557" spans="5:5">
-      <c r="E557" s="51"/>
+      <c r="E557" s="50"/>
     </row>
     <row r="558" spans="5:5">
-      <c r="E558" s="51"/>
+      <c r="E558" s="50"/>
     </row>
     <row r="559" spans="5:5">
-      <c r="E559" s="51"/>
+      <c r="E559" s="50"/>
     </row>
     <row r="560" spans="5:5">
-      <c r="E560" s="51"/>
+      <c r="E560" s="50"/>
     </row>
     <row r="561" spans="5:5">
-      <c r="E561" s="51"/>
+      <c r="E561" s="50"/>
     </row>
     <row r="562" spans="5:5">
-      <c r="E562" s="51"/>
+      <c r="E562" s="50"/>
     </row>
     <row r="563" spans="5:5">
-      <c r="E563" s="51"/>
+      <c r="E563" s="50"/>
     </row>
     <row r="564" spans="5:5">
-      <c r="E564" s="51"/>
+      <c r="E564" s="50"/>
     </row>
     <row r="565" spans="5:5">
-      <c r="E565" s="51"/>
+      <c r="E565" s="50"/>
     </row>
     <row r="566" spans="5:5">
-      <c r="E566" s="51"/>
+      <c r="E566" s="50"/>
     </row>
     <row r="567" spans="5:5">
-      <c r="E567" s="51"/>
+      <c r="E567" s="50"/>
     </row>
     <row r="568" spans="5:5">
-      <c r="E568" s="51"/>
+      <c r="E568" s="50"/>
     </row>
     <row r="569" spans="5:5">
-      <c r="E569" s="51"/>
+      <c r="E569" s="50"/>
     </row>
     <row r="570" spans="5:5">
-      <c r="E570" s="51"/>
+      <c r="E570" s="50"/>
     </row>
     <row r="571" spans="5:5">
-      <c r="E571" s="51"/>
+      <c r="E571" s="50"/>
     </row>
     <row r="572" spans="5:5">
-      <c r="E572" s="51"/>
+      <c r="E572" s="50"/>
     </row>
     <row r="573" spans="5:5">
-      <c r="E573" s="51"/>
+      <c r="E573" s="50"/>
     </row>
     <row r="574" spans="5:5">
-      <c r="E574" s="51"/>
+      <c r="E574" s="50"/>
     </row>
     <row r="575" spans="5:5">
-      <c r="E575" s="51"/>
+      <c r="E575" s="50"/>
     </row>
     <row r="576" spans="5:5">
-      <c r="E576" s="51"/>
+      <c r="E576" s="50"/>
     </row>
     <row r="577" spans="5:5">
-      <c r="E577" s="51"/>
+      <c r="E577" s="50"/>
     </row>
     <row r="578" spans="5:5">
-      <c r="E578" s="51"/>
+      <c r="E578" s="50"/>
     </row>
     <row r="579" spans="5:5">
-      <c r="E579" s="51"/>
+      <c r="E579" s="50"/>
     </row>
     <row r="580" spans="5:5">
-      <c r="E580" s="51"/>
+      <c r="E580" s="50"/>
     </row>
     <row r="581" spans="5:5">
-      <c r="E581" s="51"/>
+      <c r="E581" s="50"/>
     </row>
     <row r="582" spans="5:5">
-      <c r="E582" s="51"/>
+      <c r="E582" s="50"/>
     </row>
     <row r="583" spans="5:5">
-      <c r="E583" s="51"/>
+      <c r="E583" s="50"/>
     </row>
     <row r="584" spans="5:5">
-      <c r="E584" s="51"/>
+      <c r="E584" s="50"/>
     </row>
     <row r="585" spans="5:5">
-      <c r="E585" s="51"/>
+      <c r="E585" s="50"/>
     </row>
     <row r="586" spans="5:5">
-      <c r="E586" s="51"/>
+      <c r="E586" s="50"/>
     </row>
     <row r="587" spans="5:5">
-      <c r="E587" s="51"/>
+      <c r="E587" s="50"/>
     </row>
     <row r="588" spans="5:5">
-      <c r="E588" s="51"/>
+      <c r="E588" s="50"/>
     </row>
     <row r="589" spans="5:5">
-      <c r="E589" s="51"/>
+      <c r="E589" s="50"/>
     </row>
     <row r="590" spans="5:5">
-      <c r="E590" s="51"/>
+      <c r="E590" s="50"/>
     </row>
     <row r="591" spans="5:5">
-      <c r="E591" s="51"/>
+      <c r="E591" s="50"/>
     </row>
     <row r="592" spans="5:5">
-      <c r="E592" s="51"/>
+      <c r="E592" s="50"/>
     </row>
     <row r="593" spans="5:5">
-      <c r="E593" s="51"/>
+      <c r="E593" s="50"/>
     </row>
     <row r="594" spans="5:5">
-      <c r="E594" s="51"/>
+      <c r="E594" s="50"/>
     </row>
     <row r="595" spans="5:5">
-      <c r="E595" s="51"/>
+      <c r="E595" s="50"/>
     </row>
     <row r="596" spans="5:5">
-      <c r="E596" s="51"/>
+      <c r="E596" s="50"/>
     </row>
     <row r="597" spans="5:5">
-      <c r="E597" s="51"/>
+      <c r="E597" s="50"/>
     </row>
     <row r="598" spans="5:5">
-      <c r="E598" s="51"/>
+      <c r="E598" s="50"/>
     </row>
     <row r="599" spans="5:5">
-      <c r="E599" s="51"/>
+      <c r="E599" s="50"/>
     </row>
     <row r="600" spans="5:5">
-      <c r="E600" s="51"/>
+      <c r="E600" s="50"/>
     </row>
     <row r="601" spans="5:5">
-      <c r="E601" s="51"/>
+      <c r="E601" s="50"/>
     </row>
     <row r="602" spans="5:5">
-      <c r="E602" s="51"/>
+      <c r="E602" s="50"/>
     </row>
     <row r="603" spans="5:5">
-      <c r="E603" s="51"/>
+      <c r="E603" s="50"/>
     </row>
     <row r="604" spans="5:5">
-      <c r="E604" s="51"/>
+      <c r="E604" s="50"/>
     </row>
     <row r="605" spans="5:5">
-      <c r="E605" s="51"/>
+      <c r="E605" s="50"/>
     </row>
     <row r="606" spans="5:5">
-      <c r="E606" s="51"/>
+      <c r="E606" s="50"/>
     </row>
     <row r="607" spans="5:5">
-      <c r="E607" s="51"/>
+      <c r="E607" s="50"/>
     </row>
     <row r="608" spans="5:5">
-      <c r="E608" s="51"/>
+      <c r="E608" s="50"/>
     </row>
     <row r="609" spans="5:5">
-      <c r="E609" s="51"/>
+      <c r="E609" s="50"/>
     </row>
     <row r="610" spans="5:5">
-      <c r="E610" s="51"/>
+      <c r="E610" s="50"/>
     </row>
     <row r="611" spans="5:5">
-      <c r="E611" s="51"/>
+      <c r="E611" s="50"/>
     </row>
     <row r="612" spans="5:5">
-      <c r="E612" s="51"/>
+      <c r="E612" s="50"/>
     </row>
     <row r="613" spans="5:5">
-      <c r="E613" s="51"/>
+      <c r="E613" s="50"/>
     </row>
     <row r="614" spans="5:5">
-      <c r="E614" s="51"/>
+      <c r="E614" s="50"/>
     </row>
     <row r="615" spans="5:5">
-      <c r="E615" s="51"/>
+      <c r="E615" s="50"/>
     </row>
     <row r="616" spans="5:5">
-      <c r="E616" s="51"/>
+      <c r="E616" s="50"/>
     </row>
     <row r="617" spans="5:5">
-      <c r="E617" s="51"/>
+      <c r="E617" s="50"/>
     </row>
     <row r="618" spans="5:5">
-      <c r="E618" s="51"/>
+      <c r="E618" s="50"/>
     </row>
     <row r="619" spans="5:5">
-      <c r="E619" s="51"/>
+      <c r="E619" s="50"/>
     </row>
     <row r="620" spans="5:5">
-      <c r="E620" s="51"/>
+      <c r="E620" s="50"/>
     </row>
     <row r="621" spans="5:5">
-      <c r="E621" s="51"/>
+      <c r="E621" s="50"/>
     </row>
     <row r="622" spans="5:5">
-      <c r="E622" s="51"/>
+      <c r="E622" s="50"/>
     </row>
     <row r="623" spans="5:5">
-      <c r="E623" s="51"/>
+      <c r="E623" s="50"/>
     </row>
     <row r="624" spans="5:5">
-      <c r="E624" s="51"/>
+      <c r="E624" s="50"/>
     </row>
     <row r="625" spans="5:5">
-      <c r="E625" s="51"/>
+      <c r="E625" s="50"/>
     </row>
     <row r="626" spans="5:5">
-      <c r="E626" s="51"/>
+      <c r="E626" s="50"/>
     </row>
     <row r="627" spans="5:5">
-      <c r="E627" s="51"/>
+      <c r="E627" s="50"/>
     </row>
     <row r="628" spans="5:5">
-      <c r="E628" s="51"/>
+      <c r="E628" s="50"/>
     </row>
     <row r="629" spans="5:5">
-      <c r="E629" s="51"/>
+      <c r="E629" s="50"/>
     </row>
     <row r="630" spans="5:5">
-      <c r="E630" s="51"/>
+      <c r="E630" s="50"/>
     </row>
     <row r="631" spans="5:5">
-      <c r="E631" s="51"/>
+      <c r="E631" s="50"/>
     </row>
     <row r="632" spans="5:5">
-      <c r="E632" s="51"/>
+      <c r="E632" s="50"/>
     </row>
     <row r="633" spans="5:5">
-      <c r="E633" s="51"/>
+      <c r="E633" s="50"/>
     </row>
     <row r="634" spans="5:5">
-      <c r="E634" s="51"/>
+      <c r="E634" s="50"/>
     </row>
     <row r="635" spans="5:5">
-      <c r="E635" s="51"/>
+      <c r="E635" s="50"/>
     </row>
     <row r="636" spans="5:5">
-      <c r="E636" s="51"/>
+      <c r="E636" s="50"/>
     </row>
     <row r="637" spans="5:5">
-      <c r="E637" s="51"/>
+      <c r="E637" s="50"/>
     </row>
     <row r="638" spans="5:5">
-      <c r="E638" s="51"/>
+      <c r="E638" s="50"/>
     </row>
     <row r="639" spans="5:5">
-      <c r="E639" s="51"/>
+      <c r="E639" s="50"/>
     </row>
     <row r="640" spans="5:5">
-      <c r="E640" s="51"/>
+      <c r="E640" s="50"/>
     </row>
     <row r="641" spans="5:5">
-      <c r="E641" s="51"/>
+      <c r="E641" s="50"/>
     </row>
     <row r="642" spans="5:5">
-      <c r="E642" s="51"/>
+      <c r="E642" s="50"/>
     </row>
     <row r="643" spans="5:5">
-      <c r="E643" s="51"/>
+      <c r="E643" s="50"/>
     </row>
     <row r="644" spans="5:5">
-      <c r="E644" s="51"/>
+      <c r="E644" s="50"/>
     </row>
     <row r="645" spans="5:5">
-      <c r="E645" s="51"/>
+      <c r="E645" s="50"/>
     </row>
     <row r="646" spans="5:5">
-      <c r="E646" s="51"/>
+      <c r="E646" s="50"/>
     </row>
     <row r="647" spans="5:5">
-      <c r="E647" s="51"/>
+      <c r="E647" s="50"/>
     </row>
     <row r="648" spans="5:5">
-      <c r="E648" s="51"/>
+      <c r="E648" s="50"/>
     </row>
     <row r="649" spans="5:5">
-      <c r="E649" s="51"/>
+      <c r="E649" s="50"/>
     </row>
     <row r="650" spans="5:5">
-      <c r="E650" s="51"/>
+      <c r="E650" s="50"/>
     </row>
     <row r="651" spans="5:5">
-      <c r="E651" s="51"/>
+      <c r="E651" s="50"/>
     </row>
     <row r="652" spans="5:5">
-      <c r="E652" s="51"/>
+      <c r="E652" s="50"/>
     </row>
     <row r="653" spans="5:5">
-      <c r="E653" s="51"/>
+      <c r="E653" s="50"/>
     </row>
     <row r="654" spans="5:5">
-      <c r="E654" s="51"/>
+      <c r="E654" s="50"/>
     </row>
     <row r="655" spans="5:5">
-      <c r="E655" s="51"/>
+      <c r="E655" s="50"/>
     </row>
     <row r="656" spans="5:5">
-      <c r="E656" s="51"/>
+      <c r="E656" s="50"/>
     </row>
     <row r="657" spans="5:5">
-      <c r="E657" s="51"/>
+      <c r="E657" s="50"/>
     </row>
     <row r="658" spans="5:5">
-      <c r="E658" s="51"/>
+      <c r="E658" s="50"/>
     </row>
     <row r="659" spans="5:5">
-      <c r="E659" s="51"/>
+      <c r="E659" s="50"/>
     </row>
     <row r="660" spans="5:5">
-      <c r="E660" s="51"/>
+      <c r="E660" s="50"/>
     </row>
     <row r="661" spans="5:5">
-      <c r="E661" s="51"/>
+      <c r="E661" s="50"/>
     </row>
     <row r="662" spans="5:5">
-      <c r="E662" s="51"/>
+      <c r="E662" s="50"/>
     </row>
     <row r="663" spans="5:5">
-      <c r="E663" s="51"/>
+      <c r="E663" s="50"/>
     </row>
     <row r="664" spans="5:5">
-      <c r="E664" s="51"/>
+      <c r="E664" s="50"/>
     </row>
     <row r="665" spans="5:5">
-      <c r="E665" s="51"/>
+      <c r="E665" s="50"/>
     </row>
     <row r="666" spans="5:5">
-      <c r="E666" s="51"/>
+      <c r="E666" s="50"/>
     </row>
     <row r="667" spans="5:5">
-      <c r="E667" s="51"/>
+      <c r="E667" s="50"/>
     </row>
     <row r="668" spans="5:5">
-      <c r="E668" s="51"/>
+      <c r="E668" s="50"/>
     </row>
     <row r="669" spans="5:5">
-      <c r="E669" s="51"/>
+      <c r="E669" s="50"/>
     </row>
     <row r="670" spans="5:5">
-      <c r="E670" s="51"/>
+      <c r="E670" s="50"/>
     </row>
     <row r="671" spans="5:5">
-      <c r="E671" s="51"/>
+      <c r="E671" s="50"/>
     </row>
     <row r="672" spans="5:5">
-      <c r="E672" s="51"/>
+      <c r="E672" s="50"/>
     </row>
     <row r="673" spans="5:5">
-      <c r="E673" s="51"/>
+      <c r="E673" s="50"/>
     </row>
     <row r="674" spans="5:5">
-      <c r="E674" s="51"/>
+      <c r="E674" s="50"/>
     </row>
     <row r="675" spans="5:5">
-      <c r="E675" s="51"/>
+      <c r="E675" s="50"/>
     </row>
     <row r="676" spans="5:5">
-      <c r="E676" s="51"/>
+      <c r="E676" s="50"/>
     </row>
     <row r="677" spans="5:5">
-      <c r="E677" s="51"/>
+      <c r="E677" s="50"/>
     </row>
     <row r="678" spans="5:5">
-      <c r="E678" s="51"/>
+      <c r="E678" s="50"/>
     </row>
     <row r="679" spans="5:5">
-      <c r="E679" s="51"/>
+      <c r="E679" s="50"/>
     </row>
     <row r="680" spans="5:5">
-      <c r="E680" s="51"/>
+      <c r="E680" s="50"/>
     </row>
     <row r="681" spans="5:5">
-      <c r="E681" s="51"/>
+      <c r="E681" s="50"/>
     </row>
     <row r="682" spans="5:5">
-      <c r="E682" s="51"/>
+      <c r="E682" s="50"/>
     </row>
     <row r="683" spans="5:5">
-      <c r="E683" s="51"/>
+      <c r="E683" s="50"/>
     </row>
     <row r="684" spans="5:5">
-      <c r="E684" s="51"/>
+      <c r="E684" s="50"/>
     </row>
     <row r="685" spans="5:5">
-      <c r="E685" s="51"/>
+      <c r="E685" s="50"/>
     </row>
     <row r="686" spans="5:5">
-      <c r="E686" s="51"/>
+      <c r="E686" s="50"/>
     </row>
     <row r="687" spans="5:5">
-      <c r="E687" s="51"/>
+      <c r="E687" s="50"/>
     </row>
     <row r="688" spans="5:5">
-      <c r="E688" s="51"/>
+      <c r="E688" s="50"/>
     </row>
     <row r="689" spans="5:5">
-      <c r="E689" s="51"/>
+      <c r="E689" s="50"/>
     </row>
     <row r="690" spans="5:5">
-      <c r="E690" s="51"/>
+      <c r="E690" s="50"/>
     </row>
     <row r="691" spans="5:5">
-      <c r="E691" s="51"/>
+      <c r="E691" s="50"/>
     </row>
     <row r="692" spans="5:5">
-      <c r="E692" s="51"/>
+      <c r="E692" s="50"/>
     </row>
     <row r="693" spans="5:5">
-      <c r="E693" s="51"/>
+      <c r="E693" s="50"/>
     </row>
     <row r="694" spans="5:5">
-      <c r="E694" s="51"/>
+      <c r="E694" s="50"/>
     </row>
     <row r="695" spans="5:5">
-      <c r="E695" s="51"/>
+      <c r="E695" s="50"/>
     </row>
     <row r="696" spans="5:5">
-      <c r="E696" s="51"/>
+      <c r="E696" s="50"/>
     </row>
     <row r="697" spans="5:5">
-      <c r="E697" s="51"/>
+      <c r="E697" s="50"/>
     </row>
     <row r="698" spans="5:5">
-      <c r="E698" s="51"/>
+      <c r="E698" s="50"/>
     </row>
     <row r="699" spans="5:5">
-      <c r="E699" s="51"/>
+      <c r="E699" s="50"/>
     </row>
     <row r="700" spans="5:5">
-      <c r="E700" s="51"/>
+      <c r="E700" s="50"/>
     </row>
     <row r="701" spans="5:5">
-      <c r="E701" s="51"/>
+      <c r="E701" s="50"/>
     </row>
     <row r="702" spans="5:5">
-      <c r="E702" s="51"/>
+      <c r="E702" s="50"/>
     </row>
     <row r="703" spans="5:5">
-      <c r="E703" s="51"/>
+      <c r="E703" s="50"/>
     </row>
     <row r="704" spans="5:5">
-      <c r="E704" s="51"/>
+      <c r="E704" s="50"/>
     </row>
     <row r="705" spans="5:5">
-      <c r="E705" s="51"/>
+      <c r="E705" s="50"/>
     </row>
     <row r="706" spans="5:5">
-      <c r="E706" s="51"/>
+      <c r="E706" s="50"/>
     </row>
     <row r="707" spans="5:5">
-      <c r="E707" s="51"/>
+      <c r="E707" s="50"/>
     </row>
     <row r="708" spans="5:5">
-      <c r="E708" s="51"/>
+      <c r="E708" s="50"/>
     </row>
     <row r="709" spans="5:5">
-      <c r="E709" s="51"/>
+      <c r="E709" s="50"/>
     </row>
     <row r="710" spans="5:5">
-      <c r="E710" s="51"/>
+      <c r="E710" s="50"/>
     </row>
     <row r="711" spans="5:5">
-      <c r="E711" s="51"/>
+      <c r="E711" s="50"/>
     </row>
     <row r="712" spans="5:5">
-      <c r="E712" s="51"/>
+      <c r="E712" s="50"/>
     </row>
     <row r="713" spans="5:5">
-      <c r="E713" s="51"/>
+      <c r="E713" s="50"/>
     </row>
     <row r="714" spans="5:5">
-      <c r="E714" s="51"/>
+      <c r="E714" s="50"/>
     </row>
     <row r="715" spans="5:5">
-      <c r="E715" s="51"/>
+      <c r="E715" s="50"/>
     </row>
     <row r="716" spans="5:5">
-      <c r="E716" s="51"/>
+      <c r="E716" s="50"/>
     </row>
     <row r="717" spans="5:5">
-      <c r="E717" s="51"/>
+      <c r="E717" s="50"/>
     </row>
     <row r="718" spans="5:5">
-      <c r="E718" s="51"/>
+      <c r="E718" s="50"/>
     </row>
     <row r="719" spans="5:5">
-      <c r="E719" s="51"/>
+      <c r="E719" s="50"/>
     </row>
     <row r="720" spans="5:5">
-      <c r="E720" s="51"/>
+      <c r="E720" s="50"/>
     </row>
     <row r="721" spans="5:5">
-      <c r="E721" s="51"/>
+      <c r="E721" s="50"/>
     </row>
     <row r="722" spans="5:5">
-      <c r="E722" s="51"/>
+      <c r="E722" s="50"/>
     </row>
     <row r="723" spans="5:5">
-      <c r="E723" s="51"/>
+      <c r="E723" s="50"/>
     </row>
     <row r="724" spans="5:5">
-      <c r="E724" s="51"/>
+      <c r="E724" s="50"/>
     </row>
     <row r="725" spans="5:5">
-      <c r="E725" s="51"/>
+      <c r="E725" s="50"/>
     </row>
     <row r="726" spans="5:5">
-      <c r="E726" s="51"/>
+      <c r="E726" s="50"/>
     </row>
     <row r="727" spans="5:5">
-      <c r="E727" s="51"/>
+      <c r="E727" s="50"/>
     </row>
     <row r="728" spans="5:5">
-      <c r="E728" s="51"/>
+      <c r="E728" s="50"/>
     </row>
     <row r="729" spans="5:5">
-      <c r="E729" s="51"/>
+      <c r="E729" s="50"/>
     </row>
     <row r="730" spans="5:5">
-      <c r="E730" s="51"/>
+      <c r="E730" s="50"/>
     </row>
     <row r="731" spans="5:5">
-      <c r="E731" s="51"/>
+      <c r="E731" s="50"/>
     </row>
     <row r="732" spans="5:5">
-      <c r="E732" s="51"/>
+      <c r="E732" s="50"/>
     </row>
     <row r="733" spans="5:5">
-      <c r="E733" s="51"/>
+      <c r="E733" s="50"/>
     </row>
     <row r="734" spans="5:5">
-      <c r="E734" s="51"/>
+      <c r="E734" s="50"/>
     </row>
     <row r="735" spans="5:5">
-      <c r="E735" s="51"/>
+      <c r="E735" s="50"/>
     </row>
     <row r="736" spans="5:5">
-      <c r="E736" s="51"/>
+      <c r="E736" s="50"/>
     </row>
     <row r="737" spans="5:5">
-      <c r="E737" s="51"/>
+      <c r="E737" s="50"/>
     </row>
     <row r="738" spans="5:5">
-      <c r="E738" s="51"/>
+      <c r="E738" s="50"/>
     </row>
     <row r="739" spans="5:5">
-      <c r="E739" s="51"/>
+      <c r="E739" s="50"/>
     </row>
     <row r="740" spans="5:5">
-      <c r="E740" s="51"/>
+      <c r="E740" s="50"/>
     </row>
     <row r="741" spans="5:5">
-      <c r="E741" s="51"/>
+      <c r="E741" s="50"/>
     </row>
     <row r="742" spans="5:5">
-      <c r="E742" s="51"/>
+      <c r="E742" s="50"/>
     </row>
     <row r="743" spans="5:5">
-      <c r="E743" s="51"/>
+      <c r="E743" s="50"/>
     </row>
     <row r="744" spans="5:5">
-      <c r="E744" s="51"/>
+      <c r="E744" s="50"/>
     </row>
     <row r="745" spans="5:5">
-      <c r="E745" s="51"/>
+      <c r="E745" s="50"/>
     </row>
     <row r="746" spans="5:5">
-      <c r="E746" s="51"/>
+      <c r="E746" s="50"/>
     </row>
     <row r="747" spans="5:5">
-      <c r="E747" s="51"/>
+      <c r="E747" s="50"/>
     </row>
     <row r="748" spans="5:5">
-      <c r="E748" s="51"/>
+      <c r="E748" s="50"/>
     </row>
     <row r="749" spans="5:5">
-      <c r="E749" s="51"/>
+      <c r="E749" s="50"/>
     </row>
     <row r="750" spans="5:5">
-      <c r="E750" s="51"/>
+      <c r="E750" s="50"/>
     </row>
     <row r="751" spans="5:5">
-      <c r="E751" s="51"/>
+      <c r="E751" s="50"/>
     </row>
     <row r="752" spans="5:5">
-      <c r="E752" s="51"/>
+      <c r="E752" s="50"/>
     </row>
     <row r="753" spans="5:5">
-      <c r="E753" s="51"/>
+      <c r="E753" s="50"/>
     </row>
     <row r="754" spans="5:5">
-      <c r="E754" s="51"/>
+      <c r="E754" s="50"/>
     </row>
     <row r="755" spans="5:5">
-      <c r="E755" s="51"/>
+      <c r="E755" s="50"/>
     </row>
     <row r="756" spans="5:5">
-      <c r="E756" s="51"/>
+      <c r="E756" s="50"/>
     </row>
     <row r="757" spans="5:5">
-      <c r="E757" s="51"/>
+      <c r="E757" s="50"/>
     </row>
     <row r="758" spans="5:5">
-      <c r="E758" s="51"/>
+      <c r="E758" s="50"/>
     </row>
     <row r="759" spans="5:5">
-      <c r="E759" s="51"/>
+      <c r="E759" s="50"/>
     </row>
     <row r="760" spans="5:5">
-      <c r="E760" s="51"/>
+      <c r="E760" s="50"/>
     </row>
     <row r="761" spans="5:5">
-      <c r="E761" s="51"/>
+      <c r="E761" s="50"/>
     </row>
     <row r="762" spans="5:5">
-      <c r="E762" s="51"/>
+      <c r="E762" s="50"/>
     </row>
     <row r="763" spans="5:5">
-      <c r="E763" s="51"/>
+      <c r="E763" s="50"/>
     </row>
     <row r="764" spans="5:5">
-      <c r="E764" s="51"/>
+      <c r="E764" s="50"/>
     </row>
     <row r="765" spans="5:5">
-      <c r="E765" s="51"/>
+      <c r="E765" s="50"/>
     </row>
     <row r="766" spans="5:5">
-      <c r="E766" s="51"/>
+      <c r="E766" s="50"/>
     </row>
     <row r="767" spans="5:5">
-      <c r="E767" s="51"/>
+      <c r="E767" s="50"/>
     </row>
     <row r="768" spans="5:5">
-      <c r="E768" s="51"/>
+      <c r="E768" s="50"/>
     </row>
     <row r="769" spans="5:5">
-      <c r="E769" s="51"/>
+      <c r="E769" s="50"/>
     </row>
     <row r="770" spans="5:5">
-      <c r="E770" s="51"/>
+      <c r="E770" s="50"/>
     </row>
     <row r="771" spans="5:5">
-      <c r="E771" s="51"/>
+      <c r="E771" s="50"/>
     </row>
     <row r="772" spans="5:5">
-      <c r="E772" s="51"/>
+      <c r="E772" s="50"/>
     </row>
     <row r="773" spans="5:5">
-      <c r="E773" s="51"/>
+      <c r="E773" s="50"/>
     </row>
     <row r="774" spans="5:5">
-      <c r="E774" s="51"/>
+      <c r="E774" s="50"/>
     </row>
     <row r="775" spans="5:5">
-      <c r="E775" s="51"/>
+      <c r="E775" s="50"/>
     </row>
     <row r="776" spans="5:5">
-      <c r="E776" s="51"/>
+      <c r="E776" s="50"/>
     </row>
     <row r="777" spans="5:5">
-      <c r="E777" s="51"/>
+      <c r="E777" s="50"/>
     </row>
     <row r="778" spans="5:5">
-      <c r="E778" s="51"/>
+      <c r="E778" s="50"/>
     </row>
     <row r="779" spans="5:5">
-      <c r="E779" s="51"/>
+      <c r="E779" s="50"/>
     </row>
     <row r="780" spans="5:5">
-      <c r="E780" s="51"/>
+      <c r="E780" s="50"/>
     </row>
     <row r="781" spans="5:5">
-      <c r="E781" s="51"/>
+      <c r="E781" s="50"/>
     </row>
     <row r="782" spans="5:5">
-      <c r="E782" s="51"/>
+      <c r="E782" s="50"/>
     </row>
     <row r="783" spans="5:5">
-      <c r="E783" s="51"/>
+      <c r="E783" s="50"/>
     </row>
     <row r="784" spans="5:5">
-      <c r="E784" s="51"/>
+      <c r="E784" s="50"/>
     </row>
     <row r="785" spans="5:5">
-      <c r="E785" s="51"/>
+      <c r="E785" s="50"/>
     </row>
     <row r="786" spans="5:5">
-      <c r="E786" s="51"/>
+      <c r="E786" s="50"/>
     </row>
     <row r="787" spans="5:5">
-      <c r="E787" s="51"/>
+      <c r="E787" s="50"/>
     </row>
     <row r="788" spans="5:5">
-      <c r="E788" s="51"/>
+      <c r="E788" s="50"/>
     </row>
     <row r="789" spans="5:5">
-      <c r="E789" s="51"/>
+      <c r="E789" s="50"/>
     </row>
     <row r="790" spans="5:5">
-      <c r="E790" s="51"/>
+      <c r="E790" s="50"/>
     </row>
     <row r="791" spans="5:5">
-      <c r="E791" s="51"/>
+      <c r="E791" s="50"/>
     </row>
     <row r="792" spans="5:5">
-      <c r="E792" s="51"/>
+      <c r="E792" s="50"/>
     </row>
     <row r="793" spans="5:5">
-      <c r="E793" s="51"/>
+      <c r="E793" s="50"/>
     </row>
     <row r="794" spans="5:5">
-      <c r="E794" s="51"/>
+      <c r="E794" s="50"/>
     </row>
     <row r="795" spans="5:5">
-      <c r="E795" s="51"/>
+      <c r="E795" s="50"/>
     </row>
     <row r="796" spans="5:5">
-      <c r="E796" s="51"/>
+      <c r="E796" s="50"/>
     </row>
     <row r="797" spans="5:5">
-      <c r="E797" s="51"/>
+      <c r="E797" s="50"/>
     </row>
     <row r="798" spans="5:5">
-      <c r="E798" s="51"/>
+      <c r="E798" s="50"/>
     </row>
     <row r="799" spans="5:5">
-      <c r="E799" s="51"/>
+      <c r="E799" s="50"/>
     </row>
     <row r="800" spans="5:5">
-      <c r="E800" s="51"/>
+      <c r="E800" s="50"/>
     </row>
     <row r="801" spans="5:5">
-      <c r="E801" s="51"/>
+      <c r="E801" s="50"/>
     </row>
     <row r="802" spans="5:5">
-      <c r="E802" s="51"/>
+      <c r="E802" s="50"/>
     </row>
     <row r="803" spans="5:5">
-      <c r="E803" s="51"/>
+      <c r="E803" s="50"/>
     </row>
     <row r="804" spans="5:5">
-      <c r="E804" s="51"/>
+      <c r="E804" s="50"/>
     </row>
     <row r="805" spans="5:5">
-      <c r="E805" s="51"/>
+      <c r="E805" s="50"/>
     </row>
     <row r="806" spans="5:5">
-      <c r="E806" s="51"/>
+      <c r="E806" s="50"/>
     </row>
     <row r="807" spans="5:5">
-      <c r="E807" s="51"/>
+      <c r="E807" s="50"/>
     </row>
     <row r="808" spans="5:5">
-      <c r="E808" s="51"/>
+      <c r="E808" s="50"/>
     </row>
     <row r="809" spans="5:5">
-      <c r="E809" s="51"/>
+      <c r="E809" s="50"/>
     </row>
     <row r="810" spans="5:5">
-      <c r="E810" s="51"/>
+      <c r="E810" s="50"/>
     </row>
     <row r="811" spans="5:5">
-      <c r="E811" s="51"/>
+      <c r="E811" s="50"/>
     </row>
     <row r="812" spans="5:5">
-      <c r="E812" s="51"/>
+      <c r="E812" s="50"/>
     </row>
     <row r="813" spans="5:5">
-      <c r="E813" s="51"/>
+      <c r="E813" s="50"/>
     </row>
     <row r="814" spans="5:5">
-      <c r="E814" s="51"/>
+      <c r="E814" s="50"/>
     </row>
     <row r="815" spans="5:5">
-      <c r="E815" s="51"/>
+      <c r="E815" s="50"/>
     </row>
     <row r="816" spans="5:5">
-      <c r="E816" s="51"/>
+      <c r="E816" s="50"/>
     </row>
     <row r="817" spans="5:5">
-      <c r="E817" s="51"/>
+      <c r="E817" s="50"/>
     </row>
     <row r="818" spans="5:5">
-      <c r="E818" s="51"/>
+      <c r="E818" s="50"/>
     </row>
     <row r="819" spans="5:5">
-      <c r="E819" s="51"/>
+      <c r="E819" s="50"/>
     </row>
     <row r="820" spans="5:5">
-      <c r="E820" s="51"/>
+      <c r="E820" s="50"/>
     </row>
     <row r="821" spans="5:5">
-      <c r="E821" s="51"/>
+      <c r="E821" s="50"/>
     </row>
     <row r="822" spans="5:5">
-      <c r="E822" s="51"/>
+      <c r="E822" s="50"/>
     </row>
     <row r="823" spans="5:5">
-      <c r="E823" s="51"/>
+      <c r="E823" s="50"/>
     </row>
     <row r="824" spans="5:5">
-      <c r="E824" s="51"/>
+      <c r="E824" s="50"/>
     </row>
     <row r="825" spans="5:5">
-      <c r="E825" s="51"/>
+      <c r="E825" s="50"/>
     </row>
     <row r="826" spans="5:5">
-      <c r="E826" s="51"/>
+      <c r="E826" s="50"/>
     </row>
     <row r="827" spans="5:5">
-      <c r="E827" s="51"/>
+      <c r="E827" s="50"/>
     </row>
     <row r="828" spans="5:5">
-      <c r="E828" s="51"/>
+      <c r="E828" s="50"/>
     </row>
     <row r="829" spans="5:5">
-      <c r="E829" s="51"/>
+      <c r="E829" s="50"/>
     </row>
     <row r="830" spans="5:5">
-      <c r="E830" s="51"/>
+      <c r="E830" s="50"/>
     </row>
     <row r="831" spans="5:5">
-      <c r="E831" s="51"/>
+      <c r="E831" s="50"/>
     </row>
     <row r="832" spans="5:5">
-      <c r="E832" s="51"/>
+      <c r="E832" s="50"/>
     </row>
     <row r="833" spans="5:5">
-      <c r="E833" s="51"/>
+      <c r="E833" s="50"/>
     </row>
     <row r="834" spans="5:5">
-      <c r="E834" s="51"/>
+      <c r="E834" s="50"/>
     </row>
     <row r="835" spans="5:5">
-      <c r="E835" s="51"/>
+      <c r="E835" s="50"/>
     </row>
     <row r="836" spans="5:5">
-      <c r="E836" s="51"/>
+      <c r="E836" s="50"/>
     </row>
     <row r="837" spans="5:5">
-      <c r="E837" s="51"/>
+      <c r="E837" s="50"/>
     </row>
     <row r="838" spans="5:5">
-      <c r="E838" s="51"/>
+      <c r="E838" s="50"/>
     </row>
     <row r="839" spans="5:5">
-      <c r="E839" s="51"/>
+      <c r="E839" s="50"/>
     </row>
     <row r="840" spans="5:5">
-      <c r="E840" s="51"/>
+      <c r="E840" s="50"/>
     </row>
     <row r="841" spans="5:5">
-      <c r="E841" s="51"/>
+      <c r="E841" s="50"/>
     </row>
     <row r="842" spans="5:5">
-      <c r="E842" s="51"/>
+      <c r="E842" s="50"/>
     </row>
     <row r="843" spans="5:5">
-      <c r="E843" s="51"/>
+      <c r="E843" s="50"/>
     </row>
     <row r="844" spans="5:5">
-      <c r="E844" s="51"/>
+      <c r="E844" s="50"/>
     </row>
     <row r="845" spans="5:5">
-      <c r="E845" s="51"/>
+      <c r="E845" s="50"/>
     </row>
     <row r="846" spans="5:5">
-      <c r="E846" s="51"/>
+      <c r="E846" s="50"/>
     </row>
     <row r="847" spans="5:5">
-      <c r="E847" s="51"/>
+      <c r="E847" s="50"/>
     </row>
     <row r="848" spans="5:5">
-      <c r="E848" s="51"/>
+      <c r="E848" s="50"/>
     </row>
     <row r="849" spans="5:5">
-      <c r="E849" s="51"/>
+      <c r="E849" s="50"/>
     </row>
     <row r="850" spans="5:5">
-      <c r="E850" s="51"/>
+      <c r="E850" s="50"/>
     </row>
     <row r="851" spans="5:5">
-      <c r="E851" s="51"/>
+      <c r="E851" s="50"/>
     </row>
     <row r="852" spans="5:5">
-      <c r="E852" s="51"/>
+      <c r="E852" s="50"/>
     </row>
     <row r="853" spans="5:5">
-      <c r="E853" s="51"/>
+      <c r="E853" s="50"/>
     </row>
     <row r="854" spans="5:5">
-      <c r="E854" s="51"/>
+      <c r="E854" s="50"/>
     </row>
     <row r="855" spans="5:5">
-      <c r="E855" s="51"/>
+      <c r="E855" s="50"/>
     </row>
     <row r="856" spans="5:5">
-      <c r="E856" s="51"/>
+      <c r="E856" s="50"/>
     </row>
     <row r="857" spans="5:5">
-      <c r="E857" s="51"/>
+      <c r="E857" s="50"/>
     </row>
     <row r="858" spans="5:5">
-      <c r="E858" s="51"/>
+      <c r="E858" s="50"/>
     </row>
     <row r="859" spans="5:5">
-      <c r="E859" s="51"/>
+      <c r="E859" s="50"/>
     </row>
     <row r="860" spans="5:5">
-      <c r="E860" s="51"/>
+      <c r="E860" s="50"/>
     </row>
     <row r="861" spans="5:5">
-      <c r="E861" s="51"/>
+      <c r="E861" s="50"/>
     </row>
     <row r="862" spans="5:5">
-      <c r="E862" s="51"/>
+      <c r="E862" s="50"/>
     </row>
     <row r="863" spans="5:5">
-      <c r="E863" s="51"/>
+      <c r="E863" s="50"/>
     </row>
     <row r="864" spans="5:5">
-      <c r="E864" s="51"/>
+      <c r="E864" s="50"/>
     </row>
     <row r="865" spans="5:5">
-      <c r="E865" s="51"/>
+      <c r="E865" s="50"/>
     </row>
     <row r="866" spans="5:5">
-      <c r="E866" s="51"/>
+      <c r="E866" s="50"/>
     </row>
     <row r="867" spans="5:5">
-      <c r="E867" s="51"/>
+      <c r="E867" s="50"/>
     </row>
     <row r="868" spans="5:5">
-      <c r="E868" s="51"/>
+      <c r="E868" s="50"/>
     </row>
     <row r="869" spans="5:5">
-      <c r="E869" s="51"/>
+      <c r="E869" s="50"/>
     </row>
     <row r="870" spans="5:5">
-      <c r="E870" s="51"/>
+      <c r="E870" s="50"/>
     </row>
     <row r="871" spans="5:5">
-      <c r="E871" s="51"/>
+      <c r="E871" s="50"/>
     </row>
     <row r="872" spans="5:5">
-      <c r="E872" s="51"/>
+      <c r="E872" s="50"/>
     </row>
     <row r="873" spans="5:5">
-      <c r="E873" s="51"/>
+      <c r="E873" s="50"/>
     </row>
     <row r="874" spans="5:5">
-      <c r="E874" s="51"/>
+      <c r="E874" s="50"/>
     </row>
     <row r="875" spans="5:5">
-      <c r="E875" s="51"/>
+      <c r="E875" s="50"/>
     </row>
     <row r="876" spans="5:5">
-      <c r="E876" s="51"/>
+      <c r="E876" s="50"/>
     </row>
     <row r="877" spans="5:5">
-      <c r="E877" s="51"/>
+      <c r="E877" s="50"/>
     </row>
     <row r="878" spans="5:5">
-      <c r="E878" s="51"/>
+      <c r="E878" s="50"/>
     </row>
     <row r="879" spans="5:5">
-      <c r="E879" s="51"/>
+      <c r="E879" s="50"/>
     </row>
     <row r="880" spans="5:5">
-      <c r="E880" s="51"/>
+      <c r="E880" s="50"/>
     </row>
     <row r="881" spans="5:5">
-      <c r="E881" s="51"/>
+      <c r="E881" s="50"/>
     </row>
     <row r="882" spans="5:5">
-      <c r="E882" s="51"/>
+      <c r="E882" s="50"/>
     </row>
     <row r="883" spans="5:5">
-      <c r="E883" s="51"/>
+      <c r="E883" s="50"/>
     </row>
     <row r="884" spans="5:5">
-      <c r="E884" s="51"/>
+      <c r="E884" s="50"/>
     </row>
     <row r="885" spans="5:5">
-      <c r="E885" s="51"/>
+      <c r="E885" s="50"/>
     </row>
     <row r="886" spans="5:5">
-      <c r="E886" s="51"/>
+      <c r="E886" s="50"/>
     </row>
     <row r="887" spans="5:5">
-      <c r="E887" s="51"/>
+      <c r="E887" s="50"/>
     </row>
     <row r="888" spans="5:5">
-      <c r="E888" s="51"/>
+      <c r="E888" s="50"/>
     </row>
     <row r="889" spans="5:5">
-      <c r="E889" s="51"/>
+      <c r="E889" s="50"/>
     </row>
     <row r="890" spans="5:5">
-      <c r="E890" s="51"/>
+      <c r="E890" s="50"/>
     </row>
     <row r="891" spans="5:5">
-      <c r="E891" s="51"/>
+      <c r="E891" s="50"/>
     </row>
     <row r="892" spans="5:5">
-      <c r="E892" s="51"/>
+      <c r="E892" s="50"/>
     </row>
     <row r="893" spans="5:5">
-      <c r="E893" s="51"/>
+      <c r="E893" s="50"/>
     </row>
     <row r="894" spans="5:5">
-      <c r="E894" s="51"/>
+      <c r="E894" s="50"/>
     </row>
     <row r="895" spans="5:5">
-      <c r="E895" s="51"/>
+      <c r="E895" s="50"/>
     </row>
     <row r="896" spans="5:5">
-      <c r="E896" s="51"/>
+      <c r="E896" s="50"/>
     </row>
     <row r="897" spans="5:5">
-      <c r="E897" s="51"/>
+      <c r="E897" s="50"/>
     </row>
     <row r="898" spans="5:5">
-      <c r="E898" s="51"/>
+      <c r="E898" s="50"/>
     </row>
     <row r="899" spans="5:5">
-      <c r="E899" s="51"/>
+      <c r="E899" s="50"/>
     </row>
     <row r="900" spans="5:5">
-      <c r="E900" s="51"/>
+      <c r="E900" s="50"/>
     </row>
     <row r="901" spans="5:5">
-      <c r="E901" s="51"/>
+      <c r="E901" s="50"/>
     </row>
     <row r="902" spans="5:5">
-      <c r="E902" s="51"/>
+      <c r="E902" s="50"/>
     </row>
     <row r="903" spans="5:5">
-      <c r="E903" s="51"/>
+      <c r="E903" s="50"/>
     </row>
     <row r="904" spans="5:5">
-      <c r="E904" s="51"/>
+      <c r="E904" s="50"/>
     </row>
     <row r="905" spans="5:5">
-      <c r="E905" s="51"/>
+      <c r="E905" s="50"/>
     </row>
     <row r="906" spans="5:5">
-      <c r="E906" s="51"/>
+      <c r="E906" s="50"/>
     </row>
     <row r="907" spans="5:5">
-      <c r="E907" s="51"/>
+      <c r="E907" s="50"/>
     </row>
     <row r="908" spans="5:5">
-      <c r="E908" s="51"/>
+      <c r="E908" s="50"/>
     </row>
     <row r="909" spans="5:5">
-      <c r="E909" s="51"/>
+      <c r="E909" s="50"/>
     </row>
     <row r="910" spans="5:5">
-      <c r="E910" s="51"/>
+      <c r="E910" s="50"/>
     </row>
     <row r="911" spans="5:5">
-      <c r="E911" s="51"/>
+      <c r="E911" s="50"/>
     </row>
     <row r="912" spans="5:5">
-      <c r="E912" s="51"/>
+      <c r="E912" s="50"/>
     </row>
     <row r="913" spans="5:5">
-      <c r="E913" s="51"/>
+      <c r="E913" s="50"/>
     </row>
     <row r="914" spans="5:5">
-      <c r="E914" s="51"/>
+      <c r="E914" s="50"/>
     </row>
     <row r="915" spans="5:5">
-      <c r="E915" s="51"/>
+      <c r="E915" s="50"/>
     </row>
     <row r="916" spans="5:5">
-      <c r="E916" s="51"/>
+      <c r="E916" s="50"/>
     </row>
     <row r="917" spans="5:5">
-      <c r="E917" s="51"/>
+      <c r="E917" s="50"/>
     </row>
     <row r="918" spans="5:5">
-      <c r="E918" s="51"/>
+      <c r="E918" s="50"/>
     </row>
     <row r="919" spans="5:5">
-      <c r="E919" s="51"/>
+      <c r="E919" s="50"/>
     </row>
     <row r="920" spans="5:5">
-      <c r="E920" s="51"/>
+      <c r="E920" s="50"/>
     </row>
     <row r="921" spans="5:5">
-      <c r="E921" s="51"/>
+      <c r="E921" s="50"/>
     </row>
     <row r="922" spans="5:5">
-      <c r="E922" s="51"/>
+      <c r="E922" s="50"/>
     </row>
     <row r="923" spans="5:5">
-      <c r="E923" s="51"/>
+      <c r="E923" s="50"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -7450,50 +7642,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:30" s="1" customFormat="1" ht="125" customHeight="1">
-      <c r="A1" s="59" t="s">
-        <v>541</v>
-      </c>
-      <c r="B1" s="60"/>
-      <c r="C1" s="60"/>
-      <c r="D1" s="60"/>
-      <c r="E1" s="60"/>
-      <c r="F1" s="60"/>
-      <c r="G1" s="60"/>
-      <c r="H1" s="60"/>
-      <c r="I1" s="60"/>
-      <c r="J1" s="60"/>
-      <c r="K1" s="60"/>
-      <c r="L1" s="60"/>
-      <c r="M1" s="60"/>
-      <c r="N1" s="60"/>
-      <c r="O1" s="60"/>
-      <c r="P1" s="60"/>
-      <c r="Q1" s="60"/>
-      <c r="R1" s="60"/>
-      <c r="S1" s="60"/>
-      <c r="T1" s="60"/>
-      <c r="U1" s="60"/>
-      <c r="V1" s="60"/>
-      <c r="W1" s="60"/>
-      <c r="X1" s="60"/>
-      <c r="Y1" s="60"/>
-      <c r="Z1" s="60"/>
-      <c r="AA1" s="60"/>
-      <c r="AB1" s="52"/>
-      <c r="AC1" s="52"/>
-      <c r="AD1" s="52"/>
-    </row>
-    <row r="2" spans="1:30" s="54" customFormat="1" ht="32">
-      <c r="A2" s="47" t="s">
+      <c r="A1" s="60" t="s">
+        <v>540</v>
+      </c>
+      <c r="B1" s="58"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
+      <c r="F1" s="58"/>
+      <c r="G1" s="58"/>
+      <c r="H1" s="58"/>
+      <c r="I1" s="58"/>
+      <c r="J1" s="58"/>
+      <c r="K1" s="58"/>
+      <c r="L1" s="58"/>
+      <c r="M1" s="58"/>
+      <c r="N1" s="58"/>
+      <c r="O1" s="58"/>
+      <c r="P1" s="58"/>
+      <c r="Q1" s="58"/>
+      <c r="R1" s="58"/>
+      <c r="S1" s="58"/>
+      <c r="T1" s="58"/>
+      <c r="U1" s="58"/>
+      <c r="V1" s="58"/>
+      <c r="W1" s="58"/>
+      <c r="X1" s="58"/>
+      <c r="Y1" s="58"/>
+      <c r="Z1" s="58"/>
+      <c r="AA1" s="58"/>
+      <c r="AB1" s="51"/>
+      <c r="AC1" s="51"/>
+      <c r="AD1" s="51"/>
+    </row>
+    <row r="2" spans="1:30" s="53" customFormat="1" ht="32">
+      <c r="A2" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="47" t="s">
+      <c r="B2" s="46" t="s">
         <v>473</v>
       </c>
-      <c r="C2" s="48" t="s">
+      <c r="C2" s="47" t="s">
         <v>474</v>
       </c>
-      <c r="D2" s="48" t="s">
+      <c r="D2" s="47" t="s">
         <v>500</v>
       </c>
       <c r="E2" s="7" t="s">
@@ -7502,55 +7694,55 @@
       <c r="F2" s="7" t="s">
         <v>530</v>
       </c>
-      <c r="G2" s="47" t="s">
+      <c r="G2" s="46" t="s">
         <v>501</v>
       </c>
-      <c r="H2" s="47" t="s">
+      <c r="H2" s="46" t="s">
         <v>502</v>
       </c>
-      <c r="I2" s="48" t="s">
+      <c r="I2" s="47" t="s">
         <v>179</v>
       </c>
-      <c r="J2" s="47" t="s">
+      <c r="J2" s="46" t="s">
         <v>503</v>
       </c>
-      <c r="K2" s="47" t="s">
+      <c r="K2" s="46" t="s">
         <v>504</v>
       </c>
-      <c r="L2" s="47" t="s">
+      <c r="L2" s="46" t="s">
         <v>505</v>
       </c>
-      <c r="M2" s="47" t="s">
+      <c r="M2" s="46" t="s">
         <v>506</v>
       </c>
-      <c r="N2" s="47" t="s">
+      <c r="N2" s="46" t="s">
         <v>507</v>
       </c>
-      <c r="O2" s="47" t="s">
+      <c r="O2" s="46" t="s">
         <v>521</v>
       </c>
-      <c r="P2" s="47" t="s">
+      <c r="P2" s="46" t="s">
         <v>522</v>
       </c>
-      <c r="Q2" s="47" t="s">
+      <c r="Q2" s="46" t="s">
         <v>525</v>
       </c>
-      <c r="R2" s="47" t="s">
+      <c r="R2" s="46" t="s">
         <v>515</v>
       </c>
-      <c r="S2" s="47" t="s">
+      <c r="S2" s="46" t="s">
         <v>516</v>
       </c>
-      <c r="T2" s="47" t="s">
+      <c r="T2" s="46" t="s">
         <v>508</v>
       </c>
-      <c r="U2" s="47" t="s">
+      <c r="U2" s="46" t="s">
         <v>509</v>
       </c>
-      <c r="V2" s="47" t="s">
+      <c r="V2" s="46" t="s">
         <v>517</v>
       </c>
-      <c r="W2" s="53" t="s">
+      <c r="W2" s="52" t="s">
         <v>461</v>
       </c>
       <c r="X2"/>
@@ -7562,13 +7754,13 @@
       <c r="AD2"/>
     </row>
     <row r="3" spans="1:30" ht="48">
-      <c r="A3" s="50" t="s">
+      <c r="A3" s="49" t="s">
         <v>467</v>
       </c>
       <c r="B3" s="24" t="s">
         <v>528</v>
       </c>
-      <c r="C3" s="38" t="s">
+      <c r="C3" s="37" t="s">
         <v>510</v>
       </c>
       <c r="D3" s="24" t="s">
@@ -7586,44 +7778,44 @@
       <c r="H3" s="24">
         <v>4</v>
       </c>
-      <c r="I3" s="38" t="s">
+      <c r="I3" s="37" t="s">
         <v>225</v>
       </c>
-      <c r="J3" s="38" t="s">
+      <c r="J3" s="37" t="s">
         <v>537</v>
       </c>
-      <c r="K3" s="38" t="s">
+      <c r="K3" s="37" t="s">
         <v>526</v>
       </c>
-      <c r="L3" s="38">
+      <c r="L3" s="37">
         <v>914</v>
       </c>
-      <c r="M3" s="38">
+      <c r="M3" s="37">
         <v>1390</v>
       </c>
-      <c r="N3" s="38">
+      <c r="N3" s="37">
         <v>96</v>
       </c>
-      <c r="O3" s="38" t="s">
+      <c r="O3" s="37" t="s">
         <v>524</v>
       </c>
-      <c r="P3" s="56" t="s">
+      <c r="P3" s="55" t="s">
         <v>523</v>
       </c>
-      <c r="Q3" s="56"/>
-      <c r="R3" s="38" t="b">
+      <c r="Q3" s="55"/>
+      <c r="R3" s="37" t="b">
         <v>0</v>
       </c>
-      <c r="S3" s="55" t="b">
+      <c r="S3" s="54" t="b">
         <v>0</v>
       </c>
-      <c r="T3" s="38" t="s">
+      <c r="T3" s="37" t="s">
         <v>520</v>
       </c>
-      <c r="U3" s="55" t="s">
+      <c r="U3" s="54" t="s">
         <v>513</v>
       </c>
-      <c r="V3" s="55" t="s">
+      <c r="V3" s="54" t="s">
         <v>518</v>
       </c>
       <c r="W3" s="25" t="s">
@@ -7631,13 +7823,13 @@
       </c>
     </row>
     <row r="4" spans="1:30" ht="48">
-      <c r="A4" s="50" t="s">
+      <c r="A4" s="49" t="s">
         <v>467</v>
       </c>
       <c r="B4" s="24" t="s">
         <v>528</v>
       </c>
-      <c r="C4" s="38" t="s">
+      <c r="C4" s="37" t="s">
         <v>510</v>
       </c>
       <c r="D4" s="24" t="s">
@@ -7655,44 +7847,44 @@
       <c r="H4" s="24">
         <v>4</v>
       </c>
-      <c r="I4" s="38" t="s">
+      <c r="I4" s="37" t="s">
         <v>225</v>
       </c>
-      <c r="J4" s="38" t="s">
+      <c r="J4" s="37" t="s">
         <v>538</v>
       </c>
-      <c r="K4" s="38" t="s">
+      <c r="K4" s="37" t="s">
         <v>526</v>
       </c>
-      <c r="L4" s="38">
+      <c r="L4" s="37">
         <v>914</v>
       </c>
-      <c r="M4" s="38">
+      <c r="M4" s="37">
         <v>1390</v>
       </c>
-      <c r="N4" s="38">
+      <c r="N4" s="37">
         <v>96</v>
       </c>
-      <c r="O4" s="38" t="s">
+      <c r="O4" s="37" t="s">
         <v>524</v>
       </c>
-      <c r="P4" s="56" t="s">
+      <c r="P4" s="55" t="s">
         <v>523</v>
       </c>
-      <c r="Q4" s="56"/>
-      <c r="R4" s="38" t="b">
+      <c r="Q4" s="55"/>
+      <c r="R4" s="37" t="b">
         <v>0</v>
       </c>
-      <c r="S4" s="55" t="b">
+      <c r="S4" s="54" t="b">
         <v>0</v>
       </c>
-      <c r="T4" s="38" t="s">
+      <c r="T4" s="37" t="s">
         <v>520</v>
       </c>
-      <c r="U4" s="55" t="s">
+      <c r="U4" s="54" t="s">
         <v>513</v>
       </c>
-      <c r="V4" s="55" t="s">
+      <c r="V4" s="54" t="s">
         <v>518</v>
       </c>
       <c r="W4" s="25" t="s">
@@ -12554,48 +12746,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="32">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="38" t="s">
         <v>211</v>
       </c>
-      <c r="B1" s="39" t="s">
+      <c r="B1" s="38" t="s">
         <v>176</v>
       </c>
-      <c r="C1" s="40" t="s">
+      <c r="C1" s="39" t="s">
         <v>212</v>
       </c>
-      <c r="D1" s="40" t="s">
+      <c r="D1" s="39" t="s">
         <v>213</v>
       </c>
-      <c r="E1" s="39" t="s">
+      <c r="E1" s="38" t="s">
         <v>214</v>
       </c>
-      <c r="F1" s="41" t="s">
+      <c r="F1" s="40" t="s">
         <v>179</v>
       </c>
-      <c r="G1" s="41" t="s">
+      <c r="G1" s="40" t="s">
         <v>96</v>
       </c>
-      <c r="H1" s="41" t="s">
+      <c r="H1" s="40" t="s">
         <v>95</v>
       </c>
-      <c r="I1" s="42" t="s">
+      <c r="I1" s="41" t="s">
         <v>177</v>
       </c>
-      <c r="J1" s="42" t="s">
+      <c r="J1" s="41" t="s">
         <v>178</v>
       </c>
-      <c r="K1" s="41" t="s">
+      <c r="K1" s="40" t="s">
         <v>175</v>
       </c>
-      <c r="L1" s="40" t="s">
+      <c r="L1" s="39" t="s">
         <v>215</v>
       </c>
-      <c r="M1" s="40" t="s">
+      <c r="M1" s="39" t="s">
         <v>397</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="16">
-      <c r="A2" s="43" t="s">
+      <c r="A2" s="42" t="s">
         <v>216</v>
       </c>
       <c r="B2" s="22" t="s">
@@ -12613,7 +12805,7 @@
       <c r="F2" s="22" t="s">
         <v>97</v>
       </c>
-      <c r="G2" s="44" t="s">
+      <c r="G2" s="43" t="s">
         <v>101</v>
       </c>
       <c r="H2" s="18" t="s">
@@ -12636,7 +12828,7 @@
       </c>
     </row>
     <row r="3" spans="1:13" ht="16">
-      <c r="A3" s="43" t="s">
+      <c r="A3" s="42" t="s">
         <v>221</v>
       </c>
       <c r="B3" s="18" t="s">
@@ -12654,7 +12846,7 @@
       <c r="F3" s="18" t="s">
         <v>225</v>
       </c>
-      <c r="G3" s="44" t="s">
+      <c r="G3" s="43" t="s">
         <v>226</v>
       </c>
       <c r="H3" s="18" t="s">
@@ -12677,7 +12869,7 @@
       </c>
     </row>
     <row r="4" spans="1:13" ht="16">
-      <c r="A4" s="43" t="s">
+      <c r="A4" s="42" t="s">
         <v>229</v>
       </c>
       <c r="B4" s="18" t="s">
@@ -12702,7 +12894,7 @@
       </c>
     </row>
     <row r="5" spans="1:13" ht="16">
-      <c r="A5" s="43" t="s">
+      <c r="A5" s="42" t="s">
         <v>102</v>
       </c>
       <c r="B5" s="18" t="s">
@@ -12727,7 +12919,7 @@
       </c>
     </row>
     <row r="6" spans="1:13" ht="16">
-      <c r="A6" s="43" t="s">
+      <c r="A6" s="42" t="s">
         <v>239</v>
       </c>
       <c r="B6" s="18"/>
@@ -12747,7 +12939,7 @@
       </c>
     </row>
     <row r="7" spans="1:13" ht="16">
-      <c r="A7" s="43" t="s">
+      <c r="A7" s="42" t="s">
         <v>243</v>
       </c>
       <c r="B7" s="18"/>
@@ -12767,7 +12959,7 @@
       </c>
     </row>
     <row r="8" spans="1:13" ht="16">
-      <c r="A8" s="43" t="s">
+      <c r="A8" s="42" t="s">
         <v>247</v>
       </c>
       <c r="B8" s="18"/>
@@ -12787,7 +12979,7 @@
       </c>
     </row>
     <row r="9" spans="1:13" ht="16">
-      <c r="A9" s="43" t="s">
+      <c r="A9" s="42" t="s">
         <v>251</v>
       </c>
       <c r="B9" s="18"/>
@@ -12807,7 +12999,7 @@
       </c>
     </row>
     <row r="10" spans="1:13" ht="16">
-      <c r="A10" s="43" t="s">
+      <c r="A10" s="42" t="s">
         <v>254</v>
       </c>
       <c r="B10" s="18"/>
@@ -12827,7 +13019,7 @@
       </c>
     </row>
     <row r="11" spans="1:13" ht="16">
-      <c r="A11" s="43" t="s">
+      <c r="A11" s="42" t="s">
         <v>258</v>
       </c>
       <c r="B11" s="18"/>
@@ -12847,7 +13039,7 @@
       </c>
     </row>
     <row r="12" spans="1:13" ht="16">
-      <c r="A12" s="43" t="s">
+      <c r="A12" s="42" t="s">
         <v>262</v>
       </c>
       <c r="B12" s="18"/>
@@ -12867,7 +13059,7 @@
       </c>
     </row>
     <row r="13" spans="1:13" ht="16">
-      <c r="A13" s="43" t="s">
+      <c r="A13" s="42" t="s">
         <v>266</v>
       </c>
       <c r="B13" s="18"/>
@@ -12887,7 +13079,7 @@
       </c>
     </row>
     <row r="14" spans="1:13" ht="16">
-      <c r="A14" s="43" t="s">
+      <c r="A14" s="42" t="s">
         <v>103</v>
       </c>
       <c r="B14" s="18"/>
@@ -14119,7 +14311,7 @@
       <c r="K2" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="L2" s="46" t="s">
+      <c r="L2" s="45" t="s">
         <v>376</v>
       </c>
       <c r="M2" s="29" t="s">
@@ -14229,7 +14421,7 @@
         <f t="array" aca="1" ref="AT2" ca="1">_xlfn.UNIQUE(INDIRECT("B2:B"&amp;$G$5),FALSE,FALSE)</f>
         <v>#REF!</v>
       </c>
-      <c r="AU2" s="45" t="e">
+      <c r="AU2" s="44" t="e">
         <f ca="1">_xlfn.IFNA(IF($H2+1&gt;$G$2,"",INDEX(INDIRECT("SubnetsVLANs!$D$"&amp;$H2+2&amp;":$D$"&amp;$G$2),MATCH("Subnet*",INDIRECT("SubnetsVLANs!$E$"&amp;$H2+2&amp;":$E$"&amp;$G$2),0))),"")</f>
         <v>#REF!</v>
       </c>
@@ -14376,7 +14568,7 @@
       <c r="AS3" s="28" t="s">
         <v>190</v>
       </c>
-      <c r="AU3" s="45" t="e">
+      <c r="AU3" s="44" t="e">
         <f t="shared" ref="AU3:AU67" ca="1" si="1">_xlfn.IFNA(IF($H3+1&gt;$G$2,"",INDEX(INDIRECT("SubnetsVLANs!$D$"&amp;$H3+2&amp;":$D$"&amp;$G$2),MATCH("Subnet*",INDIRECT("SubnetsVLANs!$E$"&amp;$H3+2&amp;":$E$"&amp;$G$2),0))),"")</f>
         <v>#REF!</v>
       </c>
@@ -14489,7 +14681,7 @@
       <c r="AS4" s="28" t="s">
         <v>183</v>
       </c>
-      <c r="AU4" s="45" t="e">
+      <c r="AU4" s="44" t="e">
         <f t="shared" ca="1" si="1"/>
         <v>#REF!</v>
       </c>
@@ -14581,7 +14773,7 @@
       <c r="AN5" s="29">
         <v>64</v>
       </c>
-      <c r="AU5" s="45" t="e">
+      <c r="AU5" s="44" t="e">
         <f t="shared" ca="1" si="1"/>
         <v>#REF!</v>
       </c>
@@ -14665,7 +14857,7 @@
         <v>308</v>
       </c>
       <c r="AN6" s="29"/>
-      <c r="AU6" s="45" t="e">
+      <c r="AU6" s="44" t="e">
         <f t="shared" ca="1" si="1"/>
         <v>#REF!</v>
       </c>
@@ -14744,7 +14936,7 @@
       <c r="AL7" s="29"/>
       <c r="AM7" s="29"/>
       <c r="AN7" s="29"/>
-      <c r="AU7" s="45" t="e">
+      <c r="AU7" s="44" t="e">
         <f t="shared" ca="1" si="1"/>
         <v>#REF!</v>
       </c>
@@ -14823,7 +15015,7 @@
       <c r="AL8" s="29"/>
       <c r="AM8" s="29"/>
       <c r="AN8" s="29"/>
-      <c r="AU8" s="45" t="e">
+      <c r="AU8" s="44" t="e">
         <f t="shared" ca="1" si="1"/>
         <v>#REF!</v>
       </c>
@@ -14902,7 +15094,7 @@
       <c r="AL9" s="29"/>
       <c r="AM9" s="29"/>
       <c r="AN9" s="29"/>
-      <c r="AU9" s="45" t="e">
+      <c r="AU9" s="44" t="e">
         <f t="shared" ca="1" si="1"/>
         <v>#REF!</v>
       </c>
@@ -14981,7 +15173,7 @@
       <c r="AL10" s="29"/>
       <c r="AM10" s="29"/>
       <c r="AN10" s="29"/>
-      <c r="AU10" s="45" t="e">
+      <c r="AU10" s="44" t="e">
         <f t="shared" ca="1" si="1"/>
         <v>#REF!</v>
       </c>
@@ -15060,7 +15252,7 @@
       <c r="AL11" s="29"/>
       <c r="AM11" s="29"/>
       <c r="AN11" s="29"/>
-      <c r="AU11" s="45" t="e">
+      <c r="AU11" s="44" t="e">
         <f t="shared" ca="1" si="1"/>
         <v>#REF!</v>
       </c>
@@ -15137,7 +15329,7 @@
       <c r="AL12" s="29"/>
       <c r="AM12" s="29"/>
       <c r="AN12" s="29"/>
-      <c r="AU12" s="45" t="e">
+      <c r="AU12" s="44" t="e">
         <f t="shared" ca="1" si="1"/>
         <v>#REF!</v>
       </c>
@@ -15214,7 +15406,7 @@
       <c r="AL13" s="29"/>
       <c r="AM13" s="29"/>
       <c r="AN13" s="29"/>
-      <c r="AU13" s="45" t="e">
+      <c r="AU13" s="44" t="e">
         <f t="shared" ca="1" si="1"/>
         <v>#REF!</v>
       </c>
@@ -15291,7 +15483,7 @@
       <c r="AL14" s="29"/>
       <c r="AM14" s="29"/>
       <c r="AN14" s="29"/>
-      <c r="AU14" s="45" t="e">
+      <c r="AU14" s="44" t="e">
         <f t="shared" ca="1" si="1"/>
         <v>#REF!</v>
       </c>
@@ -15368,7 +15560,7 @@
       <c r="AL15" s="29"/>
       <c r="AM15" s="29"/>
       <c r="AN15" s="29"/>
-      <c r="AU15" s="45" t="e">
+      <c r="AU15" s="44" t="e">
         <f t="shared" ca="1" si="1"/>
         <v>#REF!</v>
       </c>
@@ -15445,7 +15637,7 @@
       <c r="AL16" s="29"/>
       <c r="AM16" s="29"/>
       <c r="AN16" s="29"/>
-      <c r="AU16" s="45" t="e">
+      <c r="AU16" s="44" t="e">
         <f t="shared" ca="1" si="1"/>
         <v>#REF!</v>
       </c>
@@ -15522,7 +15714,7 @@
       <c r="AL17" s="29"/>
       <c r="AM17" s="29"/>
       <c r="AN17" s="29"/>
-      <c r="AU17" s="45" t="e">
+      <c r="AU17" s="44" t="e">
         <f t="shared" ca="1" si="1"/>
         <v>#REF!</v>
       </c>
@@ -15599,7 +15791,7 @@
       <c r="AL18" s="29"/>
       <c r="AM18" s="29"/>
       <c r="AN18" s="29"/>
-      <c r="AU18" s="45" t="e">
+      <c r="AU18" s="44" t="e">
         <f t="shared" ca="1" si="1"/>
         <v>#REF!</v>
       </c>
@@ -15676,7 +15868,7 @@
       <c r="AL19" s="29"/>
       <c r="AM19" s="29"/>
       <c r="AN19" s="29"/>
-      <c r="AU19" s="45" t="e">
+      <c r="AU19" s="44" t="e">
         <f t="shared" ca="1" si="1"/>
         <v>#REF!</v>
       </c>
@@ -15753,7 +15945,7 @@
       <c r="AL20" s="29"/>
       <c r="AM20" s="29"/>
       <c r="AN20" s="29"/>
-      <c r="AU20" s="45" t="e">
+      <c r="AU20" s="44" t="e">
         <f t="shared" ca="1" si="1"/>
         <v>#REF!</v>
       </c>
@@ -15830,7 +16022,7 @@
       <c r="AL21" s="29"/>
       <c r="AM21" s="29"/>
       <c r="AN21" s="29"/>
-      <c r="AU21" s="45" t="e">
+      <c r="AU21" s="44" t="e">
         <f t="shared" ca="1" si="1"/>
         <v>#REF!</v>
       </c>
@@ -15907,7 +16099,7 @@
       <c r="AL22" s="29"/>
       <c r="AM22" s="29"/>
       <c r="AN22" s="29"/>
-      <c r="AU22" s="45" t="e">
+      <c r="AU22" s="44" t="e">
         <f t="shared" ca="1" si="1"/>
         <v>#REF!</v>
       </c>
@@ -15984,7 +16176,7 @@
       <c r="AL23" s="29"/>
       <c r="AM23" s="29"/>
       <c r="AN23" s="29"/>
-      <c r="AU23" s="45" t="e">
+      <c r="AU23" s="44" t="e">
         <f t="shared" ca="1" si="1"/>
         <v>#REF!</v>
       </c>
@@ -16061,7 +16253,7 @@
       <c r="AL24" s="29"/>
       <c r="AM24" s="29"/>
       <c r="AN24" s="29"/>
-      <c r="AU24" s="45" t="e">
+      <c r="AU24" s="44" t="e">
         <f t="shared" ca="1" si="1"/>
         <v>#REF!</v>
       </c>
@@ -16138,7 +16330,7 @@
       <c r="AL25" s="29"/>
       <c r="AM25" s="29"/>
       <c r="AN25" s="29"/>
-      <c r="AU25" s="45" t="e">
+      <c r="AU25" s="44" t="e">
         <f t="shared" ca="1" si="1"/>
         <v>#REF!</v>
       </c>
@@ -16215,7 +16407,7 @@
       <c r="AL26" s="29"/>
       <c r="AM26" s="29"/>
       <c r="AN26" s="29"/>
-      <c r="AU26" s="45" t="e">
+      <c r="AU26" s="44" t="e">
         <f t="shared" ca="1" si="1"/>
         <v>#REF!</v>
       </c>
@@ -16292,7 +16484,7 @@
       <c r="AL27" s="29"/>
       <c r="AM27" s="29"/>
       <c r="AN27" s="29"/>
-      <c r="AU27" s="45" t="e">
+      <c r="AU27" s="44" t="e">
         <f t="shared" ca="1" si="1"/>
         <v>#REF!</v>
       </c>
@@ -16369,7 +16561,7 @@
       <c r="AL28" s="29"/>
       <c r="AM28" s="29"/>
       <c r="AN28" s="29"/>
-      <c r="AU28" s="45" t="e">
+      <c r="AU28" s="44" t="e">
         <f t="shared" ca="1" si="1"/>
         <v>#REF!</v>
       </c>
@@ -16442,7 +16634,7 @@
       <c r="AL29" s="29"/>
       <c r="AM29" s="29"/>
       <c r="AN29" s="29"/>
-      <c r="AU29" s="45" t="e">
+      <c r="AU29" s="44" t="e">
         <f t="shared" ca="1" si="1"/>
         <v>#REF!</v>
       </c>
@@ -16515,7 +16707,7 @@
       <c r="AL30" s="29"/>
       <c r="AM30" s="29"/>
       <c r="AN30" s="29"/>
-      <c r="AU30" s="45" t="e">
+      <c r="AU30" s="44" t="e">
         <f t="shared" ca="1" si="1"/>
         <v>#REF!</v>
       </c>
@@ -16588,7 +16780,7 @@
       <c r="AL31" s="29"/>
       <c r="AM31" s="29"/>
       <c r="AN31" s="29"/>
-      <c r="AU31" s="45" t="e">
+      <c r="AU31" s="44" t="e">
         <f t="shared" ca="1" si="1"/>
         <v>#REF!</v>
       </c>
@@ -16661,7 +16853,7 @@
       <c r="AL32" s="29"/>
       <c r="AM32" s="29"/>
       <c r="AN32" s="29"/>
-      <c r="AU32" s="45" t="e">
+      <c r="AU32" s="44" t="e">
         <f t="shared" ca="1" si="1"/>
         <v>#REF!</v>
       </c>
@@ -16734,7 +16926,7 @@
       <c r="AL33" s="29"/>
       <c r="AM33" s="29"/>
       <c r="AN33" s="29"/>
-      <c r="AU33" s="45" t="e">
+      <c r="AU33" s="44" t="e">
         <f t="shared" ca="1" si="1"/>
         <v>#REF!</v>
       </c>
@@ -16807,7 +16999,7 @@
       <c r="AL34" s="29"/>
       <c r="AM34" s="29"/>
       <c r="AN34" s="29"/>
-      <c r="AU34" s="45" t="e">
+      <c r="AU34" s="44" t="e">
         <f t="shared" ca="1" si="1"/>
         <v>#REF!</v>
       </c>
@@ -16880,7 +17072,7 @@
       <c r="AL35" s="29"/>
       <c r="AM35" s="29"/>
       <c r="AN35" s="29"/>
-      <c r="AU35" s="45" t="e">
+      <c r="AU35" s="44" t="e">
         <f t="shared" ca="1" si="1"/>
         <v>#REF!</v>
       </c>
@@ -16923,7 +17115,7 @@
       <c r="AL36" s="29"/>
       <c r="AM36" s="29"/>
       <c r="AN36" s="29"/>
-      <c r="AU36" s="45"/>
+      <c r="AU36" s="44"/>
     </row>
     <row r="37" spans="1:47" s="28" customFormat="1">
       <c r="A37" s="28">
@@ -16993,7 +17185,7 @@
       <c r="AL37" s="29"/>
       <c r="AM37" s="29"/>
       <c r="AN37" s="29"/>
-      <c r="AU37" s="45" t="e">
+      <c r="AU37" s="44" t="e">
         <f t="shared" ca="1" si="1"/>
         <v>#REF!</v>
       </c>
@@ -17066,7 +17258,7 @@
       <c r="AL38" s="29"/>
       <c r="AM38" s="29"/>
       <c r="AN38" s="29"/>
-      <c r="AU38" s="45" t="e">
+      <c r="AU38" s="44" t="e">
         <f t="shared" ca="1" si="1"/>
         <v>#REF!</v>
       </c>
@@ -17139,7 +17331,7 @@
       <c r="AL39" s="29"/>
       <c r="AM39" s="29"/>
       <c r="AN39" s="29"/>
-      <c r="AU39" s="45" t="e">
+      <c r="AU39" s="44" t="e">
         <f t="shared" ca="1" si="1"/>
         <v>#REF!</v>
       </c>
@@ -17212,7 +17404,7 @@
       <c r="AL40" s="29"/>
       <c r="AM40" s="29"/>
       <c r="AN40" s="29"/>
-      <c r="AU40" s="45" t="e">
+      <c r="AU40" s="44" t="e">
         <f t="shared" ca="1" si="1"/>
         <v>#REF!</v>
       </c>
@@ -17284,7 +17476,7 @@
       <c r="AL41" s="29"/>
       <c r="AM41" s="29"/>
       <c r="AN41" s="29"/>
-      <c r="AU41" s="45" t="e">
+      <c r="AU41" s="44" t="e">
         <f t="shared" ca="1" si="1"/>
         <v>#REF!</v>
       </c>
@@ -17331,7 +17523,7 @@
         <v>#REF!</v>
       </c>
       <c r="AK42" s="33"/>
-      <c r="AU42" s="45" t="e">
+      <c r="AU42" s="44" t="e">
         <f t="shared" ca="1" si="1"/>
         <v>#REF!</v>
       </c>
@@ -17377,7 +17569,7 @@
         <f t="array" aca="1" ref="Z43" ca="1">IF(COUNTIF(INDIRECT(ADDRESS(3,1,1,1,"instances")&amp;":"&amp;ADDRESS(A43,1,4,1)),"*END*")&gt;0,"",INDIRECT(ADDRESS(A43,4,4,1,"instances")))</f>
         <v>#REF!</v>
       </c>
-      <c r="AU43" s="45" t="e">
+      <c r="AU43" s="44" t="e">
         <f t="shared" ca="1" si="1"/>
         <v>#REF!</v>
       </c>
@@ -17423,7 +17615,7 @@
         <f t="array" aca="1" ref="Z44" ca="1">IF(COUNTIF(INDIRECT(ADDRESS(3,1,1,1,"instances")&amp;":"&amp;ADDRESS(A44,1,4,1)),"*END*")&gt;0,"",INDIRECT(ADDRESS(A44,4,4,1,"instances")))</f>
         <v>#REF!</v>
       </c>
-      <c r="AU44" s="45" t="e">
+      <c r="AU44" s="44" t="e">
         <f t="shared" ca="1" si="1"/>
         <v>#REF!</v>
       </c>
@@ -17469,7 +17661,7 @@
         <f t="array" aca="1" ref="Z45" ca="1">IF(COUNTIF(INDIRECT(ADDRESS(3,1,1,1,"instances")&amp;":"&amp;ADDRESS(A45,1,4,1)),"*END*")&gt;0,"",INDIRECT(ADDRESS(A45,4,4,1,"instances")))</f>
         <v>#REF!</v>
       </c>
-      <c r="AU45" s="45" t="e">
+      <c r="AU45" s="44" t="e">
         <f t="shared" ca="1" si="1"/>
         <v>#REF!</v>
       </c>
@@ -17515,7 +17707,7 @@
         <f t="array" aca="1" ref="Z46" ca="1">IF(COUNTIF(INDIRECT(ADDRESS(3,1,1,1,"instances")&amp;":"&amp;ADDRESS(A46,1,4,1)),"*END*")&gt;0,"",INDIRECT(ADDRESS(A46,4,4,1,"instances")))</f>
         <v>#REF!</v>
       </c>
-      <c r="AU46" s="45" t="e">
+      <c r="AU46" s="44" t="e">
         <f t="shared" ca="1" si="1"/>
         <v>#REF!</v>
       </c>
@@ -17561,7 +17753,7 @@
         <f t="array" aca="1" ref="Z47" ca="1">IF(COUNTIF(INDIRECT(ADDRESS(3,1,1,1,"instances")&amp;":"&amp;ADDRESS(A47,1,4,1)),"*END*")&gt;0,"",INDIRECT(ADDRESS(A47,4,4,1,"instances")))</f>
         <v>#REF!</v>
       </c>
-      <c r="AU47" s="45" t="e">
+      <c r="AU47" s="44" t="e">
         <f t="shared" ca="1" si="1"/>
         <v>#REF!</v>
       </c>
@@ -17607,7 +17799,7 @@
         <f t="array" aca="1" ref="Z48" ca="1">IF(COUNTIF(INDIRECT(ADDRESS(3,1,1,1,"instances")&amp;":"&amp;ADDRESS(A48,1,4,1)),"*END*")&gt;0,"",INDIRECT(ADDRESS(A48,4,4,1,"instances")))</f>
         <v>#REF!</v>
       </c>
-      <c r="AU48" s="45" t="e">
+      <c r="AU48" s="44" t="e">
         <f t="shared" ca="1" si="1"/>
         <v>#REF!</v>
       </c>
@@ -17653,7 +17845,7 @@
         <f t="array" aca="1" ref="Z49" ca="1">IF(COUNTIF(INDIRECT(ADDRESS(3,1,1,1,"instances")&amp;":"&amp;ADDRESS(A49,1,4,1)),"*END*")&gt;0,"",INDIRECT(ADDRESS(A49,4,4,1,"instances")))</f>
         <v>#REF!</v>
       </c>
-      <c r="AU49" s="45" t="e">
+      <c r="AU49" s="44" t="e">
         <f t="shared" ca="1" si="1"/>
         <v>#REF!</v>
       </c>
@@ -17699,7 +17891,7 @@
         <f t="array" aca="1" ref="Z50" ca="1">IF(COUNTIF(INDIRECT(ADDRESS(3,1,1,1,"instances")&amp;":"&amp;ADDRESS(A50,1,4,1)),"*END*")&gt;0,"",INDIRECT(ADDRESS(A50,4,4,1,"instances")))</f>
         <v>#REF!</v>
       </c>
-      <c r="AU50" s="45" t="e">
+      <c r="AU50" s="44" t="e">
         <f t="shared" ca="1" si="1"/>
         <v>#REF!</v>
       </c>
@@ -17719,7 +17911,7 @@
         <v>201</v>
       </c>
       <c r="AG51" s="34"/>
-      <c r="AU51" s="45" t="e">
+      <c r="AU51" s="44" t="e">
         <f t="shared" ca="1" si="1"/>
         <v>#REF!</v>
       </c>
@@ -17738,7 +17930,7 @@
       <c r="L52" s="20" t="s">
         <v>377</v>
       </c>
-      <c r="AU52" s="45" t="e">
+      <c r="AU52" s="44" t="e">
         <f t="shared" ca="1" si="1"/>
         <v>#REF!</v>
       </c>
@@ -17758,7 +17950,7 @@
       <c r="L53" t="s">
         <v>202</v>
       </c>
-      <c r="AU53" s="45" t="e">
+      <c r="AU53" s="44" t="e">
         <f t="shared" ca="1" si="1"/>
         <v>#REF!</v>
       </c>
@@ -17778,7 +17970,7 @@
       <c r="L54" t="s">
         <v>203</v>
       </c>
-      <c r="AU54" s="45" t="e">
+      <c r="AU54" s="44" t="e">
         <f t="shared" ca="1" si="1"/>
         <v>#REF!</v>
       </c>
@@ -17798,7 +17990,7 @@
       <c r="L55" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="AU55" s="45" t="e">
+      <c r="AU55" s="44" t="e">
         <f t="shared" ca="1" si="1"/>
         <v>#REF!</v>
       </c>
@@ -17816,7 +18008,7 @@
       <c r="I56" s="18"/>
       <c r="J56" s="18"/>
       <c r="L56" s="28"/>
-      <c r="AU56" s="45" t="e">
+      <c r="AU56" s="44" t="e">
         <f t="shared" ca="1" si="1"/>
         <v>#REF!</v>
       </c>
@@ -17834,7 +18026,7 @@
       <c r="I57" s="18"/>
       <c r="J57" s="18"/>
       <c r="L57" s="28"/>
-      <c r="AU57" s="45" t="e">
+      <c r="AU57" s="44" t="e">
         <f t="shared" ca="1" si="1"/>
         <v>#REF!</v>
       </c>
@@ -17851,7 +18043,7 @@
       </c>
       <c r="I58" s="18"/>
       <c r="J58" s="18"/>
-      <c r="AU58" s="45" t="e">
+      <c r="AU58" s="44" t="e">
         <f t="shared" ca="1" si="1"/>
         <v>#REF!</v>
       </c>
@@ -17868,7 +18060,7 @@
       </c>
       <c r="I59" s="18"/>
       <c r="J59" s="18"/>
-      <c r="AU59" s="45" t="e">
+      <c r="AU59" s="44" t="e">
         <f t="shared" ca="1" si="1"/>
         <v>#REF!</v>
       </c>
@@ -17885,7 +18077,7 @@
       </c>
       <c r="I60" s="18"/>
       <c r="J60" s="18"/>
-      <c r="AU60" s="45" t="e">
+      <c r="AU60" s="44" t="e">
         <f t="shared" ca="1" si="1"/>
         <v>#REF!</v>
       </c>
@@ -17902,7 +18094,7 @@
       </c>
       <c r="I61" s="18"/>
       <c r="J61" s="18"/>
-      <c r="AU61" s="45" t="e">
+      <c r="AU61" s="44" t="e">
         <f t="shared" ca="1" si="1"/>
         <v>#REF!</v>
       </c>
@@ -17919,7 +18111,7 @@
       </c>
       <c r="I62" s="18"/>
       <c r="J62" s="18"/>
-      <c r="AU62" s="45" t="e">
+      <c r="AU62" s="44" t="e">
         <f t="shared" ca="1" si="1"/>
         <v>#REF!</v>
       </c>
@@ -17936,7 +18128,7 @@
       </c>
       <c r="I63" s="18"/>
       <c r="J63" s="18"/>
-      <c r="AU63" s="45" t="e">
+      <c r="AU63" s="44" t="e">
         <f t="shared" ca="1" si="1"/>
         <v>#REF!</v>
       </c>
@@ -17953,7 +18145,7 @@
       </c>
       <c r="I64" s="18"/>
       <c r="J64" s="18"/>
-      <c r="AU64" s="45" t="e">
+      <c r="AU64" s="44" t="e">
         <f t="shared" ca="1" si="1"/>
         <v>#REF!</v>
       </c>
@@ -17970,7 +18162,7 @@
       </c>
       <c r="I65" s="18"/>
       <c r="J65" s="18"/>
-      <c r="AU65" s="45" t="e">
+      <c r="AU65" s="44" t="e">
         <f t="shared" ca="1" si="1"/>
         <v>#REF!</v>
       </c>
@@ -17987,7 +18179,7 @@
       </c>
       <c r="I66" s="18"/>
       <c r="J66" s="18"/>
-      <c r="AU66" s="45" t="e">
+      <c r="AU66" s="44" t="e">
         <f t="shared" ca="1" si="1"/>
         <v>#REF!</v>
       </c>
@@ -18004,7 +18196,7 @@
       </c>
       <c r="I67" s="18"/>
       <c r="J67" s="18"/>
-      <c r="AU67" s="45" t="e">
+      <c r="AU67" s="44" t="e">
         <f t="shared" ca="1" si="1"/>
         <v>#REF!</v>
       </c>
@@ -18021,7 +18213,7 @@
       </c>
       <c r="I68" s="18"/>
       <c r="J68" s="18"/>
-      <c r="AU68" s="45" t="e">
+      <c r="AU68" s="44" t="e">
         <f t="shared" ref="AU68:AU131" ca="1" si="3">_xlfn.IFNA(IF($H68+1&gt;$G$2,"",INDEX(INDIRECT("SubnetsVLANs!$D$"&amp;$H68+2&amp;":$D$"&amp;$G$2),MATCH("Subnet*",INDIRECT("SubnetsVLANs!$E$"&amp;$H68+2&amp;":$E$"&amp;$G$2),0))),"")</f>
         <v>#REF!</v>
       </c>
@@ -18038,7 +18230,7 @@
       </c>
       <c r="I69" s="18"/>
       <c r="J69" s="18"/>
-      <c r="AU69" s="45" t="e">
+      <c r="AU69" s="44" t="e">
         <f t="shared" ca="1" si="3"/>
         <v>#REF!</v>
       </c>
@@ -18055,7 +18247,7 @@
       </c>
       <c r="I70" s="18"/>
       <c r="J70" s="18"/>
-      <c r="AU70" s="45" t="e">
+      <c r="AU70" s="44" t="e">
         <f t="shared" ca="1" si="3"/>
         <v>#REF!</v>
       </c>
@@ -18072,7 +18264,7 @@
       </c>
       <c r="I71" s="18"/>
       <c r="J71" s="18"/>
-      <c r="AU71" s="45" t="e">
+      <c r="AU71" s="44" t="e">
         <f t="shared" ca="1" si="3"/>
         <v>#REF!</v>
       </c>
@@ -18089,7 +18281,7 @@
       </c>
       <c r="I72" s="18"/>
       <c r="J72" s="18"/>
-      <c r="AU72" s="45" t="e">
+      <c r="AU72" s="44" t="e">
         <f t="shared" ca="1" si="3"/>
         <v>#REF!</v>
       </c>
@@ -18106,7 +18298,7 @@
       </c>
       <c r="I73" s="18"/>
       <c r="J73" s="18"/>
-      <c r="AU73" s="45" t="e">
+      <c r="AU73" s="44" t="e">
         <f t="shared" ca="1" si="3"/>
         <v>#REF!</v>
       </c>
@@ -18123,7 +18315,7 @@
       </c>
       <c r="I74" s="18"/>
       <c r="J74" s="18"/>
-      <c r="AU74" s="45" t="e">
+      <c r="AU74" s="44" t="e">
         <f t="shared" ca="1" si="3"/>
         <v>#REF!</v>
       </c>
@@ -18140,7 +18332,7 @@
       </c>
       <c r="I75" s="18"/>
       <c r="J75" s="18"/>
-      <c r="AU75" s="45" t="e">
+      <c r="AU75" s="44" t="e">
         <f t="shared" ca="1" si="3"/>
         <v>#REF!</v>
       </c>
@@ -18157,7 +18349,7 @@
       </c>
       <c r="I76" s="18"/>
       <c r="J76" s="18"/>
-      <c r="AU76" s="45" t="e">
+      <c r="AU76" s="44" t="e">
         <f t="shared" ca="1" si="3"/>
         <v>#REF!</v>
       </c>
@@ -18174,7 +18366,7 @@
       </c>
       <c r="I77" s="18"/>
       <c r="J77" s="18"/>
-      <c r="AU77" s="45" t="e">
+      <c r="AU77" s="44" t="e">
         <f t="shared" ca="1" si="3"/>
         <v>#REF!</v>
       </c>
@@ -18191,7 +18383,7 @@
       </c>
       <c r="I78" s="18"/>
       <c r="J78" s="18"/>
-      <c r="AU78" s="45" t="e">
+      <c r="AU78" s="44" t="e">
         <f t="shared" ca="1" si="3"/>
         <v>#REF!</v>
       </c>
@@ -18208,7 +18400,7 @@
       </c>
       <c r="I79" s="18"/>
       <c r="J79" s="18"/>
-      <c r="AU79" s="45" t="e">
+      <c r="AU79" s="44" t="e">
         <f t="shared" ca="1" si="3"/>
         <v>#REF!</v>
       </c>
@@ -18225,7 +18417,7 @@
       </c>
       <c r="I80" s="18"/>
       <c r="J80" s="18"/>
-      <c r="AU80" s="45" t="e">
+      <c r="AU80" s="44" t="e">
         <f t="shared" ca="1" si="3"/>
         <v>#REF!</v>
       </c>
@@ -18242,7 +18434,7 @@
       </c>
       <c r="I81" s="18"/>
       <c r="J81" s="18"/>
-      <c r="AU81" s="45" t="e">
+      <c r="AU81" s="44" t="e">
         <f t="shared" ca="1" si="3"/>
         <v>#REF!</v>
       </c>
@@ -18259,7 +18451,7 @@
       </c>
       <c r="I82" s="18"/>
       <c r="J82" s="18"/>
-      <c r="AU82" s="45" t="e">
+      <c r="AU82" s="44" t="e">
         <f t="shared" ca="1" si="3"/>
         <v>#REF!</v>
       </c>
@@ -18276,7 +18468,7 @@
       </c>
       <c r="I83" s="18"/>
       <c r="J83" s="18"/>
-      <c r="AU83" s="45" t="e">
+      <c r="AU83" s="44" t="e">
         <f t="shared" ca="1" si="3"/>
         <v>#REF!</v>
       </c>
@@ -18293,7 +18485,7 @@
       </c>
       <c r="I84" s="18"/>
       <c r="J84" s="18"/>
-      <c r="AU84" s="45" t="e">
+      <c r="AU84" s="44" t="e">
         <f t="shared" ca="1" si="3"/>
         <v>#REF!</v>
       </c>
@@ -18310,7 +18502,7 @@
       </c>
       <c r="I85" s="18"/>
       <c r="J85" s="18"/>
-      <c r="AU85" s="45" t="e">
+      <c r="AU85" s="44" t="e">
         <f t="shared" ca="1" si="3"/>
         <v>#REF!</v>
       </c>
@@ -18327,7 +18519,7 @@
       </c>
       <c r="I86" s="18"/>
       <c r="J86" s="18"/>
-      <c r="AU86" s="45" t="e">
+      <c r="AU86" s="44" t="e">
         <f t="shared" ca="1" si="3"/>
         <v>#REF!</v>
       </c>
@@ -18344,7 +18536,7 @@
       </c>
       <c r="I87" s="18"/>
       <c r="J87" s="18"/>
-      <c r="AU87" s="45" t="e">
+      <c r="AU87" s="44" t="e">
         <f t="shared" ca="1" si="3"/>
         <v>#REF!</v>
       </c>
@@ -18361,7 +18553,7 @@
       </c>
       <c r="I88" s="18"/>
       <c r="J88" s="18"/>
-      <c r="AU88" s="45" t="e">
+      <c r="AU88" s="44" t="e">
         <f t="shared" ca="1" si="3"/>
         <v>#REF!</v>
       </c>
@@ -18378,7 +18570,7 @@
       </c>
       <c r="I89" s="18"/>
       <c r="J89" s="18"/>
-      <c r="AU89" s="45" t="e">
+      <c r="AU89" s="44" t="e">
         <f t="shared" ca="1" si="3"/>
         <v>#REF!</v>
       </c>
@@ -18395,7 +18587,7 @@
       </c>
       <c r="I90" s="18"/>
       <c r="J90" s="18"/>
-      <c r="AU90" s="45" t="e">
+      <c r="AU90" s="44" t="e">
         <f t="shared" ca="1" si="3"/>
         <v>#REF!</v>
       </c>
@@ -18412,7 +18604,7 @@
       </c>
       <c r="I91" s="18"/>
       <c r="J91" s="18"/>
-      <c r="AU91" s="45" t="e">
+      <c r="AU91" s="44" t="e">
         <f t="shared" ca="1" si="3"/>
         <v>#REF!</v>
       </c>
@@ -18429,7 +18621,7 @@
       </c>
       <c r="I92" s="18"/>
       <c r="J92" s="18"/>
-      <c r="AU92" s="45" t="e">
+      <c r="AU92" s="44" t="e">
         <f t="shared" ca="1" si="3"/>
         <v>#REF!</v>
       </c>
@@ -18446,7 +18638,7 @@
       </c>
       <c r="I93" s="18"/>
       <c r="J93" s="18"/>
-      <c r="AU93" s="45" t="e">
+      <c r="AU93" s="44" t="e">
         <f t="shared" ca="1" si="3"/>
         <v>#REF!</v>
       </c>
@@ -18463,7 +18655,7 @@
       </c>
       <c r="I94" s="18"/>
       <c r="J94" s="18"/>
-      <c r="AU94" s="45" t="e">
+      <c r="AU94" s="44" t="e">
         <f t="shared" ca="1" si="3"/>
         <v>#REF!</v>
       </c>
@@ -18480,7 +18672,7 @@
       </c>
       <c r="I95" s="18"/>
       <c r="J95" s="18"/>
-      <c r="AU95" s="45" t="e">
+      <c r="AU95" s="44" t="e">
         <f t="shared" ca="1" si="3"/>
         <v>#REF!</v>
       </c>
@@ -18497,7 +18689,7 @@
       </c>
       <c r="I96" s="18"/>
       <c r="J96" s="18"/>
-      <c r="AU96" s="45" t="e">
+      <c r="AU96" s="44" t="e">
         <f t="shared" ca="1" si="3"/>
         <v>#REF!</v>
       </c>
@@ -18514,7 +18706,7 @@
       </c>
       <c r="I97" s="18"/>
       <c r="J97" s="18"/>
-      <c r="AU97" s="45" t="e">
+      <c r="AU97" s="44" t="e">
         <f t="shared" ca="1" si="3"/>
         <v>#REF!</v>
       </c>
@@ -18531,7 +18723,7 @@
       </c>
       <c r="I98" s="18"/>
       <c r="J98" s="18"/>
-      <c r="AU98" s="45" t="e">
+      <c r="AU98" s="44" t="e">
         <f t="shared" ca="1" si="3"/>
         <v>#REF!</v>
       </c>
@@ -18548,7 +18740,7 @@
       </c>
       <c r="I99" s="18"/>
       <c r="J99" s="18"/>
-      <c r="AU99" s="45" t="e">
+      <c r="AU99" s="44" t="e">
         <f t="shared" ca="1" si="3"/>
         <v>#REF!</v>
       </c>
@@ -18565,7 +18757,7 @@
       </c>
       <c r="I100" s="18"/>
       <c r="J100" s="18"/>
-      <c r="AU100" s="45" t="e">
+      <c r="AU100" s="44" t="e">
         <f t="shared" ca="1" si="3"/>
         <v>#REF!</v>
       </c>
@@ -18582,7 +18774,7 @@
       </c>
       <c r="I101" s="18"/>
       <c r="J101" s="18"/>
-      <c r="AU101" s="45" t="e">
+      <c r="AU101" s="44" t="e">
         <f t="shared" ca="1" si="3"/>
         <v>#REF!</v>
       </c>
@@ -18599,7 +18791,7 @@
       </c>
       <c r="I102" s="18"/>
       <c r="J102" s="18"/>
-      <c r="AU102" s="45" t="e">
+      <c r="AU102" s="44" t="e">
         <f t="shared" ca="1" si="3"/>
         <v>#REF!</v>
       </c>
@@ -18616,7 +18808,7 @@
       </c>
       <c r="I103" s="18"/>
       <c r="J103" s="18"/>
-      <c r="AU103" s="45" t="e">
+      <c r="AU103" s="44" t="e">
         <f t="shared" ca="1" si="3"/>
         <v>#REF!</v>
       </c>
@@ -18633,7 +18825,7 @@
       </c>
       <c r="I104" s="18"/>
       <c r="J104" s="18"/>
-      <c r="AU104" s="45" t="e">
+      <c r="AU104" s="44" t="e">
         <f t="shared" ca="1" si="3"/>
         <v>#REF!</v>
       </c>
@@ -18650,7 +18842,7 @@
       </c>
       <c r="I105" s="18"/>
       <c r="J105" s="18"/>
-      <c r="AU105" s="45" t="e">
+      <c r="AU105" s="44" t="e">
         <f t="shared" ca="1" si="3"/>
         <v>#REF!</v>
       </c>
@@ -18667,7 +18859,7 @@
       </c>
       <c r="I106" s="18"/>
       <c r="J106" s="18"/>
-      <c r="AU106" s="45" t="e">
+      <c r="AU106" s="44" t="e">
         <f t="shared" ca="1" si="3"/>
         <v>#REF!</v>
       </c>
@@ -18684,7 +18876,7 @@
       </c>
       <c r="I107" s="18"/>
       <c r="J107" s="18"/>
-      <c r="AU107" s="45" t="e">
+      <c r="AU107" s="44" t="e">
         <f t="shared" ca="1" si="3"/>
         <v>#REF!</v>
       </c>
@@ -18701,7 +18893,7 @@
       </c>
       <c r="I108" s="18"/>
       <c r="J108" s="18"/>
-      <c r="AU108" s="45" t="e">
+      <c r="AU108" s="44" t="e">
         <f t="shared" ca="1" si="3"/>
         <v>#REF!</v>
       </c>
@@ -18718,7 +18910,7 @@
       </c>
       <c r="I109" s="18"/>
       <c r="J109" s="18"/>
-      <c r="AU109" s="45" t="e">
+      <c r="AU109" s="44" t="e">
         <f t="shared" ca="1" si="3"/>
         <v>#REF!</v>
       </c>
@@ -18735,7 +18927,7 @@
       </c>
       <c r="I110" s="18"/>
       <c r="J110" s="18"/>
-      <c r="AU110" s="45" t="e">
+      <c r="AU110" s="44" t="e">
         <f t="shared" ca="1" si="3"/>
         <v>#REF!</v>
       </c>
@@ -18752,7 +18944,7 @@
       </c>
       <c r="I111" s="18"/>
       <c r="J111" s="18"/>
-      <c r="AU111" s="45" t="e">
+      <c r="AU111" s="44" t="e">
         <f t="shared" ca="1" si="3"/>
         <v>#REF!</v>
       </c>
@@ -18769,7 +18961,7 @@
       </c>
       <c r="I112" s="18"/>
       <c r="J112" s="18"/>
-      <c r="AU112" s="45" t="e">
+      <c r="AU112" s="44" t="e">
         <f t="shared" ca="1" si="3"/>
         <v>#REF!</v>
       </c>
@@ -18786,7 +18978,7 @@
       </c>
       <c r="I113" s="18"/>
       <c r="J113" s="18"/>
-      <c r="AU113" s="45" t="e">
+      <c r="AU113" s="44" t="e">
         <f t="shared" ca="1" si="3"/>
         <v>#REF!</v>
       </c>
@@ -18803,7 +18995,7 @@
       </c>
       <c r="I114" s="18"/>
       <c r="J114" s="18"/>
-      <c r="AU114" s="45" t="e">
+      <c r="AU114" s="44" t="e">
         <f t="shared" ca="1" si="3"/>
         <v>#REF!</v>
       </c>
@@ -18820,7 +19012,7 @@
       </c>
       <c r="I115" s="18"/>
       <c r="J115" s="18"/>
-      <c r="AU115" s="45" t="e">
+      <c r="AU115" s="44" t="e">
         <f t="shared" ca="1" si="3"/>
         <v>#REF!</v>
       </c>
@@ -18837,7 +19029,7 @@
       </c>
       <c r="I116" s="18"/>
       <c r="J116" s="18"/>
-      <c r="AU116" s="45" t="e">
+      <c r="AU116" s="44" t="e">
         <f t="shared" ca="1" si="3"/>
         <v>#REF!</v>
       </c>
@@ -18854,7 +19046,7 @@
       </c>
       <c r="I117" s="18"/>
       <c r="J117" s="18"/>
-      <c r="AU117" s="45" t="e">
+      <c r="AU117" s="44" t="e">
         <f t="shared" ca="1" si="3"/>
         <v>#REF!</v>
       </c>
@@ -18871,7 +19063,7 @@
       </c>
       <c r="I118" s="18"/>
       <c r="J118" s="18"/>
-      <c r="AU118" s="45" t="e">
+      <c r="AU118" s="44" t="e">
         <f t="shared" ca="1" si="3"/>
         <v>#REF!</v>
       </c>
@@ -18888,7 +19080,7 @@
       </c>
       <c r="I119" s="18"/>
       <c r="J119" s="18"/>
-      <c r="AU119" s="45" t="e">
+      <c r="AU119" s="44" t="e">
         <f t="shared" ca="1" si="3"/>
         <v>#REF!</v>
       </c>
@@ -18905,7 +19097,7 @@
       </c>
       <c r="I120" s="18"/>
       <c r="J120" s="18"/>
-      <c r="AU120" s="45" t="e">
+      <c r="AU120" s="44" t="e">
         <f t="shared" ca="1" si="3"/>
         <v>#REF!</v>
       </c>
@@ -18922,7 +19114,7 @@
       </c>
       <c r="I121" s="18"/>
       <c r="J121" s="18"/>
-      <c r="AU121" s="45" t="e">
+      <c r="AU121" s="44" t="e">
         <f t="shared" ca="1" si="3"/>
         <v>#REF!</v>
       </c>
@@ -18939,7 +19131,7 @@
       </c>
       <c r="I122" s="18"/>
       <c r="J122" s="18"/>
-      <c r="AU122" s="45" t="e">
+      <c r="AU122" s="44" t="e">
         <f t="shared" ca="1" si="3"/>
         <v>#REF!</v>
       </c>
@@ -18956,7 +19148,7 @@
       </c>
       <c r="I123" s="18"/>
       <c r="J123" s="18"/>
-      <c r="AU123" s="45" t="e">
+      <c r="AU123" s="44" t="e">
         <f t="shared" ca="1" si="3"/>
         <v>#REF!</v>
       </c>
@@ -18973,7 +19165,7 @@
       </c>
       <c r="I124" s="18"/>
       <c r="J124" s="18"/>
-      <c r="AU124" s="45" t="e">
+      <c r="AU124" s="44" t="e">
         <f t="shared" ca="1" si="3"/>
         <v>#REF!</v>
       </c>
@@ -18990,7 +19182,7 @@
       </c>
       <c r="I125" s="18"/>
       <c r="J125" s="18"/>
-      <c r="AU125" s="45" t="e">
+      <c r="AU125" s="44" t="e">
         <f t="shared" ca="1" si="3"/>
         <v>#REF!</v>
       </c>
@@ -19007,7 +19199,7 @@
       </c>
       <c r="I126" s="18"/>
       <c r="J126" s="18"/>
-      <c r="AU126" s="45" t="e">
+      <c r="AU126" s="44" t="e">
         <f t="shared" ca="1" si="3"/>
         <v>#REF!</v>
       </c>
@@ -19024,7 +19216,7 @@
       </c>
       <c r="I127" s="18"/>
       <c r="J127" s="18"/>
-      <c r="AU127" s="45" t="e">
+      <c r="AU127" s="44" t="e">
         <f t="shared" ca="1" si="3"/>
         <v>#REF!</v>
       </c>
@@ -19041,7 +19233,7 @@
       </c>
       <c r="I128" s="18"/>
       <c r="J128" s="18"/>
-      <c r="AU128" s="45" t="e">
+      <c r="AU128" s="44" t="e">
         <f t="shared" ca="1" si="3"/>
         <v>#REF!</v>
       </c>
@@ -19058,7 +19250,7 @@
       </c>
       <c r="I129" s="18"/>
       <c r="J129" s="18"/>
-      <c r="AU129" s="45" t="e">
+      <c r="AU129" s="44" t="e">
         <f t="shared" ca="1" si="3"/>
         <v>#REF!</v>
       </c>
@@ -19075,7 +19267,7 @@
       </c>
       <c r="I130" s="18"/>
       <c r="J130" s="18"/>
-      <c r="AU130" s="45" t="e">
+      <c r="AU130" s="44" t="e">
         <f t="shared" ca="1" si="3"/>
         <v>#REF!</v>
       </c>
@@ -19092,7 +19284,7 @@
       </c>
       <c r="I131" s="18"/>
       <c r="J131" s="18"/>
-      <c r="AU131" s="45" t="e">
+      <c r="AU131" s="44" t="e">
         <f t="shared" ca="1" si="3"/>
         <v>#REF!</v>
       </c>
@@ -19109,7 +19301,7 @@
       </c>
       <c r="I132" s="18"/>
       <c r="J132" s="18"/>
-      <c r="AU132" s="45" t="e">
+      <c r="AU132" s="44" t="e">
         <f t="shared" ref="AU132:AU195" ca="1" si="5">_xlfn.IFNA(IF($H132+1&gt;$G$2,"",INDEX(INDIRECT("SubnetsVLANs!$D$"&amp;$H132+2&amp;":$D$"&amp;$G$2),MATCH("Subnet*",INDIRECT("SubnetsVLANs!$E$"&amp;$H132+2&amp;":$E$"&amp;$G$2),0))),"")</f>
         <v>#REF!</v>
       </c>
@@ -19126,7 +19318,7 @@
       </c>
       <c r="I133" s="18"/>
       <c r="J133" s="18"/>
-      <c r="AU133" s="45" t="e">
+      <c r="AU133" s="44" t="e">
         <f t="shared" ca="1" si="5"/>
         <v>#REF!</v>
       </c>
@@ -19143,7 +19335,7 @@
       </c>
       <c r="I134" s="18"/>
       <c r="J134" s="18"/>
-      <c r="AU134" s="45" t="e">
+      <c r="AU134" s="44" t="e">
         <f t="shared" ca="1" si="5"/>
         <v>#REF!</v>
       </c>
@@ -19160,7 +19352,7 @@
       </c>
       <c r="I135" s="18"/>
       <c r="J135" s="18"/>
-      <c r="AU135" s="45" t="e">
+      <c r="AU135" s="44" t="e">
         <f t="shared" ca="1" si="5"/>
         <v>#REF!</v>
       </c>
@@ -19177,7 +19369,7 @@
       </c>
       <c r="I136" s="18"/>
       <c r="J136" s="18"/>
-      <c r="AU136" s="45" t="e">
+      <c r="AU136" s="44" t="e">
         <f t="shared" ca="1" si="5"/>
         <v>#REF!</v>
       </c>
@@ -19194,7 +19386,7 @@
       </c>
       <c r="I137" s="18"/>
       <c r="J137" s="18"/>
-      <c r="AU137" s="45" t="e">
+      <c r="AU137" s="44" t="e">
         <f t="shared" ca="1" si="5"/>
         <v>#REF!</v>
       </c>
@@ -19211,7 +19403,7 @@
       </c>
       <c r="I138" s="18"/>
       <c r="J138" s="18"/>
-      <c r="AU138" s="45" t="e">
+      <c r="AU138" s="44" t="e">
         <f t="shared" ca="1" si="5"/>
         <v>#REF!</v>
       </c>
@@ -19228,7 +19420,7 @@
       </c>
       <c r="I139" s="18"/>
       <c r="J139" s="18"/>
-      <c r="AU139" s="45" t="e">
+      <c r="AU139" s="44" t="e">
         <f t="shared" ca="1" si="5"/>
         <v>#REF!</v>
       </c>
@@ -19245,7 +19437,7 @@
       </c>
       <c r="I140" s="18"/>
       <c r="J140" s="18"/>
-      <c r="AU140" s="45" t="e">
+      <c r="AU140" s="44" t="e">
         <f t="shared" ca="1" si="5"/>
         <v>#REF!</v>
       </c>
@@ -19262,7 +19454,7 @@
       </c>
       <c r="I141" s="18"/>
       <c r="J141" s="18"/>
-      <c r="AU141" s="45" t="e">
+      <c r="AU141" s="44" t="e">
         <f t="shared" ca="1" si="5"/>
         <v>#REF!</v>
       </c>
@@ -19279,7 +19471,7 @@
       </c>
       <c r="I142" s="18"/>
       <c r="J142" s="18"/>
-      <c r="AU142" s="45" t="e">
+      <c r="AU142" s="44" t="e">
         <f t="shared" ca="1" si="5"/>
         <v>#REF!</v>
       </c>
@@ -19296,7 +19488,7 @@
       </c>
       <c r="I143" s="18"/>
       <c r="J143" s="18"/>
-      <c r="AU143" s="45" t="e">
+      <c r="AU143" s="44" t="e">
         <f t="shared" ca="1" si="5"/>
         <v>#REF!</v>
       </c>
@@ -19313,7 +19505,7 @@
       </c>
       <c r="I144" s="18"/>
       <c r="J144" s="18"/>
-      <c r="AU144" s="45" t="e">
+      <c r="AU144" s="44" t="e">
         <f t="shared" ca="1" si="5"/>
         <v>#REF!</v>
       </c>
@@ -19330,7 +19522,7 @@
       </c>
       <c r="I145" s="18"/>
       <c r="J145" s="18"/>
-      <c r="AU145" s="45" t="e">
+      <c r="AU145" s="44" t="e">
         <f t="shared" ca="1" si="5"/>
         <v>#REF!</v>
       </c>
@@ -19347,7 +19539,7 @@
       </c>
       <c r="I146" s="18"/>
       <c r="J146" s="18"/>
-      <c r="AU146" s="45" t="e">
+      <c r="AU146" s="44" t="e">
         <f t="shared" ca="1" si="5"/>
         <v>#REF!</v>
       </c>
@@ -19364,7 +19556,7 @@
       </c>
       <c r="I147" s="18"/>
       <c r="J147" s="18"/>
-      <c r="AU147" s="45" t="e">
+      <c r="AU147" s="44" t="e">
         <f t="shared" ca="1" si="5"/>
         <v>#REF!</v>
       </c>
@@ -19381,7 +19573,7 @@
       </c>
       <c r="I148" s="18"/>
       <c r="J148" s="18"/>
-      <c r="AU148" s="45" t="e">
+      <c r="AU148" s="44" t="e">
         <f t="shared" ca="1" si="5"/>
         <v>#REF!</v>
       </c>
@@ -19398,7 +19590,7 @@
       </c>
       <c r="I149" s="18"/>
       <c r="J149" s="18"/>
-      <c r="AU149" s="45" t="e">
+      <c r="AU149" s="44" t="e">
         <f t="shared" ca="1" si="5"/>
         <v>#REF!</v>
       </c>
@@ -19415,7 +19607,7 @@
       </c>
       <c r="I150" s="18"/>
       <c r="J150" s="18"/>
-      <c r="AU150" s="45" t="e">
+      <c r="AU150" s="44" t="e">
         <f t="shared" ca="1" si="5"/>
         <v>#REF!</v>
       </c>
@@ -19432,7 +19624,7 @@
       </c>
       <c r="I151" s="18"/>
       <c r="J151" s="18"/>
-      <c r="AU151" s="45" t="e">
+      <c r="AU151" s="44" t="e">
         <f t="shared" ca="1" si="5"/>
         <v>#REF!</v>
       </c>
@@ -19449,7 +19641,7 @@
       </c>
       <c r="I152" s="18"/>
       <c r="J152" s="18"/>
-      <c r="AU152" s="45" t="e">
+      <c r="AU152" s="44" t="e">
         <f t="shared" ca="1" si="5"/>
         <v>#REF!</v>
       </c>
@@ -19466,7 +19658,7 @@
       </c>
       <c r="I153" s="18"/>
       <c r="J153" s="18"/>
-      <c r="AU153" s="45" t="e">
+      <c r="AU153" s="44" t="e">
         <f t="shared" ca="1" si="5"/>
         <v>#REF!</v>
       </c>
@@ -19483,7 +19675,7 @@
       </c>
       <c r="I154" s="18"/>
       <c r="J154" s="18"/>
-      <c r="AU154" s="45" t="e">
+      <c r="AU154" s="44" t="e">
         <f t="shared" ca="1" si="5"/>
         <v>#REF!</v>
       </c>
@@ -19500,7 +19692,7 @@
       </c>
       <c r="I155" s="18"/>
       <c r="J155" s="18"/>
-      <c r="AU155" s="45" t="e">
+      <c r="AU155" s="44" t="e">
         <f t="shared" ca="1" si="5"/>
         <v>#REF!</v>
       </c>
@@ -19517,7 +19709,7 @@
       </c>
       <c r="I156" s="18"/>
       <c r="J156" s="18"/>
-      <c r="AU156" s="45" t="e">
+      <c r="AU156" s="44" t="e">
         <f t="shared" ca="1" si="5"/>
         <v>#REF!</v>
       </c>
@@ -19534,7 +19726,7 @@
       </c>
       <c r="I157" s="18"/>
       <c r="J157" s="18"/>
-      <c r="AU157" s="45" t="e">
+      <c r="AU157" s="44" t="e">
         <f t="shared" ca="1" si="5"/>
         <v>#REF!</v>
       </c>
@@ -19551,7 +19743,7 @@
       </c>
       <c r="I158" s="18"/>
       <c r="J158" s="18"/>
-      <c r="AU158" s="45" t="e">
+      <c r="AU158" s="44" t="e">
         <f t="shared" ca="1" si="5"/>
         <v>#REF!</v>
       </c>
@@ -19568,7 +19760,7 @@
       </c>
       <c r="I159" s="18"/>
       <c r="J159" s="18"/>
-      <c r="AU159" s="45" t="e">
+      <c r="AU159" s="44" t="e">
         <f t="shared" ca="1" si="5"/>
         <v>#REF!</v>
       </c>
@@ -19585,7 +19777,7 @@
       </c>
       <c r="I160" s="18"/>
       <c r="J160" s="18"/>
-      <c r="AU160" s="45" t="e">
+      <c r="AU160" s="44" t="e">
         <f t="shared" ca="1" si="5"/>
         <v>#REF!</v>
       </c>
@@ -19602,7 +19794,7 @@
       </c>
       <c r="I161" s="18"/>
       <c r="J161" s="18"/>
-      <c r="AU161" s="45" t="e">
+      <c r="AU161" s="44" t="e">
         <f t="shared" ca="1" si="5"/>
         <v>#REF!</v>
       </c>
@@ -19619,7 +19811,7 @@
       </c>
       <c r="I162" s="18"/>
       <c r="J162" s="18"/>
-      <c r="AU162" s="45" t="e">
+      <c r="AU162" s="44" t="e">
         <f t="shared" ca="1" si="5"/>
         <v>#REF!</v>
       </c>
@@ -19636,7 +19828,7 @@
       </c>
       <c r="I163" s="18"/>
       <c r="J163" s="18"/>
-      <c r="AU163" s="45" t="e">
+      <c r="AU163" s="44" t="e">
         <f t="shared" ca="1" si="5"/>
         <v>#REF!</v>
       </c>
@@ -19653,7 +19845,7 @@
       </c>
       <c r="I164" s="18"/>
       <c r="J164" s="18"/>
-      <c r="AU164" s="45" t="e">
+      <c r="AU164" s="44" t="e">
         <f t="shared" ca="1" si="5"/>
         <v>#REF!</v>
       </c>
@@ -19670,7 +19862,7 @@
       </c>
       <c r="I165" s="18"/>
       <c r="J165" s="18"/>
-      <c r="AU165" s="45" t="e">
+      <c r="AU165" s="44" t="e">
         <f t="shared" ca="1" si="5"/>
         <v>#REF!</v>
       </c>
@@ -19687,7 +19879,7 @@
       </c>
       <c r="I166" s="18"/>
       <c r="J166" s="18"/>
-      <c r="AU166" s="45" t="e">
+      <c r="AU166" s="44" t="e">
         <f t="shared" ca="1" si="5"/>
         <v>#REF!</v>
       </c>
@@ -19704,7 +19896,7 @@
       </c>
       <c r="I167" s="18"/>
       <c r="J167" s="18"/>
-      <c r="AU167" s="45" t="e">
+      <c r="AU167" s="44" t="e">
         <f t="shared" ca="1" si="5"/>
         <v>#REF!</v>
       </c>
@@ -19721,7 +19913,7 @@
       </c>
       <c r="I168" s="18"/>
       <c r="J168" s="18"/>
-      <c r="AU168" s="45" t="e">
+      <c r="AU168" s="44" t="e">
         <f t="shared" ca="1" si="5"/>
         <v>#REF!</v>
       </c>
@@ -19738,7 +19930,7 @@
       </c>
       <c r="I169" s="18"/>
       <c r="J169" s="18"/>
-      <c r="AU169" s="45" t="e">
+      <c r="AU169" s="44" t="e">
         <f t="shared" ca="1" si="5"/>
         <v>#REF!</v>
       </c>
@@ -19755,7 +19947,7 @@
       </c>
       <c r="I170" s="18"/>
       <c r="J170" s="18"/>
-      <c r="AU170" s="45" t="e">
+      <c r="AU170" s="44" t="e">
         <f t="shared" ca="1" si="5"/>
         <v>#REF!</v>
       </c>
@@ -19772,7 +19964,7 @@
       </c>
       <c r="I171" s="18"/>
       <c r="J171" s="18"/>
-      <c r="AU171" s="45" t="e">
+      <c r="AU171" s="44" t="e">
         <f t="shared" ca="1" si="5"/>
         <v>#REF!</v>
       </c>
@@ -19789,7 +19981,7 @@
       </c>
       <c r="I172" s="18"/>
       <c r="J172" s="18"/>
-      <c r="AU172" s="45" t="e">
+      <c r="AU172" s="44" t="e">
         <f t="shared" ca="1" si="5"/>
         <v>#REF!</v>
       </c>
@@ -19806,7 +19998,7 @@
       </c>
       <c r="I173" s="18"/>
       <c r="J173" s="18"/>
-      <c r="AU173" s="45" t="e">
+      <c r="AU173" s="44" t="e">
         <f t="shared" ca="1" si="5"/>
         <v>#REF!</v>
       </c>
@@ -19823,7 +20015,7 @@
       </c>
       <c r="I174" s="18"/>
       <c r="J174" s="18"/>
-      <c r="AU174" s="45" t="e">
+      <c r="AU174" s="44" t="e">
         <f t="shared" ca="1" si="5"/>
         <v>#REF!</v>
       </c>
@@ -19840,7 +20032,7 @@
       </c>
       <c r="I175" s="18"/>
       <c r="J175" s="18"/>
-      <c r="AU175" s="45" t="e">
+      <c r="AU175" s="44" t="e">
         <f t="shared" ca="1" si="5"/>
         <v>#REF!</v>
       </c>
@@ -19857,7 +20049,7 @@
       </c>
       <c r="I176" s="18"/>
       <c r="J176" s="18"/>
-      <c r="AU176" s="45" t="e">
+      <c r="AU176" s="44" t="e">
         <f t="shared" ca="1" si="5"/>
         <v>#REF!</v>
       </c>
@@ -19874,7 +20066,7 @@
       </c>
       <c r="I177" s="18"/>
       <c r="J177" s="18"/>
-      <c r="AU177" s="45" t="e">
+      <c r="AU177" s="44" t="e">
         <f t="shared" ca="1" si="5"/>
         <v>#REF!</v>
       </c>
@@ -19891,7 +20083,7 @@
       </c>
       <c r="I178" s="18"/>
       <c r="J178" s="18"/>
-      <c r="AU178" s="45" t="e">
+      <c r="AU178" s="44" t="e">
         <f t="shared" ca="1" si="5"/>
         <v>#REF!</v>
       </c>
@@ -19908,7 +20100,7 @@
       </c>
       <c r="I179" s="18"/>
       <c r="J179" s="18"/>
-      <c r="AU179" s="45" t="e">
+      <c r="AU179" s="44" t="e">
         <f t="shared" ca="1" si="5"/>
         <v>#REF!</v>
       </c>
@@ -19925,7 +20117,7 @@
       </c>
       <c r="I180" s="18"/>
       <c r="J180" s="18"/>
-      <c r="AU180" s="45" t="e">
+      <c r="AU180" s="44" t="e">
         <f t="shared" ca="1" si="5"/>
         <v>#REF!</v>
       </c>
@@ -19942,7 +20134,7 @@
       </c>
       <c r="I181" s="18"/>
       <c r="J181" s="18"/>
-      <c r="AU181" s="45" t="e">
+      <c r="AU181" s="44" t="e">
         <f t="shared" ca="1" si="5"/>
         <v>#REF!</v>
       </c>
@@ -19959,7 +20151,7 @@
       </c>
       <c r="I182" s="18"/>
       <c r="J182" s="18"/>
-      <c r="AU182" s="45" t="e">
+      <c r="AU182" s="44" t="e">
         <f t="shared" ca="1" si="5"/>
         <v>#REF!</v>
       </c>
@@ -19976,7 +20168,7 @@
       </c>
       <c r="I183" s="18"/>
       <c r="J183" s="18"/>
-      <c r="AU183" s="45" t="e">
+      <c r="AU183" s="44" t="e">
         <f t="shared" ca="1" si="5"/>
         <v>#REF!</v>
       </c>
@@ -19993,7 +20185,7 @@
       </c>
       <c r="I184" s="18"/>
       <c r="J184" s="18"/>
-      <c r="AU184" s="45" t="e">
+      <c r="AU184" s="44" t="e">
         <f t="shared" ca="1" si="5"/>
         <v>#REF!</v>
       </c>
@@ -20010,7 +20202,7 @@
       </c>
       <c r="I185" s="18"/>
       <c r="J185" s="18"/>
-      <c r="AU185" s="45" t="e">
+      <c r="AU185" s="44" t="e">
         <f t="shared" ca="1" si="5"/>
         <v>#REF!</v>
       </c>
@@ -20027,7 +20219,7 @@
       </c>
       <c r="I186" s="18"/>
       <c r="J186" s="18"/>
-      <c r="AU186" s="45" t="e">
+      <c r="AU186" s="44" t="e">
         <f t="shared" ca="1" si="5"/>
         <v>#REF!</v>
       </c>
@@ -20044,7 +20236,7 @@
       </c>
       <c r="I187" s="18"/>
       <c r="J187" s="18"/>
-      <c r="AU187" s="45" t="e">
+      <c r="AU187" s="44" t="e">
         <f t="shared" ca="1" si="5"/>
         <v>#REF!</v>
       </c>
@@ -20061,7 +20253,7 @@
       </c>
       <c r="I188" s="18"/>
       <c r="J188" s="18"/>
-      <c r="AU188" s="45" t="e">
+      <c r="AU188" s="44" t="e">
         <f t="shared" ca="1" si="5"/>
         <v>#REF!</v>
       </c>
@@ -20078,7 +20270,7 @@
       </c>
       <c r="I189" s="18"/>
       <c r="J189" s="18"/>
-      <c r="AU189" s="45" t="e">
+      <c r="AU189" s="44" t="e">
         <f t="shared" ca="1" si="5"/>
         <v>#REF!</v>
       </c>
@@ -20095,7 +20287,7 @@
       </c>
       <c r="I190" s="18"/>
       <c r="J190" s="18"/>
-      <c r="AU190" s="45" t="e">
+      <c r="AU190" s="44" t="e">
         <f t="shared" ca="1" si="5"/>
         <v>#REF!</v>
       </c>
@@ -20112,7 +20304,7 @@
       </c>
       <c r="I191" s="18"/>
       <c r="J191" s="18"/>
-      <c r="AU191" s="45" t="e">
+      <c r="AU191" s="44" t="e">
         <f t="shared" ca="1" si="5"/>
         <v>#REF!</v>
       </c>
@@ -20129,7 +20321,7 @@
       </c>
       <c r="I192" s="18"/>
       <c r="J192" s="18"/>
-      <c r="AU192" s="45" t="e">
+      <c r="AU192" s="44" t="e">
         <f t="shared" ca="1" si="5"/>
         <v>#REF!</v>
       </c>
@@ -20146,7 +20338,7 @@
       </c>
       <c r="I193" s="18"/>
       <c r="J193" s="18"/>
-      <c r="AU193" s="45" t="e">
+      <c r="AU193" s="44" t="e">
         <f t="shared" ca="1" si="5"/>
         <v>#REF!</v>
       </c>
@@ -20163,7 +20355,7 @@
       </c>
       <c r="I194" s="18"/>
       <c r="J194" s="18"/>
-      <c r="AU194" s="45" t="e">
+      <c r="AU194" s="44" t="e">
         <f t="shared" ca="1" si="5"/>
         <v>#REF!</v>
       </c>
@@ -20180,7 +20372,7 @@
       </c>
       <c r="I195" s="18"/>
       <c r="J195" s="18"/>
-      <c r="AU195" s="45" t="e">
+      <c r="AU195" s="44" t="e">
         <f t="shared" ca="1" si="5"/>
         <v>#REF!</v>
       </c>
@@ -20197,7 +20389,7 @@
       </c>
       <c r="I196" s="18"/>
       <c r="J196" s="18"/>
-      <c r="AU196" s="45" t="e">
+      <c r="AU196" s="44" t="e">
         <f t="shared" ref="AU196:AU201" ca="1" si="7">_xlfn.IFNA(IF($H196+1&gt;$G$2,"",INDEX(INDIRECT("SubnetsVLANs!$D$"&amp;$H196+2&amp;":$D$"&amp;$G$2),MATCH("Subnet*",INDIRECT("SubnetsVLANs!$E$"&amp;$H196+2&amp;":$E$"&amp;$G$2),0))),"")</f>
         <v>#REF!</v>
       </c>
@@ -20214,7 +20406,7 @@
       </c>
       <c r="I197" s="18"/>
       <c r="J197" s="18"/>
-      <c r="AU197" s="45" t="e">
+      <c r="AU197" s="44" t="e">
         <f t="shared" ca="1" si="7"/>
         <v>#REF!</v>
       </c>
@@ -20231,7 +20423,7 @@
       </c>
       <c r="I198" s="18"/>
       <c r="J198" s="18"/>
-      <c r="AU198" s="45" t="e">
+      <c r="AU198" s="44" t="e">
         <f t="shared" ca="1" si="7"/>
         <v>#REF!</v>
       </c>
@@ -20248,7 +20440,7 @@
       </c>
       <c r="I199" s="18"/>
       <c r="J199" s="18"/>
-      <c r="AU199" s="45" t="e">
+      <c r="AU199" s="44" t="e">
         <f t="shared" ca="1" si="7"/>
         <v>#REF!</v>
       </c>
@@ -20265,7 +20457,7 @@
       </c>
       <c r="I200" s="18"/>
       <c r="J200" s="18"/>
-      <c r="AU200" s="45" t="e">
+      <c r="AU200" s="44" t="e">
         <f t="shared" ca="1" si="7"/>
         <v>#REF!</v>
       </c>
@@ -20282,7 +20474,7 @@
       </c>
       <c r="I201" s="18"/>
       <c r="J201" s="18"/>
-      <c r="AU201" s="45" t="e">
+      <c r="AU201" s="44" t="e">
         <f t="shared" ca="1" si="7"/>
         <v>#REF!</v>
       </c>
